--- a/ABBV.xlsx
+++ b/ABBV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D84578-0538-4CC5-BC8A-92B71B1FBFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F78FE02-1E15-4B4C-8B71-FDA5A40E8783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6800" yWindow="2560" windowWidth="28030" windowHeight="18090" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8220" yWindow="1940" windowWidth="14740" windowHeight="16580" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="4" r:id="rId1"/>
@@ -329,7 +329,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="706">
   <si>
     <t>Humira</t>
   </si>
@@ -2441,6 +2441,12 @@
   </si>
   <si>
     <t>1,707</t>
+  </si>
+  <si>
+    <t>1,677</t>
+  </si>
+  <si>
+    <t>CRL</t>
   </si>
 </sst>
 </file>
@@ -2972,14 +2978,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>94</xdr:col>
-      <xdr:colOff>22762</xdr:colOff>
+      <xdr:col>95</xdr:col>
+      <xdr:colOff>11718</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>94</xdr:col>
-      <xdr:colOff>22762</xdr:colOff>
+      <xdr:col>95</xdr:col>
+      <xdr:colOff>11718</xdr:colOff>
       <xdr:row>161</xdr:row>
       <xdr:rowOff>39414</xdr:rowOff>
     </xdr:to>
@@ -2996,7 +3002,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="60783979" y="0"/>
+          <a:off x="61413457" y="0"/>
           <a:ext cx="0" cy="25848023"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -5218,7 +5224,7 @@
         <v>312</v>
       </c>
       <c r="D25" s="84" t="s">
-        <v>379</v>
+        <v>705</v>
       </c>
       <c r="E25" s="84"/>
       <c r="F25" s="92"/>
@@ -7054,7 +7060,7 @@
       </c>
       <c r="CQ3" s="43">
         <f t="shared" si="7"/>
-        <v>7523</v>
+        <v>7290</v>
       </c>
       <c r="CR3" s="43">
         <f t="shared" si="7"/>
@@ -7481,8 +7487,7 @@
         <v>1246</v>
       </c>
       <c r="CQ5" s="6">
-        <f>+CM5*0.9</f>
-        <v>1008.9</v>
+        <v>688</v>
       </c>
       <c r="CR5" s="6">
         <f t="shared" ref="CR5:CT5" si="10">+CN5*0.9</f>
@@ -7760,7 +7765,9 @@
       <c r="CP6" s="81" t="s">
         <v>703</v>
       </c>
-      <c r="CQ6" s="6"/>
+      <c r="CQ6" s="81" t="s">
+        <v>704</v>
+      </c>
       <c r="CR6" s="6"/>
       <c r="CS6" s="6"/>
       <c r="CT6" s="6"/>
@@ -8007,8 +8014,7 @@
         <v>671</v>
       </c>
       <c r="CQ7" s="6">
-        <f>+CM7*0.9</f>
-        <v>716.4899999999999</v>
+        <v>556</v>
       </c>
       <c r="CR7" s="6">
         <f t="shared" ref="CR7" si="26">+CN7*0.9</f>
@@ -8267,8 +8273,7 @@
         <v>5006</v>
       </c>
       <c r="CQ8" s="6">
-        <f>+CM8*1.3</f>
-        <v>4452.5</v>
+        <v>4483</v>
       </c>
       <c r="CR8" s="6">
         <f>+CN8*1.3</f>
@@ -8548,15 +8553,14 @@
         <v>692</v>
       </c>
       <c r="CO9" s="6">
-        <f t="shared" ref="CO9:CP9" si="53">+CK9*0.97</f>
+        <f t="shared" ref="CO9" si="53">+CK9*0.97</f>
         <v>650.87</v>
       </c>
       <c r="CP9" s="6">
         <v>717</v>
       </c>
       <c r="CQ9" s="6">
-        <f>+CM9*1.1</f>
-        <v>611.6</v>
+        <v>668</v>
       </c>
       <c r="CR9" s="6">
         <f t="shared" ref="CR9:CR10" si="54">+CN9*1.1</f>
@@ -8843,8 +8847,7 @@
         <v>990</v>
       </c>
       <c r="CQ10" s="6">
-        <f t="shared" ref="CQ10" si="63">+CM10*1.1</f>
-        <v>952.6</v>
+        <v>1009</v>
       </c>
       <c r="CR10" s="6">
         <f t="shared" si="54"/>
@@ -8918,23 +8921,23 @@
         <v>3716.8</v>
       </c>
       <c r="DL10" s="6">
-        <f t="shared" ref="DL10:DP10" si="64">+DK10*1.05</f>
+        <f t="shared" ref="DL10:DP10" si="63">+DK10*1.05</f>
         <v>3902.6400000000003</v>
       </c>
       <c r="DM10" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>4097.7720000000008</v>
       </c>
       <c r="DN10" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>4302.6606000000011</v>
       </c>
       <c r="DO10" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>4517.793630000001</v>
       </c>
       <c r="DP10" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>4743.6833115000009</v>
       </c>
       <c r="DQ10" s="6">
@@ -9279,19 +9282,18 @@
         <v>710</v>
       </c>
       <c r="CQ12" s="6">
-        <f t="shared" ref="CQ12" si="65">+CM12*1.1</f>
-        <v>731.50000000000011</v>
+        <v>770</v>
       </c>
       <c r="CR12" s="6">
-        <f t="shared" ref="CR12" si="66">+CN12*1.1</f>
+        <f t="shared" ref="CR12" si="64">+CN12*1.1</f>
         <v>760.1</v>
       </c>
       <c r="CS12" s="6">
-        <f t="shared" ref="CS12" si="67">+CO12*1.1</f>
+        <f t="shared" ref="CS12" si="65">+CO12*1.1</f>
         <v>798.6</v>
       </c>
       <c r="CT12" s="6">
-        <f t="shared" ref="CT12" si="68">+CP12*1.1</f>
+        <f t="shared" ref="CT12" si="66">+CP12*1.1</f>
         <v>781.00000000000011</v>
       </c>
       <c r="CU12" s="6"/>
@@ -9342,19 +9344,19 @@
         <v>2792</v>
       </c>
       <c r="DL12" s="6">
-        <f t="shared" ref="DL12:DO12" si="69">+DK12*1.03</f>
+        <f t="shared" ref="DL12:DO12" si="67">+DK12*1.03</f>
         <v>2875.76</v>
       </c>
       <c r="DM12" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>2962.0328000000004</v>
       </c>
       <c r="DN12" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>3050.8937840000003</v>
       </c>
       <c r="DO12" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>3142.4205975200002</v>
       </c>
       <c r="DP12" s="5">
@@ -9362,23 +9364,23 @@
         <v>314.24205975200005</v>
       </c>
       <c r="DQ12" s="5">
-        <f t="shared" ref="DQ12:DU14" si="70">+DP12*0.1</f>
+        <f t="shared" ref="DQ12:DU14" si="68">+DP12*0.1</f>
         <v>31.424205975200007</v>
       </c>
       <c r="DR12" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>3.142420597520001</v>
       </c>
       <c r="DS12" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>0.31424205975200015</v>
       </c>
       <c r="DT12" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>3.1424205975200015E-2</v>
       </c>
       <c r="DU12" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>3.1424205975200017E-3</v>
       </c>
     </row>
@@ -9531,46 +9533,45 @@
         <v>2374</v>
       </c>
       <c r="CQ13" s="6">
-        <f>+CM13*1.2</f>
-        <v>2061.6</v>
+        <v>2119</v>
       </c>
       <c r="CR13" s="6">
-        <f t="shared" ref="CR13:CR14" si="71">+CN13*1.2</f>
+        <f t="shared" ref="CR13:CR14" si="69">+CN13*1.2</f>
         <v>2433.6</v>
       </c>
       <c r="CS13" s="6">
-        <f t="shared" ref="CS13:CS14" si="72">+CO13*1.2</f>
+        <f t="shared" ref="CS13:CS14" si="70">+CO13*1.2</f>
         <v>2620.7999999999997</v>
       </c>
       <c r="CT13" s="6">
-        <f t="shared" ref="CT13:CT14" si="73">+CP13*1.2</f>
+        <f t="shared" ref="CT13:CT14" si="71">+CP13*1.2</f>
         <v>2848.7999999999997</v>
       </c>
       <c r="CU13" s="6"/>
       <c r="CV13" s="6"/>
       <c r="CW13" s="6"/>
       <c r="CX13" s="6">
-        <f t="shared" ref="CX13:CX15" si="74">SUM(BE13:BH13)</f>
+        <f t="shared" ref="CX13:CX15" si="72">SUM(BE13:BH13)</f>
         <v>0</v>
       </c>
       <c r="CY13" s="6">
-        <f t="shared" ref="CY13:CY15" si="75">SUM(BF13:BI13)</f>
+        <f t="shared" ref="CY13:CY15" si="73">SUM(BF13:BI13)</f>
         <v>0</v>
       </c>
       <c r="CZ13" s="6">
-        <f t="shared" ref="CZ13:CZ15" si="76">SUM(BG13:BJ13)</f>
+        <f t="shared" ref="CZ13:CZ15" si="74">SUM(BG13:BJ13)</f>
         <v>0</v>
       </c>
       <c r="DA13" s="6">
-        <f t="shared" ref="DA13:DA15" si="77">SUM(BH13:BK13)</f>
+        <f t="shared" ref="DA13:DA15" si="75">SUM(BH13:BK13)</f>
         <v>0</v>
       </c>
       <c r="DB13" s="6">
-        <f t="shared" ref="DB13:DB15" si="78">SUM(BI13:BL13)</f>
+        <f t="shared" ref="DB13:DB15" si="76">SUM(BI13:BL13)</f>
         <v>0</v>
       </c>
       <c r="DC13" s="6">
-        <f t="shared" ref="DC13:DC15" si="79">SUM(BJ13:BM13)</f>
+        <f t="shared" ref="DC13:DC15" si="77">SUM(BJ13:BM13)</f>
         <v>0</v>
       </c>
       <c r="DD13" s="6">
@@ -9614,35 +9615,35 @@
         <v>11957.759999999998</v>
       </c>
       <c r="DN13" s="6">
-        <f t="shared" ref="DN13:DP13" si="80">+DM13*1.03</f>
+        <f t="shared" ref="DN13:DP13" si="78">+DM13*1.03</f>
         <v>12316.492799999998</v>
       </c>
       <c r="DO13" s="6">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>12685.987583999999</v>
       </c>
       <c r="DP13" s="6">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>13066.56721152</v>
       </c>
       <c r="DQ13" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>1306.656721152</v>
       </c>
       <c r="DR13" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>130.66567211520001</v>
       </c>
       <c r="DS13" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>13.066567211520002</v>
       </c>
       <c r="DT13" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>1.3066567211520004</v>
       </c>
       <c r="DU13" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>0.13066567211520005</v>
       </c>
     </row>
@@ -9817,46 +9818,45 @@
         <v>1022</v>
       </c>
       <c r="CQ14" s="6">
-        <f t="shared" ref="CQ14" si="81">+CM14*1.2</f>
-        <v>918</v>
+        <v>905</v>
       </c>
       <c r="CR14" s="6">
+        <f t="shared" si="69"/>
+        <v>1080</v>
+      </c>
+      <c r="CS14" s="6">
+        <f t="shared" si="70"/>
+        <v>1120.8</v>
+      </c>
+      <c r="CT14" s="6">
         <f t="shared" si="71"/>
-        <v>1080</v>
-      </c>
-      <c r="CS14" s="6">
-        <f t="shared" si="72"/>
-        <v>1120.8</v>
-      </c>
-      <c r="CT14" s="6">
-        <f t="shared" si="73"/>
         <v>1226.3999999999999</v>
       </c>
       <c r="CU14" s="6"/>
       <c r="CV14" s="6"/>
       <c r="CW14" s="6"/>
       <c r="CX14" s="6">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="CY14" s="6">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="CZ14" s="6">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="CY14" s="6">
+      <c r="DA14" s="6">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="CZ14" s="6">
+      <c r="DB14" s="6">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="DA14" s="6">
+      <c r="DC14" s="6">
         <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="DB14" s="6">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="DC14" s="6">
-        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="DD14" s="6">
@@ -9892,43 +9892,43 @@
         <v>3621</v>
       </c>
       <c r="DL14" s="6">
-        <f t="shared" ref="DL14:DO14" si="82">+DK14*1.03</f>
+        <f t="shared" ref="DL14:DO14" si="79">+DK14*1.03</f>
         <v>3729.63</v>
       </c>
       <c r="DM14" s="6">
-        <f t="shared" si="82"/>
+        <f t="shared" si="79"/>
         <v>3841.5189</v>
       </c>
       <c r="DN14" s="6">
-        <f t="shared" si="82"/>
+        <f t="shared" si="79"/>
         <v>3956.764467</v>
       </c>
       <c r="DO14" s="6">
-        <f t="shared" si="82"/>
+        <f t="shared" si="79"/>
         <v>4075.4674010100002</v>
       </c>
       <c r="DP14" s="5">
-        <f t="shared" ref="DP14" si="83">+DO14*0.1</f>
+        <f t="shared" ref="DP14" si="80">+DO14*0.1</f>
         <v>407.54674010100007</v>
       </c>
       <c r="DQ14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>40.754674010100011</v>
       </c>
       <c r="DR14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>4.0754674010100009</v>
       </c>
       <c r="DS14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>0.40754674010100012</v>
       </c>
       <c r="DT14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>4.0754674010100016E-2</v>
       </c>
       <c r="DU14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>4.0754674010100014E-3</v>
       </c>
     </row>
@@ -10103,46 +10103,45 @@
         <v>249</v>
       </c>
       <c r="CQ15" s="6">
-        <f>+CM15</f>
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="CR15" s="6">
-        <f t="shared" ref="CR15:CR19" si="84">+CN15</f>
+        <f t="shared" ref="CR15:CR19" si="81">+CN15</f>
         <v>260</v>
       </c>
       <c r="CS15" s="6">
-        <f t="shared" ref="CS15:CS19" si="85">+CO15</f>
+        <f t="shared" ref="CS15:CS19" si="82">+CO15</f>
         <v>253</v>
       </c>
       <c r="CT15" s="6">
-        <f t="shared" ref="CT15:CT19" si="86">+CP15</f>
+        <f t="shared" ref="CT15:CT19" si="83">+CP15</f>
         <v>249</v>
       </c>
       <c r="CU15" s="6"/>
       <c r="CV15" s="6"/>
       <c r="CW15" s="6"/>
       <c r="CX15" s="6">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="CY15" s="6">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="CZ15" s="6">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="CY15" s="6">
+      <c r="DA15" s="6">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="CZ15" s="6">
+      <c r="DB15" s="6">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="DA15" s="6">
+      <c r="DC15" s="6">
         <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="DB15" s="6">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="DC15" s="6">
-        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="DD15" s="6">
@@ -10178,43 +10177,43 @@
         <v>993</v>
       </c>
       <c r="DL15" s="6">
-        <f t="shared" ref="DL15:DP15" si="87">+DK15*1.05</f>
+        <f t="shared" ref="DL15:DP15" si="84">+DK15*1.05</f>
         <v>1042.6500000000001</v>
       </c>
       <c r="DM15" s="6">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>1094.7825000000003</v>
       </c>
       <c r="DN15" s="6">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>1149.5216250000003</v>
       </c>
       <c r="DO15" s="6">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>1206.9977062500004</v>
       </c>
       <c r="DP15" s="6">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>1267.3475915625004</v>
       </c>
       <c r="DQ15" s="6">
-        <f t="shared" ref="DQ15" si="88">+DP15*1.05</f>
+        <f t="shared" ref="DQ15" si="85">+DP15*1.05</f>
         <v>1330.7149711406255</v>
       </c>
       <c r="DR15" s="6">
-        <f t="shared" ref="DR15" si="89">+DQ15*1.05</f>
+        <f t="shared" ref="DR15" si="86">+DQ15*1.05</f>
         <v>1397.2507196976569</v>
       </c>
       <c r="DS15" s="6">
-        <f t="shared" ref="DS15" si="90">+DR15*1.05</f>
+        <f t="shared" ref="DS15" si="87">+DR15*1.05</f>
         <v>1467.1132556825398</v>
       </c>
       <c r="DT15" s="6">
-        <f t="shared" ref="DT15" si="91">+DS15*1.05</f>
+        <f t="shared" ref="DT15" si="88">+DS15*1.05</f>
         <v>1540.468918466667</v>
       </c>
       <c r="DU15" s="6">
-        <f t="shared" ref="DU15" si="92">+DT15*1.05</f>
+        <f t="shared" ref="DU15" si="89">+DT15*1.05</f>
         <v>1617.4923643900004</v>
       </c>
     </row>
@@ -10389,19 +10388,18 @@
         <v>324</v>
       </c>
       <c r="CQ16" s="6">
-        <f t="shared" ref="CQ16:CQ19" si="93">+CM16</f>
-        <v>306</v>
+        <v>351</v>
       </c>
       <c r="CR16" s="6">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>375</v>
       </c>
       <c r="CS16" s="6">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>312</v>
       </c>
       <c r="CT16" s="6">
-        <f t="shared" si="86"/>
+        <f t="shared" si="83"/>
         <v>324</v>
       </c>
       <c r="CU16" s="6"/>
@@ -10446,43 +10444,43 @@
         <v>1317</v>
       </c>
       <c r="DL16" s="6">
-        <f t="shared" ref="DL16:DP16" si="94">+DK16*0.7</f>
+        <f t="shared" ref="DL16:DP16" si="90">+DK16*0.7</f>
         <v>921.9</v>
       </c>
       <c r="DM16" s="6">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>645.32999999999993</v>
       </c>
       <c r="DN16" s="6">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>451.73099999999994</v>
       </c>
       <c r="DO16" s="6">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>316.21169999999995</v>
       </c>
       <c r="DP16" s="6">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>221.34818999999996</v>
       </c>
       <c r="DQ16" s="6">
-        <f t="shared" ref="DQ16" si="95">+DP16*0.7</f>
+        <f t="shared" ref="DQ16" si="91">+DP16*0.7</f>
         <v>154.94373299999995</v>
       </c>
       <c r="DR16" s="6">
-        <f t="shared" ref="DR16" si="96">+DQ16*0.7</f>
+        <f t="shared" ref="DR16" si="92">+DQ16*0.7</f>
         <v>108.46061309999996</v>
       </c>
       <c r="DS16" s="6">
-        <f t="shared" ref="DS16" si="97">+DR16*0.7</f>
+        <f t="shared" ref="DS16" si="93">+DR16*0.7</f>
         <v>75.922429169999972</v>
       </c>
       <c r="DT16" s="6">
-        <f t="shared" ref="DT16" si="98">+DS16*0.7</f>
+        <f t="shared" ref="DT16" si="94">+DS16*0.7</f>
         <v>53.145700418999979</v>
       </c>
       <c r="DU16" s="6">
-        <f t="shared" ref="DU16" si="99">+DT16*0.7</f>
+        <f t="shared" ref="DU16" si="95">+DT16*0.7</f>
         <v>37.201990293299986</v>
       </c>
     </row>
@@ -10657,19 +10655,18 @@
         <v>320</v>
       </c>
       <c r="CQ17" s="6">
-        <f t="shared" si="93"/>
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="CR17" s="6">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>327</v>
       </c>
       <c r="CS17" s="6">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>303</v>
       </c>
       <c r="CT17" s="6">
-        <f t="shared" si="86"/>
+        <f t="shared" si="83"/>
         <v>320</v>
       </c>
       <c r="CU17" s="6"/>
@@ -10714,43 +10711,43 @@
         <v>1265</v>
       </c>
       <c r="DL17" s="6">
-        <f t="shared" ref="DL17:DP17" si="100">+DK17*0.9</f>
+        <f t="shared" ref="DL17:DP17" si="96">+DK17*0.9</f>
         <v>1138.5</v>
       </c>
       <c r="DM17" s="6">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>1024.6500000000001</v>
       </c>
       <c r="DN17" s="6">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>922.18500000000006</v>
       </c>
       <c r="DO17" s="6">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>829.96650000000011</v>
       </c>
       <c r="DP17" s="6">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>746.96985000000006</v>
       </c>
       <c r="DQ17" s="6">
-        <f t="shared" ref="DQ17" si="101">+DP17*0.9</f>
+        <f t="shared" ref="DQ17" si="97">+DP17*0.9</f>
         <v>672.27286500000002</v>
       </c>
       <c r="DR17" s="6">
-        <f t="shared" ref="DR17" si="102">+DQ17*0.9</f>
+        <f t="shared" ref="DR17" si="98">+DQ17*0.9</f>
         <v>605.04557850000003</v>
       </c>
       <c r="DS17" s="6">
-        <f t="shared" ref="DS17" si="103">+DR17*0.9</f>
+        <f t="shared" ref="DS17" si="99">+DR17*0.9</f>
         <v>544.54102065000006</v>
       </c>
       <c r="DT17" s="6">
-        <f t="shared" ref="DT17" si="104">+DS17*0.9</f>
+        <f t="shared" ref="DT17" si="100">+DS17*0.9</f>
         <v>490.08691858500009</v>
       </c>
       <c r="DU17" s="6">
-        <f t="shared" ref="DU17" si="105">+DT17*0.9</f>
+        <f t="shared" ref="DU17" si="101">+DT17*0.9</f>
         <v>441.07822672650008</v>
       </c>
     </row>
@@ -10963,19 +10960,18 @@
         <v>385</v>
       </c>
       <c r="CQ18" s="6">
-        <f t="shared" si="93"/>
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="CR18" s="6">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>404</v>
       </c>
       <c r="CS18" s="6">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>368</v>
       </c>
       <c r="CT18" s="6">
-        <f t="shared" si="86"/>
+        <f t="shared" si="83"/>
         <v>385</v>
       </c>
       <c r="CU18" s="6"/>
@@ -11032,43 +11028,43 @@
         <v>1512</v>
       </c>
       <c r="DL18" s="6">
-        <f t="shared" ref="DL18:DP18" si="106">+DK18*1.03</f>
+        <f t="shared" ref="DL18:DP18" si="102">+DK18*1.03</f>
         <v>1557.3600000000001</v>
       </c>
       <c r="DM18" s="6">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>1604.0808000000002</v>
       </c>
       <c r="DN18" s="6">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>1652.2032240000003</v>
       </c>
       <c r="DO18" s="6">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>1701.7693207200005</v>
       </c>
       <c r="DP18" s="6">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>1752.8224003416005</v>
       </c>
       <c r="DQ18" s="6">
-        <f t="shared" ref="DQ18" si="107">+DP18*1.03</f>
+        <f t="shared" ref="DQ18" si="103">+DP18*1.03</f>
         <v>1805.4070723518487</v>
       </c>
       <c r="DR18" s="6">
-        <f t="shared" ref="DR18" si="108">+DQ18*1.03</f>
+        <f t="shared" ref="DR18" si="104">+DQ18*1.03</f>
         <v>1859.5692845224041</v>
       </c>
       <c r="DS18" s="6">
-        <f t="shared" ref="DS18" si="109">+DR18*1.03</f>
+        <f t="shared" ref="DS18" si="105">+DR18*1.03</f>
         <v>1915.3563630580763</v>
       </c>
       <c r="DT18" s="6">
-        <f t="shared" ref="DT18" si="110">+DS18*1.03</f>
+        <f t="shared" ref="DT18" si="106">+DS18*1.03</f>
         <v>1972.8170539498187</v>
       </c>
       <c r="DU18" s="6">
-        <f t="shared" ref="DU18" si="111">+DT18*1.03</f>
+        <f t="shared" ref="DU18" si="107">+DT18*1.03</f>
         <v>2032.0015655683133</v>
       </c>
     </row>
@@ -11242,22 +11238,10 @@
       <c r="CP19" s="6">
         <v>294</v>
       </c>
-      <c r="CQ19" s="6">
-        <f t="shared" si="93"/>
-        <v>217</v>
-      </c>
-      <c r="CR19" s="6">
-        <f t="shared" si="84"/>
-        <v>250</v>
-      </c>
-      <c r="CS19" s="6">
-        <f t="shared" si="85"/>
-        <v>248</v>
-      </c>
-      <c r="CT19" s="6">
-        <f t="shared" si="86"/>
-        <v>294</v>
-      </c>
+      <c r="CQ19" s="6"/>
+      <c r="CR19" s="6"/>
+      <c r="CS19" s="6"/>
+      <c r="CT19" s="6"/>
       <c r="CU19" s="6"/>
       <c r="CV19" s="6"/>
       <c r="CW19" s="6"/>
@@ -11300,43 +11284,43 @@
         <v>1009</v>
       </c>
       <c r="DL19" s="6">
-        <f t="shared" ref="DL19:DP19" si="112">+DK19*0.9</f>
+        <f t="shared" ref="DL19:DP19" si="108">+DK19*0.9</f>
         <v>908.1</v>
       </c>
       <c r="DM19" s="6">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>817.29000000000008</v>
       </c>
       <c r="DN19" s="6">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>735.56100000000004</v>
       </c>
       <c r="DO19" s="6">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>662.00490000000002</v>
       </c>
       <c r="DP19" s="6">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>595.80441000000008</v>
       </c>
       <c r="DQ19" s="6">
-        <f t="shared" ref="DQ19:DQ20" si="113">+DP19*0.9</f>
+        <f t="shared" ref="DQ19:DQ20" si="109">+DP19*0.9</f>
         <v>536.22396900000012</v>
       </c>
       <c r="DR19" s="6">
-        <f t="shared" ref="DR19:DR20" si="114">+DQ19*0.9</f>
+        <f t="shared" ref="DR19:DR20" si="110">+DQ19*0.9</f>
         <v>482.60157210000011</v>
       </c>
       <c r="DS19" s="6">
-        <f t="shared" ref="DS19:DS20" si="115">+DR19*0.9</f>
+        <f t="shared" ref="DS19:DS20" si="111">+DR19*0.9</f>
         <v>434.34141489000012</v>
       </c>
       <c r="DT19" s="6">
-        <f t="shared" ref="DT19:DT20" si="116">+DS19*0.9</f>
+        <f t="shared" ref="DT19:DT20" si="112">+DS19*0.9</f>
         <v>390.90727340100011</v>
       </c>
       <c r="DU19" s="6">
-        <f t="shared" ref="DU19:DU20" si="117">+DT19*0.9</f>
+        <f t="shared" ref="DU19:DU20" si="113">+DT19*0.9</f>
         <v>351.81654606090012</v>
       </c>
     </row>
@@ -11546,43 +11530,43 @@
         <v>0</v>
       </c>
       <c r="DL20" s="6">
-        <f t="shared" ref="DL20:DP20" si="118">+DK20*0.9</f>
+        <f t="shared" ref="DL20:DP20" si="114">+DK20*0.9</f>
         <v>0</v>
       </c>
       <c r="DM20" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="DN20" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="DO20" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="DP20" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="DQ20" s="6">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="DR20" s="6">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="DS20" s="6">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="DT20" s="6">
+        <f t="shared" si="112"/>
+        <v>0</v>
+      </c>
+      <c r="DU20" s="6">
         <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="DR20" s="6">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="DS20" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="DT20" s="6">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="DU20" s="6">
-        <f t="shared" si="117"/>
         <v>0</v>
       </c>
     </row>
@@ -11755,20 +11739,19 @@
         <v>175</v>
       </c>
       <c r="CQ21" s="6">
-        <f>+CP21-5</f>
-        <v>170</v>
+        <v>283</v>
       </c>
       <c r="CR21" s="6">
-        <f t="shared" ref="CR21:CT21" si="119">+CQ21-5</f>
-        <v>165</v>
+        <f t="shared" ref="CR21:CT21" si="115">+CQ21-5</f>
+        <v>278</v>
       </c>
       <c r="CS21" s="6">
-        <f t="shared" si="119"/>
-        <v>160</v>
+        <f t="shared" si="115"/>
+        <v>273</v>
       </c>
       <c r="CT21" s="6">
-        <f t="shared" si="119"/>
-        <v>155</v>
+        <f t="shared" si="115"/>
+        <v>268</v>
       </c>
       <c r="CU21" s="6"/>
       <c r="CV21" s="6"/>
@@ -11812,43 +11795,43 @@
         <v>907</v>
       </c>
       <c r="DL21" s="6">
-        <f t="shared" ref="DL21:DP21" si="120">+DK21*0.5</f>
+        <f t="shared" ref="DL21:DP21" si="116">+DK21*0.5</f>
         <v>453.5</v>
       </c>
       <c r="DM21" s="6">
-        <f t="shared" si="120"/>
+        <f t="shared" si="116"/>
         <v>226.75</v>
       </c>
       <c r="DN21" s="6">
-        <f t="shared" si="120"/>
+        <f t="shared" si="116"/>
         <v>113.375</v>
       </c>
       <c r="DO21" s="6">
-        <f t="shared" si="120"/>
+        <f t="shared" si="116"/>
         <v>56.6875</v>
       </c>
       <c r="DP21" s="6">
-        <f t="shared" si="120"/>
+        <f t="shared" si="116"/>
         <v>28.34375</v>
       </c>
       <c r="DQ21" s="6">
-        <f t="shared" ref="DQ21" si="121">+DP21*0.5</f>
+        <f t="shared" ref="DQ21" si="117">+DP21*0.5</f>
         <v>14.171875</v>
       </c>
       <c r="DR21" s="6">
-        <f t="shared" ref="DR21" si="122">+DQ21*0.5</f>
+        <f t="shared" ref="DR21" si="118">+DQ21*0.5</f>
         <v>7.0859375</v>
       </c>
       <c r="DS21" s="6">
-        <f t="shared" ref="DS21" si="123">+DR21*0.5</f>
+        <f t="shared" ref="DS21" si="119">+DR21*0.5</f>
         <v>3.54296875</v>
       </c>
       <c r="DT21" s="6">
-        <f t="shared" ref="DT21" si="124">+DS21*0.5</f>
+        <f t="shared" ref="DT21" si="120">+DS21*0.5</f>
         <v>1.771484375</v>
       </c>
       <c r="DU21" s="6">
-        <f t="shared" ref="DU21" si="125">+DT21*0.5</f>
+        <f t="shared" ref="DU21" si="121">+DT21*0.5</f>
         <v>0.8857421875</v>
       </c>
     </row>
@@ -12009,7 +11992,7 @@
         <v>100</v>
       </c>
       <c r="CM22" s="6">
-        <f t="shared" ref="CM22" si="126">+CI22</f>
+        <f t="shared" ref="CM22" si="122">+CI22</f>
         <v>74</v>
       </c>
       <c r="CN22" s="6">
@@ -12022,20 +12005,19 @@
         <v>47</v>
       </c>
       <c r="CQ22" s="6">
-        <f>+CP22</f>
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="CR22" s="6">
-        <f t="shared" ref="CR22:CT22" si="127">+CQ22</f>
-        <v>47</v>
+        <f t="shared" ref="CR22:CT22" si="123">+CQ22</f>
+        <v>125</v>
       </c>
       <c r="CS22" s="6">
-        <f t="shared" si="127"/>
-        <v>47</v>
+        <f t="shared" si="123"/>
+        <v>125</v>
       </c>
       <c r="CT22" s="6">
-        <f t="shared" si="127"/>
-        <v>47</v>
+        <f t="shared" si="123"/>
+        <v>125</v>
       </c>
       <c r="CU22" s="6"/>
       <c r="CV22" s="6"/>
@@ -12079,43 +12061,43 @@
         <v>222</v>
       </c>
       <c r="DL22" s="6">
-        <f t="shared" ref="DL22:DP22" si="128">+DK22*0.9</f>
+        <f t="shared" ref="DL22:DP22" si="124">+DK22*0.9</f>
         <v>199.8</v>
       </c>
       <c r="DM22" s="6">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>179.82000000000002</v>
       </c>
       <c r="DN22" s="6">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>161.83800000000002</v>
       </c>
       <c r="DO22" s="6">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>145.65420000000003</v>
       </c>
       <c r="DP22" s="6">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>131.08878000000004</v>
       </c>
       <c r="DQ22" s="6">
-        <f t="shared" ref="DQ22:DQ23" si="129">+DP22*0.9</f>
+        <f t="shared" ref="DQ22:DQ23" si="125">+DP22*0.9</f>
         <v>117.97990200000004</v>
       </c>
       <c r="DR22" s="6">
-        <f t="shared" ref="DR22:DR23" si="130">+DQ22*0.9</f>
+        <f t="shared" ref="DR22:DR23" si="126">+DQ22*0.9</f>
         <v>106.18191180000004</v>
       </c>
       <c r="DS22" s="6">
-        <f t="shared" ref="DS22:DS23" si="131">+DR22*0.9</f>
+        <f t="shared" ref="DS22:DS23" si="127">+DR22*0.9</f>
         <v>95.563720620000041</v>
       </c>
       <c r="DT22" s="6">
-        <f t="shared" ref="DT22:DT23" si="132">+DS22*0.9</f>
+        <f t="shared" ref="DT22:DT23" si="128">+DS22*0.9</f>
         <v>86.007348558000032</v>
       </c>
       <c r="DU22" s="6">
-        <f t="shared" ref="DU22:DU23" si="133">+DT22*0.9</f>
+        <f t="shared" ref="DU22:DU23" si="129">+DT22*0.9</f>
         <v>77.406613702200033</v>
       </c>
     </row>
@@ -12287,22 +12269,10 @@
       <c r="CP23" s="6">
         <v>104</v>
       </c>
-      <c r="CQ23" s="6">
-        <f>+CM23</f>
-        <v>106</v>
-      </c>
-      <c r="CR23" s="6">
-        <f t="shared" ref="CR23:CT23" si="134">+CN23</f>
-        <v>103</v>
-      </c>
-      <c r="CS23" s="6">
-        <f t="shared" si="134"/>
-        <v>97</v>
-      </c>
-      <c r="CT23" s="6">
-        <f t="shared" si="134"/>
-        <v>104</v>
-      </c>
+      <c r="CQ23" s="6"/>
+      <c r="CR23" s="6"/>
+      <c r="CS23" s="6"/>
+      <c r="CT23" s="6"/>
       <c r="CU23" s="6"/>
       <c r="CV23" s="6"/>
       <c r="CW23" s="6"/>
@@ -12345,43 +12315,43 @@
         <v>410</v>
       </c>
       <c r="DL23" s="6">
-        <f t="shared" ref="DL23:DP23" si="135">+DK23*0.9</f>
+        <f t="shared" ref="DL23:DP23" si="130">+DK23*0.9</f>
         <v>369</v>
       </c>
       <c r="DM23" s="6">
-        <f t="shared" si="135"/>
+        <f t="shared" si="130"/>
         <v>332.1</v>
       </c>
       <c r="DN23" s="6">
-        <f t="shared" si="135"/>
+        <f t="shared" si="130"/>
         <v>298.89000000000004</v>
       </c>
       <c r="DO23" s="6">
-        <f t="shared" si="135"/>
+        <f t="shared" si="130"/>
         <v>269.00100000000003</v>
       </c>
       <c r="DP23" s="6">
-        <f t="shared" si="135"/>
+        <f t="shared" si="130"/>
         <v>242.10090000000002</v>
       </c>
       <c r="DQ23" s="6">
+        <f t="shared" si="125"/>
+        <v>217.89081000000002</v>
+      </c>
+      <c r="DR23" s="6">
+        <f t="shared" si="126"/>
+        <v>196.10172900000001</v>
+      </c>
+      <c r="DS23" s="6">
+        <f t="shared" si="127"/>
+        <v>176.4915561</v>
+      </c>
+      <c r="DT23" s="6">
+        <f t="shared" si="128"/>
+        <v>158.84240048999999</v>
+      </c>
+      <c r="DU23" s="6">
         <f t="shared" si="129"/>
-        <v>217.89081000000002</v>
-      </c>
-      <c r="DR23" s="6">
-        <f t="shared" si="130"/>
-        <v>196.10172900000001</v>
-      </c>
-      <c r="DS23" s="6">
-        <f t="shared" si="131"/>
-        <v>176.4915561</v>
-      </c>
-      <c r="DT23" s="6">
-        <f t="shared" si="132"/>
-        <v>158.84240048999999</v>
-      </c>
-      <c r="DU23" s="6">
-        <f t="shared" si="133"/>
         <v>142.95816044099999</v>
       </c>
     </row>
@@ -12554,20 +12524,19 @@
         <v>339</v>
       </c>
       <c r="CQ24" s="6">
-        <f>+CP24+5</f>
+        <v>339</v>
+      </c>
+      <c r="CR24" s="6">
+        <f t="shared" ref="CR24:CT24" si="131">+CQ24+5</f>
         <v>344</v>
       </c>
-      <c r="CR24" s="6">
-        <f t="shared" ref="CR24:CT24" si="136">+CQ24+5</f>
+      <c r="CS24" s="6">
+        <f t="shared" si="131"/>
         <v>349</v>
       </c>
-      <c r="CS24" s="6">
-        <f t="shared" si="136"/>
+      <c r="CT24" s="6">
+        <f t="shared" si="131"/>
         <v>354</v>
-      </c>
-      <c r="CT24" s="6">
-        <f t="shared" si="136"/>
-        <v>359</v>
       </c>
       <c r="CU24" s="6"/>
       <c r="CV24" s="6"/>
@@ -12631,23 +12600,23 @@
         <v>190.08567600000006</v>
       </c>
       <c r="DQ24" s="5">
-        <f t="shared" ref="DQ24:DU24" si="137">+DP24*0.1</f>
+        <f t="shared" ref="DQ24:DU24" si="132">+DP24*0.1</f>
         <v>19.008567600000006</v>
       </c>
       <c r="DR24" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="132"/>
         <v>1.9008567600000008</v>
       </c>
       <c r="DS24" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="132"/>
         <v>0.19008567600000009</v>
       </c>
       <c r="DT24" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="132"/>
         <v>1.9008567600000012E-2</v>
       </c>
       <c r="DU24" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="132"/>
         <v>1.9008567600000013E-3</v>
       </c>
     </row>
@@ -12853,22 +12822,10 @@
       <c r="CP25" s="6">
         <v>92</v>
       </c>
-      <c r="CQ25" s="6">
-        <f>+CM25</f>
-        <v>96</v>
-      </c>
-      <c r="CR25" s="6">
-        <f t="shared" ref="CR25:CR26" si="138">+CN25</f>
-        <v>97</v>
-      </c>
-      <c r="CS25" s="6">
-        <f t="shared" ref="CS25:CS26" si="139">+CO25</f>
-        <v>96</v>
-      </c>
-      <c r="CT25" s="6">
-        <f t="shared" ref="CT25:CT26" si="140">+CP25</f>
-        <v>92</v>
-      </c>
+      <c r="CQ25" s="6"/>
+      <c r="CR25" s="6"/>
+      <c r="CS25" s="6"/>
+      <c r="CT25" s="6"/>
       <c r="CU25" s="6"/>
       <c r="CV25" s="6"/>
       <c r="CW25" s="6"/>
@@ -12923,43 +12880,43 @@
         <v>381</v>
       </c>
       <c r="DL25" s="6">
-        <f t="shared" ref="DL25:DP25" si="141">+DK25*0.9</f>
+        <f t="shared" ref="DL25:DP25" si="133">+DK25*0.9</f>
         <v>342.90000000000003</v>
       </c>
       <c r="DM25" s="6">
-        <f t="shared" si="141"/>
+        <f t="shared" si="133"/>
         <v>308.61</v>
       </c>
       <c r="DN25" s="6">
-        <f t="shared" si="141"/>
+        <f t="shared" si="133"/>
         <v>277.74900000000002</v>
       </c>
       <c r="DO25" s="6">
-        <f t="shared" si="141"/>
+        <f t="shared" si="133"/>
         <v>249.97410000000002</v>
       </c>
       <c r="DP25" s="6">
-        <f t="shared" si="141"/>
+        <f t="shared" si="133"/>
         <v>224.97669000000002</v>
       </c>
       <c r="DQ25" s="6">
-        <f t="shared" ref="DQ25:DQ26" si="142">+DP25*0.9</f>
+        <f t="shared" ref="DQ25:DQ26" si="134">+DP25*0.9</f>
         <v>202.47902100000002</v>
       </c>
       <c r="DR25" s="6">
-        <f t="shared" ref="DR25:DR26" si="143">+DQ25*0.9</f>
+        <f t="shared" ref="DR25:DR26" si="135">+DQ25*0.9</f>
         <v>182.23111890000001</v>
       </c>
       <c r="DS25" s="6">
-        <f t="shared" ref="DS25:DS26" si="144">+DR25*0.9</f>
+        <f t="shared" ref="DS25:DS26" si="136">+DR25*0.9</f>
         <v>164.00800701000003</v>
       </c>
       <c r="DT25" s="6">
-        <f t="shared" ref="DT25:DT26" si="145">+DS25*0.9</f>
+        <f t="shared" ref="DT25:DT26" si="137">+DS25*0.9</f>
         <v>147.60720630900002</v>
       </c>
       <c r="DU25" s="6">
-        <f t="shared" ref="DU25:DU26" si="146">+DT25*0.9</f>
+        <f t="shared" ref="DU25:DU26" si="138">+DT25*0.9</f>
         <v>132.84648567810001</v>
       </c>
     </row>
@@ -13131,22 +13088,10 @@
       <c r="CP26" s="6">
         <v>54</v>
       </c>
-      <c r="CQ26" s="6">
-        <f>+CM26</f>
-        <v>60</v>
-      </c>
-      <c r="CR26" s="6">
-        <f t="shared" si="138"/>
-        <v>36</v>
-      </c>
-      <c r="CS26" s="6">
-        <f t="shared" si="139"/>
-        <v>47</v>
-      </c>
-      <c r="CT26" s="6">
-        <f t="shared" si="140"/>
-        <v>54</v>
-      </c>
+      <c r="CQ26" s="6"/>
+      <c r="CR26" s="6"/>
+      <c r="CS26" s="6"/>
+      <c r="CT26" s="6"/>
       <c r="CU26" s="6"/>
       <c r="CV26" s="6"/>
       <c r="CW26" s="6"/>
@@ -13189,43 +13134,43 @@
         <v>197</v>
       </c>
       <c r="DL26" s="6">
-        <f t="shared" ref="DL26:DP26" si="147">+DK26*0.9</f>
+        <f t="shared" ref="DL26:DP26" si="139">+DK26*0.9</f>
         <v>177.3</v>
       </c>
       <c r="DM26" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="139"/>
         <v>159.57000000000002</v>
       </c>
       <c r="DN26" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="139"/>
         <v>143.61300000000003</v>
       </c>
       <c r="DO26" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="139"/>
         <v>129.25170000000003</v>
       </c>
       <c r="DP26" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="139"/>
         <v>116.32653000000003</v>
       </c>
       <c r="DQ26" s="6">
-        <f t="shared" si="142"/>
+        <f t="shared" si="134"/>
         <v>104.69387700000003</v>
       </c>
       <c r="DR26" s="6">
-        <f t="shared" si="143"/>
+        <f t="shared" si="135"/>
         <v>94.22448930000003</v>
       </c>
       <c r="DS26" s="6">
-        <f t="shared" si="144"/>
+        <f t="shared" si="136"/>
         <v>84.802040370000029</v>
       </c>
       <c r="DT26" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="137"/>
         <v>76.321836333000022</v>
       </c>
       <c r="DU26" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>68.689652699700019</v>
       </c>
     </row>
@@ -13398,20 +13343,19 @@
         <v>288</v>
       </c>
       <c r="CQ27" s="6">
-        <f>+CP27+5</f>
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="CR27" s="6">
-        <f t="shared" ref="CR27:CT27" si="148">+CQ27+5</f>
-        <v>298</v>
+        <f t="shared" ref="CR27:CT27" si="140">+CQ27+5</f>
+        <v>301</v>
       </c>
       <c r="CS27" s="6">
-        <f t="shared" si="148"/>
-        <v>303</v>
+        <f t="shared" si="140"/>
+        <v>306</v>
       </c>
       <c r="CT27" s="6">
-        <f t="shared" si="148"/>
-        <v>308</v>
+        <f t="shared" si="140"/>
+        <v>311</v>
       </c>
       <c r="CU27" s="6"/>
       <c r="CV27" s="6"/>
@@ -13475,23 +13419,23 @@
         <v>154.94001600000004</v>
       </c>
       <c r="DQ27" s="5">
-        <f t="shared" ref="DQ27:DU27" si="149">+DP27*0.1</f>
+        <f t="shared" ref="DQ27:DU27" si="141">+DP27*0.1</f>
         <v>15.494001600000004</v>
       </c>
       <c r="DR27" s="5">
-        <f t="shared" si="149"/>
+        <f t="shared" si="141"/>
         <v>1.5494001600000005</v>
       </c>
       <c r="DS27" s="5">
-        <f t="shared" si="149"/>
+        <f t="shared" si="141"/>
         <v>0.15494001600000007</v>
       </c>
       <c r="DT27" s="5">
-        <f t="shared" si="149"/>
+        <f t="shared" si="141"/>
         <v>1.5494001600000008E-2</v>
       </c>
       <c r="DU27" s="5">
-        <f t="shared" si="149"/>
+        <f t="shared" si="141"/>
         <v>1.5494001600000009E-3</v>
       </c>
     </row>
@@ -13608,20 +13552,19 @@
         <v>182</v>
       </c>
       <c r="CQ28" s="6">
-        <f>+CP28+5</f>
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="CR28" s="6">
-        <f t="shared" ref="CR28:CT28" si="150">+CQ28+5</f>
-        <v>192</v>
+        <f>+CQ28+5</f>
+        <v>203</v>
       </c>
       <c r="CS28" s="6">
-        <f t="shared" si="150"/>
-        <v>197</v>
+        <f>+CR28+5</f>
+        <v>208</v>
       </c>
       <c r="CT28" s="6">
-        <f t="shared" si="150"/>
-        <v>202</v>
+        <f>+CS28+5</f>
+        <v>213</v>
       </c>
       <c r="CU28" s="6"/>
       <c r="CV28" s="6"/>
@@ -13667,23 +13610,23 @@
         <v>1111.2519000000007</v>
       </c>
       <c r="DQ28" s="6">
-        <f t="shared" ref="DQ28:DU28" si="151">+DP28*1.1</f>
+        <f t="shared" ref="DQ28:DU28" si="142">+DP28*1.1</f>
         <v>1222.3770900000009</v>
       </c>
       <c r="DR28" s="6">
-        <f t="shared" si="151"/>
+        <f t="shared" si="142"/>
         <v>1344.6147990000011</v>
       </c>
       <c r="DS28" s="6">
-        <f t="shared" si="151"/>
+        <f t="shared" si="142"/>
         <v>1479.0762789000014</v>
       </c>
       <c r="DT28" s="6">
-        <f t="shared" si="151"/>
+        <f t="shared" si="142"/>
         <v>1626.9839067900016</v>
       </c>
       <c r="DU28" s="6">
-        <f t="shared" si="151"/>
+        <f t="shared" si="142"/>
         <v>1789.6822974690019</v>
       </c>
     </row>
@@ -13937,20 +13880,19 @@
         <v>20</v>
       </c>
       <c r="CQ30" s="6">
-        <f>+CP30</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="CR30" s="6">
-        <f t="shared" ref="CR30:CT30" si="152">+CQ30</f>
-        <v>20</v>
+        <f>+CQ30</f>
+        <v>24</v>
       </c>
       <c r="CS30" s="6">
-        <f t="shared" si="152"/>
-        <v>20</v>
+        <f>+CR30</f>
+        <v>24</v>
       </c>
       <c r="CT30" s="6">
-        <f t="shared" si="152"/>
-        <v>20</v>
+        <f>+CS30</f>
+        <v>24</v>
       </c>
       <c r="CU30" s="6"/>
       <c r="CV30" s="6"/>
@@ -14097,20 +14039,19 @@
         <v>81</v>
       </c>
       <c r="CQ31" s="6">
-        <f>+CP31+3</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="CR31" s="6">
-        <f t="shared" ref="CR31:CT31" si="153">+CQ31+3</f>
-        <v>87</v>
+        <f t="shared" ref="CR31:CT31" si="143">+CQ31+3</f>
+        <v>86</v>
       </c>
       <c r="CS31" s="6">
-        <f t="shared" si="153"/>
-        <v>90</v>
+        <f t="shared" si="143"/>
+        <v>89</v>
       </c>
       <c r="CT31" s="6">
-        <f t="shared" si="153"/>
-        <v>93</v>
+        <f t="shared" si="143"/>
+        <v>92</v>
       </c>
       <c r="CU31" s="6"/>
       <c r="CV31" s="6"/>
@@ -14127,7 +14068,7 @@
       <c r="DG31" s="6"/>
       <c r="DH31" s="6"/>
       <c r="DI31" s="6">
-        <f t="shared" ref="DI31:DI32" si="154">SUM(CE31:CH31)</f>
+        <f t="shared" ref="DI31:DI32" si="144">SUM(CE31:CH31)</f>
         <v>31</v>
       </c>
       <c r="DJ31" s="6">
@@ -14147,11 +14088,11 @@
         <v>493.21999999999997</v>
       </c>
       <c r="DN31" s="6">
-        <f t="shared" ref="DN31:DO31" si="155">+DM31*1.2</f>
+        <f t="shared" ref="DN31:DO31" si="145">+DM31*1.2</f>
         <v>591.86399999999992</v>
       </c>
       <c r="DO31" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="145"/>
         <v>710.2367999999999</v>
       </c>
       <c r="DP31" s="6">
@@ -14163,19 +14104,19 @@
         <v>820.32350399999996</v>
       </c>
       <c r="DR31" s="6">
-        <f t="shared" ref="DR31:DU31" si="156">+DQ31*1.05</f>
+        <f t="shared" ref="DR31:DU31" si="146">+DQ31*1.05</f>
         <v>861.33967919999998</v>
       </c>
       <c r="DS31" s="6">
-        <f t="shared" si="156"/>
+        <f t="shared" si="146"/>
         <v>904.40666315999999</v>
       </c>
       <c r="DT31" s="6">
-        <f t="shared" si="156"/>
+        <f t="shared" si="146"/>
         <v>949.62699631800001</v>
       </c>
       <c r="DU31" s="6">
-        <f t="shared" si="156"/>
+        <f t="shared" si="146"/>
         <v>997.1083461339</v>
       </c>
     </row>
@@ -14306,22 +14247,10 @@
       <c r="CP32" s="6">
         <v>128</v>
       </c>
-      <c r="CQ32" s="6">
-        <f>+CM32</f>
-        <v>123</v>
-      </c>
-      <c r="CR32" s="6">
-        <f t="shared" ref="CR32:CT32" si="157">+CN32</f>
-        <v>125</v>
-      </c>
-      <c r="CS32" s="6">
-        <f t="shared" si="157"/>
-        <v>117</v>
-      </c>
-      <c r="CT32" s="6">
-        <f t="shared" si="157"/>
-        <v>128</v>
-      </c>
+      <c r="CQ32" s="6"/>
+      <c r="CR32" s="6"/>
+      <c r="CS32" s="6"/>
+      <c r="CT32" s="6"/>
       <c r="CU32" s="6"/>
       <c r="CV32" s="6"/>
       <c r="CW32" s="6"/>
@@ -14340,7 +14269,7 @@
         <v>428</v>
       </c>
       <c r="DI32" s="6">
-        <f t="shared" si="154"/>
+        <f t="shared" si="144"/>
         <v>472</v>
       </c>
       <c r="DJ32" s="6">
@@ -14356,39 +14285,39 @@
         <v>493</v>
       </c>
       <c r="DM32" s="6">
-        <f t="shared" ref="DM32:DU32" si="158">+DL32</f>
+        <f t="shared" ref="DM32:DU32" si="147">+DL32</f>
         <v>493</v>
       </c>
       <c r="DN32" s="6">
-        <f t="shared" si="158"/>
+        <f t="shared" si="147"/>
         <v>493</v>
       </c>
       <c r="DO32" s="6">
-        <f t="shared" si="158"/>
+        <f t="shared" si="147"/>
         <v>493</v>
       </c>
       <c r="DP32" s="6">
-        <f t="shared" si="158"/>
+        <f t="shared" si="147"/>
         <v>493</v>
       </c>
       <c r="DQ32" s="6">
-        <f t="shared" si="158"/>
+        <f t="shared" si="147"/>
         <v>493</v>
       </c>
       <c r="DR32" s="6">
-        <f t="shared" si="158"/>
+        <f t="shared" si="147"/>
         <v>493</v>
       </c>
       <c r="DS32" s="6">
-        <f t="shared" si="158"/>
+        <f t="shared" si="147"/>
         <v>493</v>
       </c>
       <c r="DT32" s="6">
-        <f t="shared" si="158"/>
+        <f t="shared" si="147"/>
         <v>493</v>
       </c>
       <c r="DU32" s="6">
-        <f t="shared" si="158"/>
+        <f t="shared" si="147"/>
         <v>493</v>
       </c>
     </row>
@@ -14523,27 +14452,27 @@
         <v>303</v>
       </c>
       <c r="DO33" s="6">
-        <f t="shared" ref="DO33:DT33" si="159">+DN33*1.01</f>
+        <f t="shared" ref="DO33:DT33" si="148">+DN33*1.01</f>
         <v>306.03000000000003</v>
       </c>
       <c r="DP33" s="6">
-        <f t="shared" si="159"/>
+        <f t="shared" si="148"/>
         <v>309.09030000000001</v>
       </c>
       <c r="DQ33" s="6">
-        <f t="shared" si="159"/>
+        <f t="shared" si="148"/>
         <v>312.18120300000004</v>
       </c>
       <c r="DR33" s="6">
-        <f t="shared" si="159"/>
+        <f t="shared" si="148"/>
         <v>315.30301503000004</v>
       </c>
       <c r="DS33" s="6">
-        <f t="shared" si="159"/>
+        <f t="shared" si="148"/>
         <v>318.45604518030007</v>
       </c>
       <c r="DT33" s="6">
-        <f t="shared" si="159"/>
+        <f t="shared" si="148"/>
         <v>321.64060563210307</v>
       </c>
       <c r="DU33" s="6">
@@ -14656,20 +14585,19 @@
         <v>183</v>
       </c>
       <c r="CQ34" s="6">
-        <f>+CP34+10</f>
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="CR34" s="6">
         <f>+CQ34+10</f>
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="CS34" s="6">
         <f>+CR34+10</f>
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="CT34" s="6">
         <f>+CS34+10</f>
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="CU34" s="6"/>
       <c r="CV34" s="6"/>
@@ -18696,227 +18624,227 @@
         <v>13</v>
       </c>
       <c r="C56" s="6">
-        <f t="shared" ref="C56:AH56" si="160">SUM(C5:C55)</f>
+        <f t="shared" ref="C56:AH56" si="149">SUM(C5:C55)</f>
         <v>30</v>
       </c>
       <c r="D56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>60</v>
       </c>
       <c r="E56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>80</v>
       </c>
       <c r="F56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>110</v>
       </c>
       <c r="G56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2207</v>
       </c>
       <c r="H56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2435</v>
       </c>
       <c r="I56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2684</v>
       </c>
       <c r="J56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2994</v>
       </c>
       <c r="K56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2871</v>
       </c>
       <c r="L56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2662</v>
       </c>
       <c r="M56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>3248</v>
       </c>
       <c r="N56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>3440</v>
       </c>
       <c r="O56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2725</v>
       </c>
       <c r="P56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2925</v>
       </c>
       <c r="Q56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2889</v>
       </c>
       <c r="R56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>3311</v>
       </c>
       <c r="S56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2250</v>
       </c>
       <c r="T56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2414</v>
       </c>
       <c r="U56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2440</v>
       </c>
       <c r="V56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2910</v>
       </c>
       <c r="W56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2605</v>
       </c>
       <c r="X56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>3012</v>
       </c>
       <c r="Y56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>3171</v>
       </c>
       <c r="Z56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>3380</v>
       </c>
       <c r="AA56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2173</v>
       </c>
       <c r="AB56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2613</v>
       </c>
       <c r="AC56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2810</v>
       </c>
       <c r="AD56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>3178</v>
       </c>
       <c r="AE56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2480</v>
       </c>
       <c r="AF56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2802</v>
       </c>
       <c r="AG56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>2968</v>
       </c>
       <c r="AH56" s="6">
-        <f t="shared" si="160"/>
+        <f t="shared" si="149"/>
         <v>3365</v>
       </c>
       <c r="AI56" s="6">
-        <f t="shared" ref="AI56:BF56" si="161">SUM(AI5:AI55)</f>
+        <f t="shared" ref="AI56:BF56" si="150">SUM(AI5:AI55)</f>
         <v>2821</v>
       </c>
       <c r="AJ56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>3373</v>
       </c>
       <c r="AK56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>3446</v>
       </c>
       <c r="AL56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>3578</v>
       </c>
       <c r="AM56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>3416</v>
       </c>
       <c r="AN56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>3995</v>
       </c>
       <c r="AO56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4383</v>
       </c>
       <c r="AP56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4443</v>
       </c>
       <c r="AQ56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4009</v>
       </c>
       <c r="AR56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4297</v>
       </c>
       <c r="AS56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4335</v>
       </c>
       <c r="AT56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4749</v>
       </c>
       <c r="AU56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4157</v>
       </c>
       <c r="AV56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4506</v>
       </c>
       <c r="AW56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4649</v>
       </c>
       <c r="AX56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4966</v>
       </c>
       <c r="AY56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>4694</v>
       </c>
       <c r="AZ56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>5129</v>
       </c>
       <c r="BA56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>5591</v>
       </c>
       <c r="BB56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>6043</v>
       </c>
       <c r="BC56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>5681</v>
       </c>
       <c r="BD56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>6143</v>
       </c>
       <c r="BE56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>6090</v>
       </c>
       <c r="BF56" s="6">
-        <f t="shared" si="161"/>
+        <f t="shared" si="150"/>
         <v>6507</v>
       </c>
       <c r="BG56" s="6">
@@ -19242,11 +19170,20 @@
         <v>617</v>
       </c>
       <c r="CQ57" s="6">
-        <v>617</v>
-      </c>
-      <c r="CR57" s="6"/>
-      <c r="CS57" s="6"/>
-      <c r="CT57" s="6"/>
+        <v>1025</v>
+      </c>
+      <c r="CR57" s="6">
+        <f>+CQ57</f>
+        <v>1025</v>
+      </c>
+      <c r="CS57" s="6">
+        <f>+CR57</f>
+        <v>1025</v>
+      </c>
+      <c r="CT57" s="6">
+        <f>+CS57</f>
+        <v>1025</v>
+      </c>
       <c r="CU57" s="6"/>
       <c r="CV57" s="6"/>
       <c r="CW57" s="6"/>
@@ -19261,11 +19198,11 @@
         <v>423</v>
       </c>
       <c r="DE57" s="6">
-        <f t="shared" ref="DE57" si="162">SUM(BO57:BR57)</f>
+        <f t="shared" ref="DE57" si="151">SUM(BO57:BR57)</f>
         <v>524</v>
       </c>
       <c r="DF57" s="6">
-        <f t="shared" ref="DF57" si="163">SUM(BS57:BV57)</f>
+        <f t="shared" ref="DF57" si="152">SUM(BS57:BV57)</f>
         <v>3647</v>
       </c>
       <c r="DG57" s="6">
@@ -19289,43 +19226,43 @@
         <v>2414</v>
       </c>
       <c r="DL57" s="6">
-        <f t="shared" ref="DL57:DP57" si="164">+DK57*0.9</f>
+        <f t="shared" ref="DL57:DP57" si="153">+DK57*0.9</f>
         <v>2172.6</v>
       </c>
       <c r="DM57" s="6">
-        <f t="shared" si="164"/>
+        <f t="shared" si="153"/>
         <v>1955.34</v>
       </c>
       <c r="DN57" s="6">
-        <f t="shared" si="164"/>
+        <f t="shared" si="153"/>
         <v>1759.806</v>
       </c>
       <c r="DO57" s="6">
-        <f t="shared" si="164"/>
+        <f t="shared" si="153"/>
         <v>1583.8254000000002</v>
       </c>
       <c r="DP57" s="6">
-        <f t="shared" si="164"/>
+        <f t="shared" si="153"/>
         <v>1425.4428600000001</v>
       </c>
       <c r="DQ57" s="6">
-        <f t="shared" ref="DQ57" si="165">+DP57*0.9</f>
+        <f t="shared" ref="DQ57" si="154">+DP57*0.9</f>
         <v>1282.8985740000001</v>
       </c>
       <c r="DR57" s="6">
-        <f t="shared" ref="DR57" si="166">+DQ57*0.9</f>
+        <f t="shared" ref="DR57" si="155">+DQ57*0.9</f>
         <v>1154.6087166</v>
       </c>
       <c r="DS57" s="6">
-        <f t="shared" ref="DS57" si="167">+DR57*0.9</f>
+        <f t="shared" ref="DS57" si="156">+DR57*0.9</f>
         <v>1039.1478449399999</v>
       </c>
       <c r="DT57" s="6">
-        <f t="shared" ref="DT57" si="168">+DS57*0.9</f>
+        <f t="shared" ref="DT57" si="157">+DS57*0.9</f>
         <v>935.23306044599997</v>
       </c>
       <c r="DU57" s="6">
-        <f t="shared" ref="DU57" si="169">+DT57*0.9</f>
+        <f t="shared" ref="DU57" si="158">+DT57*0.9</f>
         <v>841.70975440140001</v>
       </c>
     </row>
@@ -19334,163 +19271,163 @@
         <v>241</v>
       </c>
       <c r="C58" s="8">
-        <f t="shared" ref="C58:AP58" si="170">+C57+C56</f>
+        <f t="shared" ref="C58:AP58" si="159">+C57+C56</f>
         <v>30</v>
       </c>
       <c r="D58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>60</v>
       </c>
       <c r="E58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>80</v>
       </c>
       <c r="F58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>110</v>
       </c>
       <c r="G58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2207</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2435</v>
       </c>
       <c r="I58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2684</v>
       </c>
       <c r="J58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2994</v>
       </c>
       <c r="K58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2871</v>
       </c>
       <c r="L58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2662</v>
       </c>
       <c r="M58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3248</v>
       </c>
       <c r="N58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3440</v>
       </c>
       <c r="O58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2725</v>
       </c>
       <c r="P58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2925</v>
       </c>
       <c r="Q58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2889</v>
       </c>
       <c r="R58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3311</v>
       </c>
       <c r="S58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2250</v>
       </c>
       <c r="T58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2414</v>
       </c>
       <c r="U58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2440</v>
       </c>
       <c r="V58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2910</v>
       </c>
       <c r="W58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2605</v>
       </c>
       <c r="X58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3012</v>
       </c>
       <c r="Y58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3171</v>
       </c>
       <c r="Z58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3380</v>
       </c>
       <c r="AA58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2173</v>
       </c>
       <c r="AB58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2613</v>
       </c>
       <c r="AC58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2810</v>
       </c>
       <c r="AD58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3178</v>
       </c>
       <c r="AE58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2480</v>
       </c>
       <c r="AF58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2802</v>
       </c>
       <c r="AG58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2968</v>
       </c>
       <c r="AH58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3365</v>
       </c>
       <c r="AI58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>2821</v>
       </c>
       <c r="AJ58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3373</v>
       </c>
       <c r="AK58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3446</v>
       </c>
       <c r="AL58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3578</v>
       </c>
       <c r="AM58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3416</v>
       </c>
       <c r="AN58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>3995</v>
       </c>
       <c r="AO58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>4684</v>
       </c>
       <c r="AP58" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="159"/>
         <v>4443</v>
       </c>
       <c r="AQ58" s="8">
@@ -19501,59 +19438,59 @@
         <v>4692</v>
       </c>
       <c r="AS58" s="8">
-        <f t="shared" ref="AS58:BF58" si="171">+AS57+AS56</f>
+        <f t="shared" ref="AS58:BF58" si="160">+AS57+AS56</f>
         <v>4658</v>
       </c>
       <c r="AT58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>5111</v>
       </c>
       <c r="AU58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>4563</v>
       </c>
       <c r="AV58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>4926</v>
       </c>
       <c r="AW58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>5019</v>
       </c>
       <c r="AX58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>5452</v>
       </c>
       <c r="AY58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>5040</v>
       </c>
       <c r="AZ58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>5475</v>
       </c>
       <c r="BA58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>5944</v>
       </c>
       <c r="BB58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>6360</v>
       </c>
       <c r="BC58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>5958</v>
       </c>
       <c r="BD58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>6432</v>
       </c>
       <c r="BE58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>6386</v>
       </c>
       <c r="BF58" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="160"/>
         <v>6784</v>
       </c>
       <c r="BG58" s="8">
@@ -19573,144 +19510,144 @@
         <v>7934</v>
       </c>
       <c r="BL58" s="8">
-        <f t="shared" ref="BL58:CL58" si="172">SUM(BL5:BL57)</f>
+        <f t="shared" ref="BL58:CL58" si="161">SUM(BL5:BL57)</f>
         <v>8258</v>
       </c>
       <c r="BM58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>8236</v>
       </c>
       <c r="BN58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>8305</v>
       </c>
       <c r="BO58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>7828</v>
       </c>
       <c r="BP58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>8255</v>
       </c>
       <c r="BQ58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>8479</v>
       </c>
       <c r="BR58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>8704</v>
       </c>
       <c r="BS58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>8619</v>
       </c>
       <c r="BT58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>10425</v>
       </c>
       <c r="BU58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>12882</v>
       </c>
       <c r="BV58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>13858</v>
       </c>
       <c r="BW58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>12935</v>
       </c>
       <c r="BX58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>13959</v>
       </c>
       <c r="BY58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>14342</v>
       </c>
       <c r="BZ58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>14886</v>
       </c>
       <c r="CA58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>13538</v>
       </c>
       <c r="CB58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>14583</v>
       </c>
       <c r="CC58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>14812</v>
       </c>
       <c r="CD58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>15121</v>
       </c>
       <c r="CE58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>12225</v>
       </c>
       <c r="CF58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>13865</v>
       </c>
       <c r="CG58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>13927</v>
       </c>
       <c r="CH58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>14301</v>
       </c>
       <c r="CI58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>12310</v>
       </c>
       <c r="CJ58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>14462</v>
       </c>
       <c r="CK58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>14460</v>
       </c>
       <c r="CL58" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="161"/>
         <v>15102</v>
       </c>
       <c r="CM58" s="8">
-        <f t="shared" ref="CM58:CT58" si="173">SUM(CM5:CM57)</f>
+        <f t="shared" ref="CM58:CT58" si="162">SUM(CM5:CM57)</f>
         <v>13232.1</v>
       </c>
       <c r="CN58" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="162"/>
         <v>15423</v>
       </c>
       <c r="CO58" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="162"/>
         <v>15776.27</v>
       </c>
       <c r="CP58" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="162"/>
         <v>16618</v>
       </c>
       <c r="CQ58" s="8">
-        <f t="shared" si="173"/>
-        <v>15217.19</v>
+        <f>SUM(CQ5:CQ57)</f>
+        <v>15002</v>
       </c>
       <c r="CR58" s="8">
-        <f t="shared" si="173"/>
-        <v>16884.2</v>
+        <f t="shared" si="162"/>
+        <v>17509.2</v>
       </c>
       <c r="CS58" s="8">
-        <f t="shared" si="173"/>
-        <v>17229.277000000002</v>
+        <f t="shared" si="162"/>
+        <v>17860.277000000002</v>
       </c>
       <c r="CT58" s="8">
-        <f t="shared" si="173"/>
-        <v>18324</v>
+        <f t="shared" si="162"/>
+        <v>18888</v>
       </c>
       <c r="CU58" s="8"/>
       <c r="CV58" s="8">
@@ -19738,75 +19675,75 @@
         <v>28216</v>
       </c>
       <c r="DD58" s="8">
-        <f t="shared" ref="DD58:DP58" si="174">SUM(DD5:DD57)</f>
+        <f t="shared" ref="DD58:DP58" si="163">SUM(DD5:DD57)</f>
         <v>32733</v>
       </c>
       <c r="DE58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>33266</v>
       </c>
       <c r="DF58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>45784</v>
       </c>
       <c r="DG58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>56122</v>
       </c>
       <c r="DH58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>58054</v>
       </c>
       <c r="DI58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>54318</v>
       </c>
       <c r="DJ58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>56334</v>
       </c>
       <c r="DK58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>61029.369999999995</v>
       </c>
       <c r="DL58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>62680.693500000001</v>
       </c>
       <c r="DM58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>65331.126475000005</v>
       </c>
       <c r="DN58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>65713.38388275</v>
       </c>
       <c r="DO58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>66788.309984907493</v>
       </c>
       <c r="DP58" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="163"/>
         <v>58411.214363530591</v>
       </c>
       <c r="DQ58" s="8">
-        <f t="shared" ref="DQ58:DU58" si="175">SUM(DQ5:DQ57)</f>
+        <f t="shared" ref="DQ58:DU58" si="164">SUM(DQ5:DQ57)</f>
         <v>46737.241624688781</v>
       </c>
       <c r="DR58" s="8">
-        <f t="shared" si="175"/>
+        <f t="shared" si="164"/>
         <v>46688.074025547932</v>
       </c>
       <c r="DS58" s="8">
-        <f t="shared" si="175"/>
+        <f t="shared" si="164"/>
         <v>47953.27315225028</v>
       </c>
       <c r="DT58" s="8">
-        <f t="shared" si="175"/>
+        <f t="shared" si="164"/>
         <v>49372.2949608981</v>
       </c>
       <c r="DU58" s="8">
-        <f t="shared" si="175"/>
+        <f t="shared" si="164"/>
         <v>50633.364874617022</v>
       </c>
     </row>
@@ -20014,7 +19951,9 @@
         <f>+CP58-CP60</f>
         <v>2492.7000000000007</v>
       </c>
-      <c r="CQ59" s="6"/>
+      <c r="CQ59" s="6">
+        <v>2462</v>
+      </c>
       <c r="CR59" s="6"/>
       <c r="CS59" s="6"/>
       <c r="CT59" s="6"/>
@@ -20032,19 +19971,19 @@
         <v>6362</v>
       </c>
       <c r="DE59" s="6">
-        <f t="shared" ref="DE59" si="176">SUM(BO59:BR59)</f>
+        <f t="shared" ref="DE59" si="165">SUM(BO59:BR59)</f>
         <v>5860</v>
       </c>
       <c r="DF59" s="6">
-        <f t="shared" ref="DF59" si="177">SUM(BS59:BV59)</f>
+        <f t="shared" ref="DF59" si="166">SUM(BS59:BV59)</f>
         <v>8175</v>
       </c>
       <c r="DG59" s="6">
-        <f t="shared" ref="DG59" si="178">SUM(BW59:BZ59)</f>
+        <f t="shared" ref="DG59" si="167">SUM(BW59:BZ59)</f>
         <v>9425</v>
       </c>
       <c r="DH59" s="6">
-        <f t="shared" ref="DH59" si="179">SUM(CA59:CD59)</f>
+        <f t="shared" ref="DH59" si="168">SUM(CA59:CD59)</f>
         <v>8705.15</v>
       </c>
       <c r="DI59" s="6">
@@ -20060,23 +19999,23 @@
         <v>9388.1405000000013</v>
       </c>
       <c r="DL59" s="6">
-        <f t="shared" ref="DL59:DP59" si="180">+DL58-DL60</f>
+        <f t="shared" ref="DL59:DP59" si="169">+DL58-DL60</f>
         <v>9402.1040250000005</v>
       </c>
       <c r="DM59" s="6">
-        <f t="shared" si="180"/>
+        <f t="shared" si="169"/>
         <v>9799.6689712500011</v>
       </c>
       <c r="DN59" s="6">
-        <f t="shared" si="180"/>
+        <f t="shared" si="169"/>
         <v>9857.0075824125015</v>
       </c>
       <c r="DO59" s="6">
-        <f t="shared" si="180"/>
+        <f t="shared" si="169"/>
         <v>10018.246497736123</v>
       </c>
       <c r="DP59" s="6">
-        <f t="shared" si="180"/>
+        <f t="shared" si="169"/>
         <v>8761.6821545295898</v>
       </c>
     </row>
@@ -20125,155 +20064,155 @@
       <c r="AO60" s="6"/>
       <c r="AP60" s="6"/>
       <c r="AQ60" s="6">
-        <f t="shared" ref="AQ60:BB60" si="181">+AQ58-AQ59</f>
+        <f t="shared" ref="AQ60:BB60" si="170">+AQ58-AQ59</f>
         <v>3176</v>
       </c>
       <c r="AR60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>3638</v>
       </c>
       <c r="AS60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>3566</v>
       </c>
       <c r="AT60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>3829</v>
       </c>
       <c r="AU60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>3463</v>
       </c>
       <c r="AV60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>3891</v>
       </c>
       <c r="AW60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>3925</v>
       </c>
       <c r="AX60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>4333</v>
       </c>
       <c r="AY60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>4098</v>
       </c>
       <c r="AZ60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>4559</v>
       </c>
       <c r="BA60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>4777</v>
       </c>
       <c r="BB60" s="6">
-        <f t="shared" si="181"/>
+        <f t="shared" si="170"/>
         <v>4885</v>
       </c>
       <c r="BC60" s="6">
-        <f t="shared" ref="BC60" si="182">+BC58-BC59</f>
+        <f t="shared" ref="BC60" si="171">+BC58-BC59</f>
         <v>4589</v>
       </c>
       <c r="BD60" s="6">
-        <f t="shared" ref="BD60:BE60" si="183">+BD58-BD59</f>
+        <f t="shared" ref="BD60:BE60" si="172">+BD58-BD59</f>
         <v>5027</v>
       </c>
       <c r="BE60" s="6">
-        <f t="shared" si="183"/>
+        <f t="shared" si="172"/>
         <v>5151</v>
       </c>
       <c r="BF60" s="6">
-        <f t="shared" ref="BF60:BG60" si="184">+BF58-BF59</f>
+        <f t="shared" ref="BF60:BG60" si="173">+BF58-BF59</f>
         <v>5497</v>
       </c>
       <c r="BG60" s="6">
-        <f t="shared" si="184"/>
+        <f t="shared" si="173"/>
         <v>5225</v>
       </c>
       <c r="BH60" s="6">
-        <f t="shared" ref="BH60:BI60" si="185">+BH58-BH59</f>
+        <f t="shared" ref="BH60:BI60" si="174">+BH58-BH59</f>
         <v>5713</v>
       </c>
       <c r="BI60" s="6">
-        <f t="shared" si="185"/>
+        <f t="shared" si="174"/>
         <v>5653</v>
       </c>
       <c r="BJ60" s="6">
-        <f t="shared" ref="BJ60" si="186">+BJ58-BJ59</f>
+        <f t="shared" ref="BJ60" si="175">+BJ58-BJ59</f>
         <v>6114</v>
       </c>
       <c r="BK60" s="6">
-        <f t="shared" ref="BK60:BP60" si="187">+BK58-BK59</f>
+        <f t="shared" ref="BK60:BP60" si="176">+BK58-BK59</f>
         <v>6362</v>
       </c>
       <c r="BL60" s="6">
-        <f t="shared" si="187"/>
+        <f t="shared" si="176"/>
         <v>6651</v>
       </c>
       <c r="BM60" s="6">
-        <f t="shared" si="187"/>
+        <f t="shared" si="176"/>
         <v>6727</v>
       </c>
       <c r="BN60" s="6">
-        <f t="shared" si="187"/>
+        <f t="shared" si="176"/>
         <v>6631</v>
       </c>
       <c r="BO60" s="6">
-        <f t="shared" si="187"/>
+        <f t="shared" si="176"/>
         <v>6525</v>
       </c>
       <c r="BP60" s="6">
-        <f t="shared" si="187"/>
+        <f t="shared" si="176"/>
         <v>6828</v>
       </c>
       <c r="BQ60" s="6">
-        <f t="shared" ref="BQ60:BR60" si="188">BQ58-BQ59</f>
+        <f t="shared" ref="BQ60:BR60" si="177">BQ58-BQ59</f>
         <v>6954</v>
       </c>
       <c r="BR60" s="6">
-        <f t="shared" si="188"/>
+        <f t="shared" si="177"/>
         <v>7099</v>
       </c>
       <c r="BS60" s="6">
-        <f t="shared" ref="BS60:BT60" si="189">BS58-BS59</f>
+        <f t="shared" ref="BS60:BT60" si="178">BS58-BS59</f>
         <v>7125</v>
       </c>
       <c r="BT60" s="6">
-        <f t="shared" si="189"/>
+        <f t="shared" si="178"/>
         <v>8629</v>
       </c>
       <c r="BU60" s="6">
-        <f t="shared" ref="BU60:CA60" si="190">BU58-BU59</f>
+        <f t="shared" ref="BU60:CA60" si="179">BU58-BU59</f>
         <v>10520</v>
       </c>
       <c r="BV60" s="6">
-        <f t="shared" si="190"/>
+        <f t="shared" si="179"/>
         <v>11335</v>
       </c>
       <c r="BW60" s="6">
-        <f t="shared" si="190"/>
+        <f t="shared" si="179"/>
         <v>10850</v>
       </c>
       <c r="BX60" s="6">
-        <f t="shared" si="190"/>
+        <f t="shared" si="179"/>
         <v>11480</v>
       </c>
       <c r="BY60" s="6">
-        <f t="shared" si="190"/>
+        <f t="shared" si="179"/>
         <v>11929</v>
       </c>
       <c r="BZ60" s="6">
-        <f t="shared" si="190"/>
+        <f t="shared" si="179"/>
         <v>12438</v>
       </c>
       <c r="CA60" s="6">
-        <f t="shared" si="190"/>
+        <f t="shared" si="179"/>
         <v>11435</v>
       </c>
       <c r="CB60" s="6">
-        <f t="shared" ref="CB60" si="191">CB58-CB59</f>
+        <f t="shared" ref="CB60" si="180">CB58-CB59</f>
         <v>12416</v>
       </c>
       <c r="CC60" s="6">
@@ -20289,27 +20228,27 @@
         <v>10294</v>
       </c>
       <c r="CF60" s="6">
-        <f t="shared" ref="CF60:CK60" si="192">+CF58-CF59</f>
+        <f t="shared" ref="CF60:CK60" si="181">+CF58-CF59</f>
         <v>11748</v>
       </c>
       <c r="CG60" s="6">
-        <f t="shared" si="192"/>
+        <f t="shared" si="181"/>
         <v>11626</v>
       </c>
       <c r="CH60" s="6">
-        <f t="shared" si="192"/>
+        <f t="shared" si="181"/>
         <v>12004</v>
       </c>
       <c r="CI60" s="6">
-        <f t="shared" si="192"/>
+        <f t="shared" si="181"/>
         <v>10202</v>
       </c>
       <c r="CJ60" s="6">
-        <f t="shared" si="192"/>
+        <f t="shared" si="181"/>
         <v>12327</v>
       </c>
       <c r="CK60" s="6">
-        <f t="shared" si="192"/>
+        <f t="shared" si="181"/>
         <v>12209</v>
       </c>
       <c r="CL60" s="6">
@@ -20332,7 +20271,10 @@
         <f>+CP58*0.85</f>
         <v>14125.3</v>
       </c>
-      <c r="CQ60" s="6"/>
+      <c r="CQ60" s="6">
+        <f>+CQ58-CQ59</f>
+        <v>12540</v>
+      </c>
       <c r="CR60" s="6"/>
       <c r="CS60" s="6"/>
       <c r="CT60" s="6"/>
@@ -20346,15 +20288,15 @@
       <c r="DB60" s="6"/>
       <c r="DC60" s="6"/>
       <c r="DD60" s="6">
-        <f t="shared" ref="DD60:DF60" si="193">+DD58-DD59</f>
+        <f t="shared" ref="DD60:DF60" si="182">+DD58-DD59</f>
         <v>26371</v>
       </c>
       <c r="DE60" s="6">
-        <f t="shared" si="193"/>
+        <f t="shared" si="182"/>
         <v>27406</v>
       </c>
       <c r="DF60" s="6">
-        <f t="shared" si="193"/>
+        <f t="shared" si="182"/>
         <v>37609</v>
       </c>
       <c r="DG60" s="6">
@@ -20378,23 +20320,23 @@
         <v>51641.229499999994</v>
       </c>
       <c r="DL60" s="6">
-        <f t="shared" ref="DL60:DP60" si="194">+DL58*0.85</f>
+        <f t="shared" ref="DL60:DP60" si="183">+DL58*0.85</f>
         <v>53278.589475000001</v>
       </c>
       <c r="DM60" s="6">
-        <f t="shared" si="194"/>
+        <f t="shared" si="183"/>
         <v>55531.457503750004</v>
       </c>
       <c r="DN60" s="6">
-        <f t="shared" si="194"/>
+        <f t="shared" si="183"/>
         <v>55856.376300337499</v>
       </c>
       <c r="DO60" s="6">
-        <f t="shared" si="194"/>
+        <f t="shared" si="183"/>
         <v>56770.06348717137</v>
       </c>
       <c r="DP60" s="6">
-        <f t="shared" si="194"/>
+        <f t="shared" si="183"/>
         <v>49649.532209001001</v>
       </c>
     </row>
@@ -20595,14 +20537,16 @@
         <v>3239</v>
       </c>
       <c r="CO61" s="6">
-        <f t="shared" ref="CO61:CO62" si="195">+CK61*1.05</f>
+        <f t="shared" ref="CO61:CO62" si="184">+CK61*1.05</f>
         <v>3492.3</v>
       </c>
       <c r="CP61" s="6">
-        <f t="shared" ref="CP61:CP62" si="196">+CL61*1.05</f>
+        <f t="shared" ref="CP61:CP62" si="185">+CL61*1.05</f>
         <v>3739.05</v>
       </c>
-      <c r="CQ61" s="6"/>
+      <c r="CQ61" s="6">
+        <v>3401</v>
+      </c>
       <c r="CR61" s="6"/>
       <c r="CS61" s="6"/>
       <c r="CT61" s="6"/>
@@ -20620,19 +20564,19 @@
         <v>6685</v>
       </c>
       <c r="DE61" s="6">
-        <f t="shared" ref="DE61:DE62" si="197">SUM(BO61:BR61)</f>
+        <f t="shared" ref="DE61:DE62" si="186">SUM(BO61:BR61)</f>
         <v>6687</v>
       </c>
       <c r="DF61" s="6">
-        <f t="shared" ref="DF61:DF62" si="198">SUM(BS61:BV61)</f>
+        <f t="shared" ref="DF61:DF62" si="187">SUM(BS61:BV61)</f>
         <v>9803</v>
       </c>
       <c r="DG61" s="6">
-        <f t="shared" ref="DG61:DG62" si="199">SUM(BW61:BZ61)</f>
+        <f t="shared" ref="DG61:DG62" si="188">SUM(BW61:BZ61)</f>
         <v>11964</v>
       </c>
       <c r="DH61" s="6">
-        <f t="shared" ref="DH61:DH62" si="200">SUM(CA61:CD61)</f>
+        <f t="shared" ref="DH61:DH62" si="189">SUM(CA61:CD61)</f>
         <v>12370.07</v>
       </c>
       <c r="DI61" s="6">
@@ -20640,7 +20584,7 @@
         <v>13072</v>
       </c>
       <c r="DJ61" s="6">
-        <f t="shared" ref="DJ61:DJ62" si="201">SUM(CI61:CL61)</f>
+        <f t="shared" ref="DJ61:DJ62" si="190">SUM(CI61:CL61)</f>
         <v>13234</v>
       </c>
       <c r="DK61" s="6">
@@ -20648,23 +20592,23 @@
         <v>13750.349999999999</v>
       </c>
       <c r="DL61" s="6">
-        <f t="shared" ref="DL61:DP61" si="202">+DL58*0.2</f>
+        <f t="shared" ref="DL61:DP61" si="191">+DL58*0.2</f>
         <v>12536.138700000001</v>
       </c>
       <c r="DM61" s="6">
-        <f t="shared" si="202"/>
+        <f t="shared" si="191"/>
         <v>13066.225295000002</v>
       </c>
       <c r="DN61" s="6">
-        <f t="shared" si="202"/>
+        <f t="shared" si="191"/>
         <v>13142.676776550001</v>
       </c>
       <c r="DO61" s="6">
-        <f t="shared" si="202"/>
+        <f t="shared" si="191"/>
         <v>13357.6619969815</v>
       </c>
       <c r="DP61" s="6">
-        <f t="shared" si="202"/>
+        <f t="shared" si="191"/>
         <v>11682.24287270612</v>
       </c>
     </row>
@@ -20865,14 +20809,16 @@
         <v>2115</v>
       </c>
       <c r="CO62" s="6">
-        <f t="shared" si="195"/>
+        <f t="shared" si="184"/>
         <v>2157.75</v>
       </c>
       <c r="CP62" s="6">
-        <f t="shared" si="196"/>
+        <f t="shared" si="185"/>
         <v>2386.65</v>
       </c>
-      <c r="CQ62" s="6"/>
+      <c r="CQ62" s="6">
+        <v>2268</v>
+      </c>
       <c r="CR62" s="6"/>
       <c r="CS62" s="6"/>
       <c r="CT62" s="6"/>
@@ -20890,19 +20836,19 @@
         <v>5093</v>
       </c>
       <c r="DE62" s="6">
-        <f t="shared" si="197"/>
+        <f t="shared" si="186"/>
         <v>4989</v>
       </c>
       <c r="DF62" s="6">
-        <f t="shared" si="198"/>
+        <f t="shared" si="187"/>
         <v>5830</v>
       </c>
       <c r="DG62" s="6">
-        <f t="shared" si="199"/>
+        <f t="shared" si="188"/>
         <v>6518</v>
       </c>
       <c r="DH62" s="6">
-        <f t="shared" si="200"/>
+        <f t="shared" si="189"/>
         <v>6509.98</v>
       </c>
       <c r="DI62" s="6">
@@ -20910,7 +20856,7 @@
         <v>7099</v>
       </c>
       <c r="DJ62" s="6">
-        <f t="shared" si="201"/>
+        <f t="shared" si="190"/>
         <v>8056</v>
       </c>
       <c r="DK62" s="6">
@@ -20967,179 +20913,179 @@
       <c r="AO63" s="6"/>
       <c r="AP63" s="6"/>
       <c r="AQ63" s="6">
-        <f t="shared" ref="AQ63:BB63" si="203">+AQ62+AQ61</f>
+        <f t="shared" ref="AQ63:BB63" si="192">+AQ62+AQ61</f>
         <v>1871</v>
       </c>
       <c r="AR63" s="6">
+        <f t="shared" si="192"/>
+        <v>2115</v>
+      </c>
+      <c r="AS63" s="6">
+        <f t="shared" si="192"/>
+        <v>1975</v>
+      </c>
+      <c r="AT63" s="6">
+        <f t="shared" si="192"/>
+        <v>2246</v>
+      </c>
+      <c r="AU63" s="6">
+        <f t="shared" si="192"/>
+        <v>2112</v>
+      </c>
+      <c r="AV63" s="6">
+        <f t="shared" si="192"/>
+        <v>2139</v>
+      </c>
+      <c r="AW63" s="6">
+        <f t="shared" si="192"/>
+        <v>2407</v>
+      </c>
+      <c r="AX63" s="6">
+        <f t="shared" si="192"/>
+        <v>4220</v>
+      </c>
+      <c r="AY63" s="6">
+        <f t="shared" si="192"/>
+        <v>2284</v>
+      </c>
+      <c r="AZ63" s="6">
+        <f t="shared" si="192"/>
+        <v>2684</v>
+      </c>
+      <c r="BA63" s="6">
+        <f t="shared" si="192"/>
+        <v>2892</v>
+      </c>
+      <c r="BB63" s="6">
+        <f t="shared" si="192"/>
+        <v>2812</v>
+      </c>
+      <c r="BC63" s="6">
+        <f t="shared" ref="BC63" si="193">+BC61+BC62</f>
+        <v>2301</v>
+      </c>
+      <c r="BD63" s="6">
+        <f t="shared" ref="BD63:BE63" si="194">+BD61+BD62</f>
+        <v>2590</v>
+      </c>
+      <c r="BE63" s="6">
+        <f t="shared" si="194"/>
+        <v>2419</v>
+      </c>
+      <c r="BF63" s="6">
+        <f t="shared" ref="BF63:BG63" si="195">+BF61+BF62</f>
+        <v>2800</v>
+      </c>
+      <c r="BG63" s="6">
+        <f t="shared" si="195"/>
+        <v>2472</v>
+      </c>
+      <c r="BH63" s="6">
+        <f t="shared" ref="BH63:BI63" si="196">+BH61+BH62</f>
+        <v>2617</v>
+      </c>
+      <c r="BI63" s="6">
+        <f t="shared" si="196"/>
+        <v>2638</v>
+      </c>
+      <c r="BJ63" s="6">
+        <f t="shared" ref="BJ63" si="197">+BJ61+BJ62</f>
+        <v>2963</v>
+      </c>
+      <c r="BK63" s="6">
+        <f t="shared" ref="BK63:BP63" si="198">+BK61+BK62</f>
+        <v>2859</v>
+      </c>
+      <c r="BL63" s="6">
+        <f t="shared" si="198"/>
+        <v>2910</v>
+      </c>
+      <c r="BM63" s="6">
+        <f t="shared" si="198"/>
+        <v>2843</v>
+      </c>
+      <c r="BN63" s="6">
+        <f t="shared" si="198"/>
+        <v>3166</v>
+      </c>
+      <c r="BO63" s="6">
+        <f t="shared" si="198"/>
+        <v>2762</v>
+      </c>
+      <c r="BP63" s="6">
+        <f t="shared" si="198"/>
+        <v>2852</v>
+      </c>
+      <c r="BQ63" s="6">
+        <f t="shared" ref="BQ63:BR63" si="199">BQ62+BQ61</f>
+        <v>2848</v>
+      </c>
+      <c r="BR63" s="6">
+        <f t="shared" si="199"/>
+        <v>3214</v>
+      </c>
+      <c r="BS63" s="6">
+        <f t="shared" ref="BS63:BT63" si="200">BS62+BS61</f>
+        <v>2833</v>
+      </c>
+      <c r="BT63" s="6">
+        <f t="shared" si="200"/>
+        <v>3724</v>
+      </c>
+      <c r="BU63" s="6">
+        <f t="shared" ref="BU63:CA63" si="201">BU62+BU61</f>
+        <v>4236</v>
+      </c>
+      <c r="BV63" s="6">
+        <f t="shared" si="201"/>
+        <v>4840</v>
+      </c>
+      <c r="BW63" s="6">
+        <f t="shared" si="201"/>
+        <v>4248</v>
+      </c>
+      <c r="BX63" s="6">
+        <f t="shared" si="201"/>
+        <v>4536</v>
+      </c>
+      <c r="BY63" s="6">
+        <f t="shared" si="201"/>
+        <v>4593</v>
+      </c>
+      <c r="BZ63" s="6">
+        <f t="shared" si="201"/>
+        <v>5105</v>
+      </c>
+      <c r="CA63" s="6">
+        <f t="shared" si="201"/>
+        <v>4332</v>
+      </c>
+      <c r="CB63" s="6">
+        <f t="shared" ref="CB63:CD63" si="202">CB62+CB61</f>
+        <v>4696</v>
+      </c>
+      <c r="CC63" s="6">
+        <f t="shared" si="202"/>
+        <v>4696</v>
+      </c>
+      <c r="CD63" s="6">
+        <f t="shared" si="202"/>
+        <v>5156.05</v>
+      </c>
+      <c r="CE63" s="6">
+        <f t="shared" ref="CE63:CH63" si="203">CE62+CE61</f>
+        <v>4641</v>
+      </c>
+      <c r="CF63" s="6">
         <f t="shared" si="203"/>
-        <v>2115</v>
-      </c>
-      <c r="AS63" s="6">
+        <v>4948</v>
+      </c>
+      <c r="CG63" s="6">
         <f t="shared" si="203"/>
-        <v>1975</v>
-      </c>
-      <c r="AT63" s="6">
+        <v>5050</v>
+      </c>
+      <c r="CH63" s="6">
         <f t="shared" si="203"/>
-        <v>2246</v>
-      </c>
-      <c r="AU63" s="6">
-        <f t="shared" si="203"/>
-        <v>2112</v>
-      </c>
-      <c r="AV63" s="6">
-        <f t="shared" si="203"/>
-        <v>2139</v>
-      </c>
-      <c r="AW63" s="6">
-        <f t="shared" si="203"/>
-        <v>2407</v>
-      </c>
-      <c r="AX63" s="6">
-        <f t="shared" si="203"/>
-        <v>4220</v>
-      </c>
-      <c r="AY63" s="6">
-        <f t="shared" si="203"/>
-        <v>2284</v>
-      </c>
-      <c r="AZ63" s="6">
-        <f t="shared" si="203"/>
-        <v>2684</v>
-      </c>
-      <c r="BA63" s="6">
-        <f t="shared" si="203"/>
-        <v>2892</v>
-      </c>
-      <c r="BB63" s="6">
-        <f t="shared" si="203"/>
-        <v>2812</v>
-      </c>
-      <c r="BC63" s="6">
-        <f t="shared" ref="BC63" si="204">+BC61+BC62</f>
-        <v>2301</v>
-      </c>
-      <c r="BD63" s="6">
-        <f t="shared" ref="BD63:BE63" si="205">+BD61+BD62</f>
-        <v>2590</v>
-      </c>
-      <c r="BE63" s="6">
-        <f t="shared" si="205"/>
-        <v>2419</v>
-      </c>
-      <c r="BF63" s="6">
-        <f t="shared" ref="BF63:BG63" si="206">+BF61+BF62</f>
-        <v>2800</v>
-      </c>
-      <c r="BG63" s="6">
-        <f t="shared" si="206"/>
-        <v>2472</v>
-      </c>
-      <c r="BH63" s="6">
-        <f t="shared" ref="BH63:BI63" si="207">+BH61+BH62</f>
-        <v>2617</v>
-      </c>
-      <c r="BI63" s="6">
-        <f t="shared" si="207"/>
-        <v>2638</v>
-      </c>
-      <c r="BJ63" s="6">
-        <f t="shared" ref="BJ63" si="208">+BJ61+BJ62</f>
-        <v>2963</v>
-      </c>
-      <c r="BK63" s="6">
-        <f t="shared" ref="BK63:BP63" si="209">+BK61+BK62</f>
-        <v>2859</v>
-      </c>
-      <c r="BL63" s="6">
-        <f t="shared" si="209"/>
-        <v>2910</v>
-      </c>
-      <c r="BM63" s="6">
-        <f t="shared" si="209"/>
-        <v>2843</v>
-      </c>
-      <c r="BN63" s="6">
-        <f t="shared" si="209"/>
-        <v>3166</v>
-      </c>
-      <c r="BO63" s="6">
-        <f t="shared" si="209"/>
-        <v>2762</v>
-      </c>
-      <c r="BP63" s="6">
-        <f t="shared" si="209"/>
-        <v>2852</v>
-      </c>
-      <c r="BQ63" s="6">
-        <f t="shared" ref="BQ63:BR63" si="210">BQ62+BQ61</f>
-        <v>2848</v>
-      </c>
-      <c r="BR63" s="6">
-        <f t="shared" si="210"/>
-        <v>3214</v>
-      </c>
-      <c r="BS63" s="6">
-        <f t="shared" ref="BS63:BT63" si="211">BS62+BS61</f>
-        <v>2833</v>
-      </c>
-      <c r="BT63" s="6">
-        <f t="shared" si="211"/>
-        <v>3724</v>
-      </c>
-      <c r="BU63" s="6">
-        <f t="shared" ref="BU63:CA63" si="212">BU62+BU61</f>
-        <v>4236</v>
-      </c>
-      <c r="BV63" s="6">
-        <f t="shared" si="212"/>
-        <v>4840</v>
-      </c>
-      <c r="BW63" s="6">
-        <f t="shared" si="212"/>
-        <v>4248</v>
-      </c>
-      <c r="BX63" s="6">
-        <f t="shared" si="212"/>
-        <v>4536</v>
-      </c>
-      <c r="BY63" s="6">
-        <f t="shared" si="212"/>
-        <v>4593</v>
-      </c>
-      <c r="BZ63" s="6">
-        <f t="shared" si="212"/>
-        <v>5105</v>
-      </c>
-      <c r="CA63" s="6">
-        <f t="shared" si="212"/>
-        <v>4332</v>
-      </c>
-      <c r="CB63" s="6">
-        <f t="shared" ref="CB63:CD63" si="213">CB62+CB61</f>
-        <v>4696</v>
-      </c>
-      <c r="CC63" s="6">
-        <f t="shared" si="213"/>
-        <v>4696</v>
-      </c>
-      <c r="CD63" s="6">
-        <f t="shared" si="213"/>
-        <v>5156.05</v>
-      </c>
-      <c r="CE63" s="6">
-        <f t="shared" ref="CE63:CH63" si="214">CE62+CE61</f>
-        <v>4641</v>
-      </c>
-      <c r="CF63" s="6">
-        <f t="shared" si="214"/>
-        <v>4948</v>
-      </c>
-      <c r="CG63" s="6">
-        <f t="shared" si="214"/>
-        <v>5050</v>
-      </c>
-      <c r="CH63" s="6">
-        <f t="shared" si="214"/>
         <v>5532</v>
       </c>
       <c r="CI63" s="6">
@@ -21147,11 +21093,11 @@
         <v>4843</v>
       </c>
       <c r="CJ63" s="6">
-        <f t="shared" ref="CJ63:CK63" si="215">+CJ61+CJ62</f>
+        <f t="shared" ref="CJ63:CK63" si="204">+CJ61+CJ62</f>
         <v>5232</v>
       </c>
       <c r="CK63" s="6">
-        <f t="shared" si="215"/>
+        <f t="shared" si="204"/>
         <v>5381</v>
       </c>
       <c r="CL63" s="6">
@@ -21159,22 +21105,25 @@
         <v>5834</v>
       </c>
       <c r="CM63" s="6">
-        <f t="shared" ref="CM63:CP63" si="216">+CM61+CM62</f>
+        <f t="shared" ref="CM63:CQ63" si="205">+CM61+CM62</f>
         <v>5331</v>
       </c>
       <c r="CN63" s="6">
-        <f t="shared" si="216"/>
+        <f t="shared" si="205"/>
         <v>5354</v>
       </c>
       <c r="CO63" s="6">
-        <f t="shared" si="216"/>
+        <f t="shared" si="205"/>
         <v>5650.05</v>
       </c>
       <c r="CP63" s="6">
-        <f t="shared" si="216"/>
+        <f t="shared" si="205"/>
         <v>6125.7000000000007</v>
       </c>
-      <c r="CQ63" s="6"/>
+      <c r="CQ63" s="6">
+        <f t="shared" si="205"/>
+        <v>5669</v>
+      </c>
       <c r="CR63" s="6"/>
       <c r="CS63" s="6"/>
       <c r="CT63" s="6"/>
@@ -21188,15 +21137,15 @@
       <c r="DB63" s="6"/>
       <c r="DC63" s="6"/>
       <c r="DD63" s="6">
-        <f t="shared" ref="DD63" si="217">+DD61+DD62</f>
+        <f t="shared" ref="DD63" si="206">+DD61+DD62</f>
         <v>11778</v>
       </c>
       <c r="DE63" s="6">
-        <f t="shared" ref="DE63:DF63" si="218">+DE61+DE62</f>
+        <f t="shared" ref="DE63:DF63" si="207">+DE61+DE62</f>
         <v>11676</v>
       </c>
       <c r="DF63" s="6">
-        <f t="shared" si="218"/>
+        <f t="shared" si="207"/>
         <v>15633</v>
       </c>
       <c r="DG63" s="6">
@@ -21208,35 +21157,35 @@
         <v>18880.05</v>
       </c>
       <c r="DI63" s="6">
-        <f t="shared" ref="DI63:DP63" si="219">+DI61+DI62</f>
+        <f t="shared" ref="DI63:DP63" si="208">+DI61+DI62</f>
         <v>20171</v>
       </c>
       <c r="DJ63" s="6">
-        <f t="shared" si="219"/>
+        <f t="shared" si="208"/>
         <v>21290</v>
       </c>
       <c r="DK63" s="6">
-        <f t="shared" si="219"/>
+        <f t="shared" si="208"/>
         <v>22460.75</v>
       </c>
       <c r="DL63" s="6">
-        <f t="shared" si="219"/>
+        <f t="shared" si="208"/>
         <v>12536.138700000001</v>
       </c>
       <c r="DM63" s="6">
-        <f t="shared" si="219"/>
+        <f t="shared" si="208"/>
         <v>13066.225295000002</v>
       </c>
       <c r="DN63" s="6">
-        <f t="shared" si="219"/>
+        <f t="shared" si="208"/>
         <v>13142.676776550001</v>
       </c>
       <c r="DO63" s="6">
-        <f t="shared" si="219"/>
+        <f t="shared" si="208"/>
         <v>13357.6619969815</v>
       </c>
       <c r="DP63" s="6">
-        <f t="shared" si="219"/>
+        <f t="shared" si="208"/>
         <v>11682.24287270612</v>
       </c>
     </row>
@@ -21305,159 +21254,159 @@
         <v>1351</v>
       </c>
       <c r="AV64" s="6">
-        <f t="shared" ref="AV64:BB64" si="220">+AV60-AV63</f>
+        <f t="shared" ref="AV64:BB64" si="209">+AV60-AV63</f>
         <v>1752</v>
       </c>
       <c r="AW64" s="6">
+        <f t="shared" si="209"/>
+        <v>1518</v>
+      </c>
+      <c r="AX64" s="6">
+        <f t="shared" si="209"/>
+        <v>113</v>
+      </c>
+      <c r="AY64" s="6">
+        <f t="shared" si="209"/>
+        <v>1814</v>
+      </c>
+      <c r="AZ64" s="6">
+        <f t="shared" si="209"/>
+        <v>1875</v>
+      </c>
+      <c r="BA64" s="6">
+        <f t="shared" si="209"/>
+        <v>1885</v>
+      </c>
+      <c r="BB64" s="6">
+        <f t="shared" si="209"/>
+        <v>2073</v>
+      </c>
+      <c r="BC64" s="6">
+        <f t="shared" ref="BC64" si="210">+BC60-BC63</f>
+        <v>2288</v>
+      </c>
+      <c r="BD64" s="6">
+        <f t="shared" ref="BD64:BE64" si="211">+BD60-BD63</f>
+        <v>2437</v>
+      </c>
+      <c r="BE64" s="6">
+        <f t="shared" si="211"/>
+        <v>2732</v>
+      </c>
+      <c r="BF64" s="6">
+        <f t="shared" ref="BF64:BG64" si="212">+BF60-BF63</f>
+        <v>2697</v>
+      </c>
+      <c r="BG64" s="6">
+        <f t="shared" si="212"/>
+        <v>2753</v>
+      </c>
+      <c r="BH64" s="6">
+        <f t="shared" ref="BH64:BI64" si="213">+BH60-BH63</f>
+        <v>3096</v>
+      </c>
+      <c r="BI64" s="6">
+        <f t="shared" si="213"/>
+        <v>3015</v>
+      </c>
+      <c r="BJ64" s="6">
+        <f t="shared" ref="BJ64" si="214">+BJ60-BJ63</f>
+        <v>3151</v>
+      </c>
+      <c r="BK64" s="6">
+        <f t="shared" ref="BK64:BP64" si="215">+BK60-BK63</f>
+        <v>3503</v>
+      </c>
+      <c r="BL64" s="6">
+        <f t="shared" si="215"/>
+        <v>3741</v>
+      </c>
+      <c r="BM64" s="6">
+        <f t="shared" si="215"/>
+        <v>3884</v>
+      </c>
+      <c r="BN64" s="6">
+        <f t="shared" si="215"/>
+        <v>3465</v>
+      </c>
+      <c r="BO64" s="6">
+        <f t="shared" si="215"/>
+        <v>3763</v>
+      </c>
+      <c r="BP64" s="6">
+        <f t="shared" si="215"/>
+        <v>3976</v>
+      </c>
+      <c r="BQ64" s="6">
+        <f t="shared" ref="BQ64:BR64" si="216">BQ60-BQ63</f>
+        <v>4106</v>
+      </c>
+      <c r="BR64" s="6">
+        <f t="shared" si="216"/>
+        <v>3885</v>
+      </c>
+      <c r="BS64" s="6">
+        <f t="shared" ref="BS64:BT64" si="217">BS60-BS63</f>
+        <v>4292</v>
+      </c>
+      <c r="BT64" s="6">
+        <f t="shared" si="217"/>
+        <v>4905</v>
+      </c>
+      <c r="BU64" s="6">
+        <f t="shared" ref="BU64:CA64" si="218">BU60-BU63</f>
+        <v>6284</v>
+      </c>
+      <c r="BV64" s="6">
+        <f t="shared" si="218"/>
+        <v>6495</v>
+      </c>
+      <c r="BW64" s="6">
+        <f t="shared" si="218"/>
+        <v>6602</v>
+      </c>
+      <c r="BX64" s="6">
+        <f t="shared" si="218"/>
+        <v>6944</v>
+      </c>
+      <c r="BY64" s="6">
+        <f t="shared" si="218"/>
+        <v>7336</v>
+      </c>
+      <c r="BZ64" s="6">
+        <f t="shared" si="218"/>
+        <v>7333</v>
+      </c>
+      <c r="CA64" s="6">
+        <f t="shared" si="218"/>
+        <v>7103</v>
+      </c>
+      <c r="CB64" s="6">
+        <f t="shared" ref="CB64:CD64" si="219">CB60-CB63</f>
+        <v>7720</v>
+      </c>
+      <c r="CC64" s="6">
+        <f t="shared" si="219"/>
+        <v>7949</v>
+      </c>
+      <c r="CD64" s="6">
+        <f t="shared" si="219"/>
+        <v>7696.8</v>
+      </c>
+      <c r="CE64" s="6">
+        <f t="shared" ref="CE64:CH64" si="220">CE60-CE63</f>
+        <v>5653</v>
+      </c>
+      <c r="CF64" s="6">
         <f t="shared" si="220"/>
-        <v>1518</v>
-      </c>
-      <c r="AX64" s="6">
+        <v>6800</v>
+      </c>
+      <c r="CG64" s="6">
         <f t="shared" si="220"/>
-        <v>113</v>
-      </c>
-      <c r="AY64" s="6">
+        <v>6576</v>
+      </c>
+      <c r="CH64" s="6">
         <f t="shared" si="220"/>
-        <v>1814</v>
-      </c>
-      <c r="AZ64" s="6">
-        <f t="shared" si="220"/>
-        <v>1875</v>
-      </c>
-      <c r="BA64" s="6">
-        <f t="shared" si="220"/>
-        <v>1885</v>
-      </c>
-      <c r="BB64" s="6">
-        <f t="shared" si="220"/>
-        <v>2073</v>
-      </c>
-      <c r="BC64" s="6">
-        <f t="shared" ref="BC64" si="221">+BC60-BC63</f>
-        <v>2288</v>
-      </c>
-      <c r="BD64" s="6">
-        <f t="shared" ref="BD64:BE64" si="222">+BD60-BD63</f>
-        <v>2437</v>
-      </c>
-      <c r="BE64" s="6">
-        <f t="shared" si="222"/>
-        <v>2732</v>
-      </c>
-      <c r="BF64" s="6">
-        <f t="shared" ref="BF64:BG64" si="223">+BF60-BF63</f>
-        <v>2697</v>
-      </c>
-      <c r="BG64" s="6">
-        <f t="shared" si="223"/>
-        <v>2753</v>
-      </c>
-      <c r="BH64" s="6">
-        <f t="shared" ref="BH64:BI64" si="224">+BH60-BH63</f>
-        <v>3096</v>
-      </c>
-      <c r="BI64" s="6">
-        <f t="shared" si="224"/>
-        <v>3015</v>
-      </c>
-      <c r="BJ64" s="6">
-        <f t="shared" ref="BJ64" si="225">+BJ60-BJ63</f>
-        <v>3151</v>
-      </c>
-      <c r="BK64" s="6">
-        <f t="shared" ref="BK64:BP64" si="226">+BK60-BK63</f>
-        <v>3503</v>
-      </c>
-      <c r="BL64" s="6">
-        <f t="shared" si="226"/>
-        <v>3741</v>
-      </c>
-      <c r="BM64" s="6">
-        <f t="shared" si="226"/>
-        <v>3884</v>
-      </c>
-      <c r="BN64" s="6">
-        <f t="shared" si="226"/>
-        <v>3465</v>
-      </c>
-      <c r="BO64" s="6">
-        <f t="shared" si="226"/>
-        <v>3763</v>
-      </c>
-      <c r="BP64" s="6">
-        <f t="shared" si="226"/>
-        <v>3976</v>
-      </c>
-      <c r="BQ64" s="6">
-        <f t="shared" ref="BQ64:BR64" si="227">BQ60-BQ63</f>
-        <v>4106</v>
-      </c>
-      <c r="BR64" s="6">
-        <f t="shared" si="227"/>
-        <v>3885</v>
-      </c>
-      <c r="BS64" s="6">
-        <f t="shared" ref="BS64:BT64" si="228">BS60-BS63</f>
-        <v>4292</v>
-      </c>
-      <c r="BT64" s="6">
-        <f t="shared" si="228"/>
-        <v>4905</v>
-      </c>
-      <c r="BU64" s="6">
-        <f t="shared" ref="BU64:CA64" si="229">BU60-BU63</f>
-        <v>6284</v>
-      </c>
-      <c r="BV64" s="6">
-        <f t="shared" si="229"/>
-        <v>6495</v>
-      </c>
-      <c r="BW64" s="6">
-        <f t="shared" si="229"/>
-        <v>6602</v>
-      </c>
-      <c r="BX64" s="6">
-        <f t="shared" si="229"/>
-        <v>6944</v>
-      </c>
-      <c r="BY64" s="6">
-        <f t="shared" si="229"/>
-        <v>7336</v>
-      </c>
-      <c r="BZ64" s="6">
-        <f t="shared" si="229"/>
-        <v>7333</v>
-      </c>
-      <c r="CA64" s="6">
-        <f t="shared" si="229"/>
-        <v>7103</v>
-      </c>
-      <c r="CB64" s="6">
-        <f t="shared" ref="CB64:CD64" si="230">CB60-CB63</f>
-        <v>7720</v>
-      </c>
-      <c r="CC64" s="6">
-        <f t="shared" si="230"/>
-        <v>7949</v>
-      </c>
-      <c r="CD64" s="6">
-        <f t="shared" si="230"/>
-        <v>7696.8</v>
-      </c>
-      <c r="CE64" s="6">
-        <f t="shared" ref="CE64:CH64" si="231">CE60-CE63</f>
-        <v>5653</v>
-      </c>
-      <c r="CF64" s="6">
-        <f t="shared" si="231"/>
-        <v>6800</v>
-      </c>
-      <c r="CG64" s="6">
-        <f t="shared" si="231"/>
-        <v>6576</v>
-      </c>
-      <c r="CH64" s="6">
-        <f t="shared" si="231"/>
         <v>6472</v>
       </c>
       <c r="CI64" s="6">
@@ -21465,11 +21414,11 @@
         <v>5359</v>
       </c>
       <c r="CJ64" s="6">
-        <f t="shared" ref="CJ64:CK64" si="232">+CJ60-CJ63</f>
+        <f t="shared" ref="CJ64:CK64" si="221">+CJ60-CJ63</f>
         <v>7095</v>
       </c>
       <c r="CK64" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="221"/>
         <v>6828</v>
       </c>
       <c r="CL64" s="6">
@@ -21477,22 +21426,25 @@
         <v>6815</v>
       </c>
       <c r="CM64" s="6">
-        <f t="shared" ref="CM64:CP64" si="233">+CM60-CM63</f>
+        <f t="shared" ref="CM64:CQ64" si="222">+CM60-CM63</f>
         <v>5785.1</v>
       </c>
       <c r="CN64" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="222"/>
         <v>7656</v>
       </c>
       <c r="CO64" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="222"/>
         <v>7759.7794999999996</v>
       </c>
       <c r="CP64" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="222"/>
         <v>7999.5999999999985</v>
       </c>
-      <c r="CQ64" s="6"/>
+      <c r="CQ64" s="6">
+        <f t="shared" si="222"/>
+        <v>6871</v>
+      </c>
       <c r="CR64" s="6"/>
       <c r="CS64" s="6"/>
       <c r="CT64" s="6"/>
@@ -21506,15 +21458,15 @@
       <c r="DB64" s="6"/>
       <c r="DC64" s="6"/>
       <c r="DD64" s="6">
-        <f t="shared" ref="DD64" si="234">+DD60-DD63</f>
+        <f t="shared" ref="DD64" si="223">+DD60-DD63</f>
         <v>14593</v>
       </c>
       <c r="DE64" s="6">
-        <f t="shared" ref="DE64:DF64" si="235">+DE60-DE63</f>
+        <f t="shared" ref="DE64:DF64" si="224">+DE60-DE63</f>
         <v>15730</v>
       </c>
       <c r="DF64" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="224"/>
         <v>21976</v>
       </c>
       <c r="DG64" s="6">
@@ -21526,35 +21478,35 @@
         <v>30468.799999999999</v>
       </c>
       <c r="DI64" s="6">
-        <f t="shared" ref="DI64:DP64" si="236">+DI60-DI63</f>
+        <f t="shared" ref="DI64:DP64" si="225">+DI60-DI63</f>
         <v>25501</v>
       </c>
       <c r="DJ64" s="6">
-        <f t="shared" si="236"/>
+        <f t="shared" si="225"/>
         <v>26097</v>
       </c>
       <c r="DK64" s="6">
-        <f t="shared" si="236"/>
+        <f t="shared" si="225"/>
         <v>29180.479499999994</v>
       </c>
       <c r="DL64" s="6">
-        <f t="shared" si="236"/>
+        <f t="shared" si="225"/>
         <v>40742.450774999998</v>
       </c>
       <c r="DM64" s="6">
-        <f t="shared" si="236"/>
+        <f t="shared" si="225"/>
         <v>42465.23220875</v>
       </c>
       <c r="DN64" s="6">
-        <f t="shared" si="236"/>
+        <f t="shared" si="225"/>
         <v>42713.699523787494</v>
       </c>
       <c r="DO64" s="6">
-        <f t="shared" si="236"/>
+        <f t="shared" si="225"/>
         <v>43412.40149018987</v>
       </c>
       <c r="DP64" s="6">
-        <f t="shared" si="236"/>
+        <f t="shared" si="225"/>
         <v>37967.289336294882</v>
       </c>
     </row>
@@ -21801,7 +21753,10 @@
         <f>+CO65</f>
         <v>-506</v>
       </c>
-      <c r="CQ65" s="6"/>
+      <c r="CQ65" s="6">
+        <f>-645+87</f>
+        <v>-558</v>
+      </c>
       <c r="CR65" s="6"/>
       <c r="CS65" s="6"/>
       <c r="CT65" s="6"/>
@@ -21815,23 +21770,23 @@
       <c r="DB65" s="6"/>
       <c r="DC65" s="6"/>
       <c r="DD65" s="6">
-        <f t="shared" ref="DD65:DD67" si="237">SUM(BK65:BN65)</f>
+        <f t="shared" ref="DD65:DD67" si="226">SUM(BK65:BN65)</f>
         <v>-1150</v>
       </c>
       <c r="DE65" s="6">
-        <f t="shared" ref="DE65" si="238">SUM(BO65:BR65)</f>
+        <f t="shared" ref="DE65" si="227">SUM(BO65:BR65)</f>
         <v>-1142</v>
       </c>
       <c r="DF65" s="6">
-        <f t="shared" ref="DF65" si="239">SUM(BS65:BV65)</f>
+        <f t="shared" ref="DF65" si="228">SUM(BS65:BV65)</f>
         <v>439</v>
       </c>
       <c r="DG65" s="6">
-        <f t="shared" ref="DG65" si="240">SUM(BW65:BZ65)</f>
+        <f t="shared" ref="DG65" si="229">SUM(BW65:BZ65)</f>
         <v>-2384</v>
       </c>
       <c r="DH65" s="6">
-        <f t="shared" ref="DH65" si="241">SUM(CA65:CD65)</f>
+        <f t="shared" ref="DH65" si="230">SUM(CA65:CD65)</f>
         <v>-1552</v>
       </c>
       <c r="DI65" s="6">
@@ -21839,7 +21794,7 @@
         <v>-977</v>
       </c>
       <c r="DJ65" s="6">
-        <f t="shared" ref="DJ65" si="242">SUM(CI65:CL65)</f>
+        <f t="shared" ref="DJ65" si="231">SUM(CI65:CL65)</f>
         <v>-1508</v>
       </c>
       <c r="DK65" s="6">
@@ -21847,11 +21802,11 @@
         <v>-2063</v>
       </c>
       <c r="DL65" s="6">
-        <f t="shared" ref="DL65:DM65" si="243">+DK65+300</f>
+        <f t="shared" ref="DL65:DM65" si="232">+DK65+300</f>
         <v>-1763</v>
       </c>
       <c r="DM65" s="6">
-        <f t="shared" si="243"/>
+        <f t="shared" si="232"/>
         <v>-1463</v>
       </c>
       <c r="DN65" s="6">
@@ -21932,159 +21887,159 @@
         <v>1289</v>
       </c>
       <c r="AV66" s="6">
-        <f t="shared" ref="AV66:BB66" si="244">+AV65+AV64</f>
+        <f t="shared" ref="AV66:BB66" si="233">+AV65+AV64</f>
         <v>1670</v>
       </c>
       <c r="AW66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="233"/>
         <v>1169</v>
       </c>
       <c r="AX66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="233"/>
         <v>-13</v>
       </c>
       <c r="AY66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="233"/>
         <v>1687</v>
       </c>
       <c r="AZ66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="233"/>
         <v>1715</v>
       </c>
       <c r="BA66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="233"/>
         <v>1660</v>
       </c>
       <c r="BB66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="233"/>
         <v>1886</v>
       </c>
       <c r="BC66" s="6">
-        <f t="shared" ref="BC66" si="245">+BC64+BC65</f>
+        <f t="shared" ref="BC66" si="234">+BC64+BC65</f>
         <v>2088</v>
       </c>
       <c r="BD66" s="6">
-        <f t="shared" ref="BD66:BE66" si="246">+BD64+BD65</f>
+        <f t="shared" ref="BD66:BE66" si="235">+BD64+BD65</f>
         <v>2161</v>
       </c>
       <c r="BE66" s="6">
-        <f t="shared" si="246"/>
+        <f t="shared" si="235"/>
         <v>2485</v>
       </c>
       <c r="BF66" s="6">
-        <f t="shared" ref="BF66:BG66" si="247">+BF64+BF65</f>
+        <f t="shared" ref="BF66:BG66" si="236">+BF64+BF65</f>
         <v>2451</v>
       </c>
       <c r="BG66" s="6">
-        <f t="shared" si="247"/>
+        <f t="shared" si="236"/>
         <v>2531</v>
       </c>
       <c r="BH66" s="6">
-        <f t="shared" ref="BH66:BI66" si="248">+BH64+BH65</f>
+        <f t="shared" ref="BH66:BI66" si="237">+BH64+BH65</f>
         <v>2843</v>
       </c>
       <c r="BI66" s="6">
-        <f t="shared" si="248"/>
+        <f t="shared" si="237"/>
         <v>2815</v>
       </c>
       <c r="BJ66" s="6">
-        <f t="shared" ref="BJ66:BP66" si="249">+BJ64+BJ65</f>
+        <f t="shared" ref="BJ66:BP66" si="238">+BJ64+BJ65</f>
         <v>2949</v>
       </c>
       <c r="BK66" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="238"/>
         <v>3257</v>
       </c>
       <c r="BL66" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="238"/>
         <v>3454</v>
       </c>
       <c r="BM66" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="238"/>
         <v>3581</v>
       </c>
       <c r="BN66" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="238"/>
         <v>3151</v>
       </c>
       <c r="BO66" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="238"/>
         <v>3472</v>
       </c>
       <c r="BP66" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="238"/>
         <v>3700</v>
       </c>
       <c r="BQ66" s="6">
-        <f t="shared" ref="BQ66:BR66" si="250">BQ64+BQ65</f>
+        <f t="shared" ref="BQ66:BR66" si="239">BQ64+BQ65</f>
         <v>3802</v>
       </c>
       <c r="BR66" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="239"/>
         <v>3614</v>
       </c>
       <c r="BS66" s="6">
-        <f t="shared" ref="BS66:BT66" si="251">BS64+BS65</f>
+        <f t="shared" ref="BS66:BT66" si="240">BS64+BS65</f>
         <v>4003</v>
       </c>
       <c r="BT66" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="240"/>
         <v>4395</v>
       </c>
       <c r="BU66" s="6">
-        <f t="shared" ref="BU66:CA66" si="252">BU64+BU65</f>
+        <f t="shared" ref="BU66:CA66" si="241">BU64+BU65</f>
         <v>6904</v>
       </c>
       <c r="BV66" s="6">
-        <f t="shared" si="252"/>
+        <f t="shared" si="241"/>
         <v>7113</v>
       </c>
       <c r="BW66" s="6">
-        <f t="shared" si="252"/>
+        <f t="shared" si="241"/>
         <v>5980</v>
       </c>
       <c r="BX66" s="6">
-        <f t="shared" si="252"/>
+        <f t="shared" si="241"/>
         <v>6338</v>
       </c>
       <c r="BY66" s="6">
-        <f t="shared" si="252"/>
+        <f t="shared" si="241"/>
         <v>6751</v>
       </c>
       <c r="BZ66" s="6">
-        <f t="shared" si="252"/>
+        <f t="shared" si="241"/>
         <v>6762</v>
       </c>
       <c r="CA66" s="6">
-        <f t="shared" si="252"/>
+        <f t="shared" si="241"/>
         <v>6592</v>
       </c>
       <c r="CB66" s="6">
-        <f t="shared" ref="CB66:CD66" si="253">CB64+CB65</f>
+        <f t="shared" ref="CB66:CD66" si="242">CB64+CB65</f>
         <v>7433</v>
       </c>
       <c r="CC66" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="242"/>
         <v>7572</v>
       </c>
       <c r="CD66" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="242"/>
         <v>7319.8</v>
       </c>
       <c r="CE66" s="6">
-        <f t="shared" ref="CE66:CH66" si="254">CE64+CE65</f>
+        <f t="shared" ref="CE66:CH66" si="243">CE64+CE65</f>
         <v>5722</v>
       </c>
       <c r="CF66" s="6">
-        <f t="shared" si="254"/>
+        <f t="shared" si="243"/>
         <v>6227</v>
       </c>
       <c r="CG66" s="6">
-        <f t="shared" si="254"/>
+        <f t="shared" si="243"/>
         <v>6324</v>
       </c>
       <c r="CH66" s="6">
-        <f t="shared" si="254"/>
+        <f t="shared" si="243"/>
         <v>6251</v>
       </c>
       <c r="CI66" s="6">
@@ -22104,22 +22059,25 @@
         <v>6406</v>
       </c>
       <c r="CM66" s="6">
-        <f t="shared" ref="CM66:CP66" si="255">+CM64+CM65</f>
+        <f t="shared" ref="CM66:CQ66" si="244">+CM64+CM65</f>
         <v>5240.1000000000004</v>
       </c>
       <c r="CN66" s="6">
-        <f t="shared" si="255"/>
+        <f t="shared" si="244"/>
         <v>7150</v>
       </c>
       <c r="CO66" s="6">
-        <f t="shared" si="255"/>
+        <f t="shared" si="244"/>
         <v>7253.7794999999996</v>
       </c>
       <c r="CP66" s="6">
-        <f t="shared" si="255"/>
+        <f t="shared" si="244"/>
         <v>7493.5999999999985</v>
       </c>
-      <c r="CQ66" s="6"/>
+      <c r="CQ66" s="6">
+        <f t="shared" si="244"/>
+        <v>6313</v>
+      </c>
       <c r="CR66" s="6"/>
       <c r="CS66" s="6"/>
       <c r="CT66" s="6"/>
@@ -22133,15 +22091,15 @@
       <c r="DB66" s="6"/>
       <c r="DC66" s="6"/>
       <c r="DD66" s="6">
-        <f t="shared" ref="DD66:DF66" si="256">+DD64+DD65</f>
+        <f t="shared" ref="DD66:DF66" si="245">+DD64+DD65</f>
         <v>13443</v>
       </c>
       <c r="DE66" s="6">
-        <f t="shared" si="256"/>
+        <f t="shared" si="245"/>
         <v>14588</v>
       </c>
       <c r="DF66" s="6">
-        <f t="shared" si="256"/>
+        <f t="shared" si="245"/>
         <v>22415</v>
       </c>
       <c r="DG66" s="6">
@@ -22153,23 +22111,23 @@
         <v>28916.799999999999</v>
       </c>
       <c r="DI66" s="6">
-        <f t="shared" ref="DI66:DP66" si="257">+DI64+DI65</f>
+        <f t="shared" ref="DI66:DP66" si="246">+DI64+DI65</f>
         <v>24524</v>
       </c>
       <c r="DJ66" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="246"/>
         <v>24589</v>
       </c>
       <c r="DK66" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="246"/>
         <v>27117.479499999994</v>
       </c>
       <c r="DL66" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="246"/>
         <v>38979.450774999998</v>
       </c>
       <c r="DM66" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="246"/>
         <v>41002.23220875</v>
       </c>
       <c r="DN66" s="6">
@@ -22177,11 +22135,11 @@
         <v>41550.699523787494</v>
       </c>
       <c r="DO66" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="246"/>
         <v>42549.40149018987</v>
       </c>
       <c r="DP66" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="246"/>
         <v>37404.289336294882</v>
       </c>
     </row>
@@ -22387,14 +22345,16 @@
         <v>1023</v>
       </c>
       <c r="CO67" s="6">
-        <f t="shared" ref="CO67:CP67" si="258">+CO66*0.1</f>
+        <f t="shared" ref="CO67:CP67" si="247">+CO66*0.1</f>
         <v>725.37795000000006</v>
       </c>
       <c r="CP67" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="247"/>
         <v>749.3599999999999</v>
       </c>
-      <c r="CQ67" s="6"/>
+      <c r="CQ67" s="6">
+        <v>514</v>
+      </c>
       <c r="CR67" s="6"/>
       <c r="CS67" s="6"/>
       <c r="CT67" s="6"/>
@@ -22408,23 +22368,23 @@
       <c r="DB67" s="6"/>
       <c r="DC67" s="6"/>
       <c r="DD67" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="226"/>
         <v>1175</v>
       </c>
       <c r="DE67" s="6">
-        <f t="shared" ref="DE67" si="259">SUM(BO67:BR67)</f>
+        <f t="shared" ref="DE67" si="248">SUM(BO67:BR67)</f>
         <v>1252</v>
       </c>
       <c r="DF67" s="6">
-        <f t="shared" ref="DF67" si="260">SUM(BS67:BV67)</f>
+        <f t="shared" ref="DF67" si="249">SUM(BS67:BV67)</f>
         <v>2245</v>
       </c>
       <c r="DG67" s="6">
-        <f t="shared" ref="DG67" si="261">SUM(BW67:BZ67)</f>
+        <f t="shared" ref="DG67" si="250">SUM(BW67:BZ67)</f>
         <v>3248</v>
       </c>
       <c r="DH67" s="6">
-        <f t="shared" ref="DH67" si="262">SUM(CA67:CD67)</f>
+        <f t="shared" ref="DH67" si="251">SUM(CA67:CD67)</f>
         <v>3805.9700000000003</v>
       </c>
       <c r="DI67" s="6">
@@ -22432,7 +22392,7 @@
         <v>2737</v>
       </c>
       <c r="DJ67" s="6">
-        <f t="shared" ref="DJ67" si="263">SUM(CI67:CL67)</f>
+        <f t="shared" ref="DJ67" si="252">SUM(CI67:CL67)</f>
         <v>3803</v>
       </c>
       <c r="DK67" s="6">
@@ -22440,23 +22400,23 @@
         <v>3223.7379499999997</v>
       </c>
       <c r="DL67" s="6">
-        <f t="shared" ref="DL67:DP67" si="264">+DL66*0.15</f>
+        <f t="shared" ref="DL67:DP67" si="253">+DL66*0.15</f>
         <v>5846.9176162499998</v>
       </c>
       <c r="DM67" s="6">
-        <f t="shared" si="264"/>
+        <f t="shared" si="253"/>
         <v>6150.3348313124998</v>
       </c>
       <c r="DN67" s="6">
-        <f t="shared" si="264"/>
+        <f t="shared" si="253"/>
         <v>6232.6049285681238</v>
       </c>
       <c r="DO67" s="6">
-        <f t="shared" si="264"/>
+        <f t="shared" si="253"/>
         <v>6382.4102235284799</v>
       </c>
       <c r="DP67" s="6">
-        <f t="shared" si="264"/>
+        <f t="shared" si="253"/>
         <v>5610.6434004442317</v>
       </c>
     </row>
@@ -22505,214 +22465,217 @@
       <c r="AO68" s="6"/>
       <c r="AP68" s="6"/>
       <c r="AQ68" s="6">
-        <f t="shared" ref="AQ68:BB68" si="265">+AQ66-AQ67</f>
+        <f t="shared" ref="AQ68:BB68" si="254">+AQ66-AQ67</f>
         <v>968</v>
       </c>
       <c r="AR68" s="6">
+        <f t="shared" si="254"/>
+        <v>1152</v>
+      </c>
+      <c r="AS68" s="6">
+        <f t="shared" si="254"/>
+        <v>1184</v>
+      </c>
+      <c r="AT68" s="6">
+        <f t="shared" si="254"/>
+        <v>1191</v>
+      </c>
+      <c r="AU68" s="6">
+        <f t="shared" si="254"/>
+        <v>983</v>
+      </c>
+      <c r="AV68" s="6">
+        <f t="shared" si="254"/>
+        <v>1335</v>
+      </c>
+      <c r="AW68" s="6">
+        <f t="shared" si="254"/>
+        <v>988</v>
+      </c>
+      <c r="AX68" s="6">
+        <f t="shared" si="254"/>
+        <v>-13</v>
+      </c>
+      <c r="AY68" s="6">
+        <f t="shared" si="254"/>
+        <v>1313</v>
+      </c>
+      <c r="AZ68" s="6">
+        <f t="shared" si="254"/>
+        <v>1403</v>
+      </c>
+      <c r="BA68" s="6">
+        <f t="shared" si="254"/>
+        <v>1252</v>
+      </c>
+      <c r="BB68" s="6">
+        <f t="shared" si="254"/>
+        <v>1479</v>
+      </c>
+      <c r="BC68" s="6">
+        <f t="shared" ref="BC68" si="255">+BC66-BC67</f>
+        <v>1666</v>
+      </c>
+      <c r="BD68" s="6">
+        <f t="shared" ref="BD68:BE68" si="256">+BD66-BD67</f>
+        <v>1675</v>
+      </c>
+      <c r="BE68" s="6">
+        <f t="shared" si="256"/>
+        <v>1990</v>
+      </c>
+      <c r="BF68" s="6">
+        <f t="shared" ref="BF68:BG68" si="257">+BF66-BF67</f>
+        <v>1954</v>
+      </c>
+      <c r="BG68" s="6">
+        <f t="shared" si="257"/>
+        <v>2073</v>
+      </c>
+      <c r="BH68" s="6">
+        <f t="shared" ref="BH68:BI68" si="258">+BH66-BH67</f>
+        <v>2295</v>
+      </c>
+      <c r="BI68" s="6">
+        <f t="shared" si="258"/>
+        <v>2282</v>
+      </c>
+      <c r="BJ68" s="6">
+        <f t="shared" ref="BJ68" si="259">+BJ66-BJ67</f>
+        <v>2393</v>
+      </c>
+      <c r="BK68" s="6">
+        <f t="shared" ref="BK68:BP68" si="260">+BK66-BK67</f>
+        <v>3008</v>
+      </c>
+      <c r="BL68" s="6">
+        <f t="shared" si="260"/>
+        <v>3143</v>
+      </c>
+      <c r="BM68" s="6">
+        <f t="shared" si="260"/>
+        <v>3255</v>
+      </c>
+      <c r="BN68" s="6">
+        <f t="shared" si="260"/>
+        <v>2862</v>
+      </c>
+      <c r="BO68" s="6">
+        <f t="shared" si="260"/>
+        <v>3198</v>
+      </c>
+      <c r="BP68" s="6">
+        <f t="shared" si="260"/>
+        <v>3376</v>
+      </c>
+      <c r="BQ68" s="6">
+        <f t="shared" ref="BQ68:BR68" si="261">BQ66-BQ67</f>
+        <v>3468</v>
+      </c>
+      <c r="BR68" s="6">
+        <f t="shared" si="261"/>
+        <v>3294</v>
+      </c>
+      <c r="BS68" s="6">
+        <f t="shared" ref="BS68:BT68" si="262">BS66-BS67</f>
+        <v>3613</v>
+      </c>
+      <c r="BT68" s="6">
+        <f t="shared" si="262"/>
+        <v>3894</v>
+      </c>
+      <c r="BU68" s="6">
+        <f t="shared" ref="BU68:CA68" si="263">BU66-BU67</f>
+        <v>6236</v>
+      </c>
+      <c r="BV68" s="6">
+        <f t="shared" si="263"/>
+        <v>6427</v>
+      </c>
+      <c r="BW68" s="6">
+        <f t="shared" si="263"/>
+        <v>5242</v>
+      </c>
+      <c r="BX68" s="6">
+        <f t="shared" si="263"/>
+        <v>5536</v>
+      </c>
+      <c r="BY68" s="6">
+        <f t="shared" si="263"/>
+        <v>5888</v>
+      </c>
+      <c r="BZ68" s="6">
+        <f t="shared" si="263"/>
+        <v>5917</v>
+      </c>
+      <c r="CA68" s="6">
+        <f t="shared" si="263"/>
+        <v>5814</v>
+      </c>
+      <c r="CB68" s="6">
+        <f t="shared" ref="CB68:CD68" si="264">CB66-CB67</f>
+        <v>6468</v>
+      </c>
+      <c r="CC68" s="6">
+        <f t="shared" si="264"/>
+        <v>6607</v>
+      </c>
+      <c r="CD68" s="6">
+        <f t="shared" si="264"/>
+        <v>6221.83</v>
+      </c>
+      <c r="CE68" s="6">
+        <f t="shared" ref="CE68:CJ68" si="265">CE66-CE67</f>
+        <v>4941</v>
+      </c>
+      <c r="CF68" s="6">
         <f t="shared" si="265"/>
-        <v>1152</v>
-      </c>
-      <c r="AS68" s="6">
+        <v>5641</v>
+      </c>
+      <c r="CG68" s="6">
         <f t="shared" si="265"/>
-        <v>1184</v>
-      </c>
-      <c r="AT68" s="6">
+        <v>5344</v>
+      </c>
+      <c r="CH68" s="6">
         <f t="shared" si="265"/>
-        <v>1191</v>
-      </c>
-      <c r="AU68" s="6">
+        <v>5861</v>
+      </c>
+      <c r="CI68" s="6">
         <f t="shared" si="265"/>
-        <v>983</v>
-      </c>
-      <c r="AV68" s="6">
+        <v>4291</v>
+      </c>
+      <c r="CJ68" s="6">
         <f t="shared" si="265"/>
-        <v>1335</v>
-      </c>
-      <c r="AW68" s="6">
-        <f t="shared" si="265"/>
-        <v>988</v>
-      </c>
-      <c r="AX68" s="6">
-        <f t="shared" si="265"/>
-        <v>-13</v>
-      </c>
-      <c r="AY68" s="6">
-        <f t="shared" si="265"/>
-        <v>1313</v>
-      </c>
-      <c r="AZ68" s="6">
-        <f t="shared" si="265"/>
-        <v>1403</v>
-      </c>
-      <c r="BA68" s="6">
-        <f t="shared" si="265"/>
-        <v>1252</v>
-      </c>
-      <c r="BB68" s="6">
-        <f t="shared" si="265"/>
-        <v>1479</v>
-      </c>
-      <c r="BC68" s="6">
-        <f t="shared" ref="BC68" si="266">+BC66-BC67</f>
-        <v>1666</v>
-      </c>
-      <c r="BD68" s="6">
-        <f t="shared" ref="BD68:BE68" si="267">+BD66-BD67</f>
-        <v>1675</v>
-      </c>
-      <c r="BE68" s="6">
+        <v>5650</v>
+      </c>
+      <c r="CK68" s="6">
+        <f t="shared" ref="CK68:CL68" si="266">CK66-CK67</f>
+        <v>5409</v>
+      </c>
+      <c r="CL68" s="6">
+        <f t="shared" si="266"/>
+        <v>5436</v>
+      </c>
+      <c r="CM68" s="6">
+        <f t="shared" ref="CM68:CQ68" si="267">CM66-CM67</f>
+        <v>4514.1000000000004</v>
+      </c>
+      <c r="CN68" s="6">
         <f t="shared" si="267"/>
-        <v>1990</v>
-      </c>
-      <c r="BF68" s="6">
-        <f t="shared" ref="BF68:BG68" si="268">+BF66-BF67</f>
-        <v>1954</v>
-      </c>
-      <c r="BG68" s="6">
-        <f t="shared" si="268"/>
-        <v>2073</v>
-      </c>
-      <c r="BH68" s="6">
-        <f t="shared" ref="BH68:BI68" si="269">+BH66-BH67</f>
-        <v>2295</v>
-      </c>
-      <c r="BI68" s="6">
-        <f t="shared" si="269"/>
-        <v>2282</v>
-      </c>
-      <c r="BJ68" s="6">
-        <f t="shared" ref="BJ68" si="270">+BJ66-BJ67</f>
-        <v>2393</v>
-      </c>
-      <c r="BK68" s="6">
-        <f t="shared" ref="BK68:BP68" si="271">+BK66-BK67</f>
-        <v>3008</v>
-      </c>
-      <c r="BL68" s="6">
-        <f t="shared" si="271"/>
-        <v>3143</v>
-      </c>
-      <c r="BM68" s="6">
-        <f t="shared" si="271"/>
-        <v>3255</v>
-      </c>
-      <c r="BN68" s="6">
-        <f t="shared" si="271"/>
-        <v>2862</v>
-      </c>
-      <c r="BO68" s="6">
-        <f t="shared" si="271"/>
-        <v>3198</v>
-      </c>
-      <c r="BP68" s="6">
-        <f t="shared" si="271"/>
-        <v>3376</v>
-      </c>
-      <c r="BQ68" s="6">
-        <f t="shared" ref="BQ68:BR68" si="272">BQ66-BQ67</f>
-        <v>3468</v>
-      </c>
-      <c r="BR68" s="6">
-        <f t="shared" si="272"/>
-        <v>3294</v>
-      </c>
-      <c r="BS68" s="6">
-        <f t="shared" ref="BS68:BT68" si="273">BS66-BS67</f>
-        <v>3613</v>
-      </c>
-      <c r="BT68" s="6">
-        <f t="shared" si="273"/>
-        <v>3894</v>
-      </c>
-      <c r="BU68" s="6">
-        <f t="shared" ref="BU68:CA68" si="274">BU66-BU67</f>
-        <v>6236</v>
-      </c>
-      <c r="BV68" s="6">
-        <f t="shared" si="274"/>
-        <v>6427</v>
-      </c>
-      <c r="BW68" s="6">
-        <f t="shared" si="274"/>
-        <v>5242</v>
-      </c>
-      <c r="BX68" s="6">
-        <f t="shared" si="274"/>
-        <v>5536</v>
-      </c>
-      <c r="BY68" s="6">
-        <f t="shared" si="274"/>
-        <v>5888</v>
-      </c>
-      <c r="BZ68" s="6">
-        <f t="shared" si="274"/>
-        <v>5917</v>
-      </c>
-      <c r="CA68" s="6">
-        <f t="shared" si="274"/>
-        <v>5814</v>
-      </c>
-      <c r="CB68" s="6">
-        <f t="shared" ref="CB68:CD68" si="275">CB66-CB67</f>
-        <v>6468</v>
-      </c>
-      <c r="CC68" s="6">
-        <f t="shared" si="275"/>
-        <v>6607</v>
-      </c>
-      <c r="CD68" s="6">
-        <f t="shared" si="275"/>
-        <v>6221.83</v>
-      </c>
-      <c r="CE68" s="6">
-        <f t="shared" ref="CE68:CJ68" si="276">CE66-CE67</f>
-        <v>4941</v>
-      </c>
-      <c r="CF68" s="6">
-        <f t="shared" si="276"/>
-        <v>5641</v>
-      </c>
-      <c r="CG68" s="6">
-        <f t="shared" si="276"/>
-        <v>5344</v>
-      </c>
-      <c r="CH68" s="6">
-        <f t="shared" si="276"/>
-        <v>5861</v>
-      </c>
-      <c r="CI68" s="6">
-        <f t="shared" si="276"/>
-        <v>4291</v>
-      </c>
-      <c r="CJ68" s="6">
-        <f t="shared" si="276"/>
-        <v>5650</v>
-      </c>
-      <c r="CK68" s="6">
-        <f t="shared" ref="CK68:CL68" si="277">CK66-CK67</f>
-        <v>5409</v>
-      </c>
-      <c r="CL68" s="6">
-        <f t="shared" si="277"/>
-        <v>5436</v>
-      </c>
-      <c r="CM68" s="6">
-        <f t="shared" ref="CM68:CP68" si="278">CM66-CM67</f>
-        <v>4514.1000000000004</v>
-      </c>
-      <c r="CN68" s="6">
-        <f t="shared" si="278"/>
         <v>6127</v>
       </c>
       <c r="CO68" s="6">
-        <f t="shared" si="278"/>
+        <f t="shared" si="267"/>
         <v>6528.4015499999996</v>
       </c>
       <c r="CP68" s="6">
-        <f t="shared" si="278"/>
+        <f t="shared" si="267"/>
         <v>6744.2399999999989</v>
       </c>
-      <c r="CQ68" s="6"/>
+      <c r="CQ68" s="6">
+        <f t="shared" si="267"/>
+        <v>5799</v>
+      </c>
       <c r="CR68" s="6"/>
       <c r="CS68" s="6"/>
       <c r="CT68" s="6"/>
@@ -22726,15 +22689,15 @@
       <c r="DB68" s="6"/>
       <c r="DC68" s="6"/>
       <c r="DD68" s="6">
-        <f t="shared" ref="DD68:DF68" si="279">+DD66-DD67</f>
+        <f t="shared" ref="DD68:DF68" si="268">+DD66-DD67</f>
         <v>12268</v>
       </c>
       <c r="DE68" s="6">
-        <f t="shared" si="279"/>
+        <f t="shared" si="268"/>
         <v>13336</v>
       </c>
       <c r="DF68" s="6">
-        <f t="shared" si="279"/>
+        <f t="shared" si="268"/>
         <v>20170</v>
       </c>
       <c r="DG68" s="6">
@@ -22750,539 +22713,539 @@
         <v>21787</v>
       </c>
       <c r="DJ68" s="6">
-        <f t="shared" ref="DJ68:DP68" si="280">+DJ66-DJ67</f>
+        <f t="shared" ref="DJ68:DP68" si="269">+DJ66-DJ67</f>
         <v>20786</v>
       </c>
       <c r="DK68" s="6">
-        <f t="shared" si="280"/>
+        <f t="shared" si="269"/>
         <v>23893.741549999995</v>
       </c>
       <c r="DL68" s="6">
-        <f t="shared" si="280"/>
+        <f t="shared" si="269"/>
         <v>33132.533158749997</v>
       </c>
       <c r="DM68" s="6">
-        <f t="shared" si="280"/>
+        <f t="shared" si="269"/>
         <v>34851.897377437497</v>
       </c>
       <c r="DN68" s="6">
-        <f t="shared" si="280"/>
+        <f t="shared" si="269"/>
         <v>35318.094595219372</v>
       </c>
       <c r="DO68" s="6">
-        <f t="shared" si="280"/>
+        <f t="shared" si="269"/>
         <v>36166.991266661389</v>
       </c>
       <c r="DP68" s="6">
-        <f t="shared" si="280"/>
+        <f t="shared" si="269"/>
         <v>31793.645935850651</v>
       </c>
       <c r="DQ68" s="5">
-        <f t="shared" ref="DQ68:EV68" si="281">DP68*(1+$DX$76)</f>
+        <f t="shared" ref="DQ68:EV68" si="270">DP68*(1+$DX$76)</f>
         <v>31475.709476492146</v>
       </c>
       <c r="DR68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>31160.952381727224</v>
       </c>
       <c r="DS68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>30849.342857909953</v>
       </c>
       <c r="DT68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>30540.849429330854</v>
       </c>
       <c r="DU68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>30235.440935037546</v>
       </c>
       <c r="DV68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>29933.086525687169</v>
       </c>
       <c r="DW68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>29633.755660430299</v>
       </c>
       <c r="DX68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>29337.418103825996</v>
       </c>
       <c r="DY68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>29044.043922787736</v>
       </c>
       <c r="DZ68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>28753.603483559858</v>
       </c>
       <c r="EA68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>28466.067448724261</v>
       </c>
       <c r="EB68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>28181.406774237017</v>
       </c>
       <c r="EC68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>27899.592706494648</v>
       </c>
       <c r="ED68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>27620.596779429703</v>
       </c>
       <c r="EE68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>27344.390811635407</v>
       </c>
       <c r="EF68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>27070.946903519052</v>
       </c>
       <c r="EG68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>26800.237434483861</v>
       </c>
       <c r="EH68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>26532.235060139021</v>
       </c>
       <c r="EI68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>26266.912709537632</v>
       </c>
       <c r="EJ68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>26004.243582442254</v>
       </c>
       <c r="EK68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>25744.20114661783</v>
       </c>
       <c r="EL68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>25486.759135151653</v>
       </c>
       <c r="EM68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>25231.891543800135</v>
       </c>
       <c r="EN68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>24979.572628362133</v>
       </c>
       <c r="EO68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>24729.776902078513</v>
       </c>
       <c r="EP68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>24482.479133057728</v>
       </c>
       <c r="EQ68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>24237.65434172715</v>
       </c>
       <c r="ER68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>23995.277798309879</v>
       </c>
       <c r="ES68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>23755.325020326778</v>
       </c>
       <c r="ET68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>23517.771770123509</v>
       </c>
       <c r="EU68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>23282.594052422275</v>
       </c>
       <c r="EV68" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="270"/>
         <v>23049.768111898051</v>
       </c>
       <c r="EW68" s="5">
-        <f t="shared" ref="EW68:GB68" si="282">EV68*(1+$DX$76)</f>
+        <f t="shared" ref="EW68:GB68" si="271">EV68*(1+$DX$76)</f>
         <v>22819.27043077907</v>
       </c>
       <c r="EX68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>22591.077726471278</v>
       </c>
       <c r="EY68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>22365.166949206567</v>
       </c>
       <c r="EZ68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>22141.515279714502</v>
       </c>
       <c r="FA68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>21920.100126917358</v>
       </c>
       <c r="FB68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>21700.899125648182</v>
       </c>
       <c r="FC68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>21483.890134391699</v>
       </c>
       <c r="FD68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>21269.051233047783</v>
       </c>
       <c r="FE68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>21056.360720717305</v>
       </c>
       <c r="FF68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>20845.797113510132</v>
       </c>
       <c r="FG68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>20637.339142375033</v>
       </c>
       <c r="FH68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>20430.965750951284</v>
       </c>
       <c r="FI68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>20226.656093441772</v>
       </c>
       <c r="FJ68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>20024.389532507354</v>
       </c>
       <c r="FK68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>19824.145637182279</v>
       </c>
       <c r="FL68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>19625.904180810456</v>
       </c>
       <c r="FM68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>19429.64513900235</v>
       </c>
       <c r="FN68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>19235.348687612328</v>
       </c>
       <c r="FO68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>19042.995200736204</v>
       </c>
       <c r="FP68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>18852.565248728843</v>
       </c>
       <c r="FQ68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>18664.039596241553</v>
       </c>
       <c r="FR68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>18477.399200279138</v>
       </c>
       <c r="FS68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>18292.625208276346</v>
       </c>
       <c r="FT68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>18109.698956193581</v>
       </c>
       <c r="FU68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>17928.601966631646</v>
       </c>
       <c r="FV68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>17749.315946965329</v>
       </c>
       <c r="FW68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>17571.822787495676</v>
       </c>
       <c r="FX68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>17396.104559620719</v>
       </c>
       <c r="FY68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>17222.143514024512</v>
       </c>
       <c r="FZ68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>17049.922078884269</v>
       </c>
       <c r="GA68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>16879.422858095426</v>
       </c>
       <c r="GB68" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="271"/>
         <v>16710.628629514471</v>
       </c>
       <c r="GC68" s="5">
-        <f t="shared" ref="GC68:HH68" si="283">GB68*(1+$DX$76)</f>
+        <f t="shared" ref="GC68:HH68" si="272">GB68*(1+$DX$76)</f>
         <v>16543.522343219327</v>
       </c>
       <c r="GD68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>16378.087119787133</v>
       </c>
       <c r="GE68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>16214.306248589261</v>
       </c>
       <c r="GF68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>16052.163186103367</v>
       </c>
       <c r="GG68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>15891.641554242333</v>
       </c>
       <c r="GH68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>15732.725138699909</v>
       </c>
       <c r="GI68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>15575.397887312909</v>
       </c>
       <c r="GJ68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>15419.643908439779</v>
       </c>
       <c r="GK68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>15265.44746935538</v>
       </c>
       <c r="GL68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>15112.792994661826</v>
       </c>
       <c r="GM68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>14961.665064715207</v>
       </c>
       <c r="GN68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>14812.048414068055</v>
       </c>
       <c r="GO68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>14663.927929927373</v>
       </c>
       <c r="GP68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>14517.288650628099</v>
       </c>
       <c r="GQ68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>14372.115764121818</v>
       </c>
       <c r="GR68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>14228.394606480599</v>
       </c>
       <c r="GS68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>14086.110660415792</v>
       </c>
       <c r="GT68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>13945.249553811635</v>
       </c>
       <c r="GU68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>13805.797058273518</v>
       </c>
       <c r="GV68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>13667.739087690783</v>
       </c>
       <c r="GW68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>13531.061696813875</v>
       </c>
       <c r="GX68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>13395.751079845735</v>
       </c>
       <c r="GY68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>13261.793569047277</v>
       </c>
       <c r="GZ68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>13129.175633356805</v>
       </c>
       <c r="HA68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>12997.883877023236</v>
       </c>
       <c r="HB68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>12867.905038253004</v>
       </c>
       <c r="HC68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>12739.225987870474</v>
       </c>
       <c r="HD68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>12611.833727991769</v>
       </c>
       <c r="HE68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>12485.71539071185</v>
       </c>
       <c r="HF68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>12360.858236804732</v>
       </c>
       <c r="HG68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>12237.249654436684</v>
       </c>
       <c r="HH68" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="272"/>
         <v>12114.877157892317</v>
       </c>
       <c r="HI68" s="5">
-        <f t="shared" ref="HI68:IM68" si="284">HH68*(1+$DX$76)</f>
+        <f t="shared" ref="HI68:IM68" si="273">HH68*(1+$DX$76)</f>
         <v>11993.728386313394</v>
       </c>
       <c r="HJ68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>11873.791102450261</v>
       </c>
       <c r="HK68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>11755.053191425759</v>
       </c>
       <c r="HL68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>11637.502659511501</v>
       </c>
       <c r="HM68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>11521.127632916387</v>
       </c>
       <c r="HN68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>11405.916356587222</v>
       </c>
       <c r="HO68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>11291.857193021349</v>
       </c>
       <c r="HP68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>11178.938621091136</v>
       </c>
       <c r="HQ68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>11067.149234880224</v>
       </c>
       <c r="HR68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10956.477742531422</v>
       </c>
       <c r="HS68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10846.912965106108</v>
       </c>
       <c r="HT68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10738.443835455048</v>
       </c>
       <c r="HU68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10631.059397100496</v>
       </c>
       <c r="HV68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10524.748803129491</v>
       </c>
       <c r="HW68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10419.501315098196</v>
       </c>
       <c r="HX68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10315.306301947214</v>
       </c>
       <c r="HY68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10212.153238927742</v>
       </c>
       <c r="HZ68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10110.031706538464</v>
       </c>
       <c r="IA68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>10008.93138947308</v>
       </c>
       <c r="IB68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9908.84207557835</v>
       </c>
       <c r="IC68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9809.7536548225671</v>
       </c>
       <c r="ID68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9711.6561182743408</v>
       </c>
       <c r="IE68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9614.5395570915971</v>
       </c>
       <c r="IF68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9518.3941615206804</v>
       </c>
       <c r="IG68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9423.2102199054734</v>
       </c>
       <c r="IH68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9328.9781177064178</v>
       </c>
       <c r="II68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9235.6883365293543</v>
       </c>
       <c r="IJ68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9143.3314531640608</v>
       </c>
       <c r="IK68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>9051.8981386324194</v>
       </c>
       <c r="IL68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>8961.3791572460959</v>
       </c>
       <c r="IM68" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="273"/>
         <v>8871.7653656736347</v>
       </c>
     </row>
@@ -23331,214 +23294,217 @@
       <c r="AO69" s="3"/>
       <c r="AP69" s="3"/>
       <c r="AQ69" s="3">
-        <f t="shared" ref="AQ69:BB69" si="285">AQ68/AQ70</f>
+        <f t="shared" ref="AQ69:BB69" si="274">AQ68/AQ70</f>
         <v>0.60311526479750777</v>
       </c>
       <c r="AR69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.71597265382224984</v>
+      </c>
+      <c r="AS69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.74465408805031441</v>
+      </c>
+      <c r="AT69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.74067164179104472</v>
+      </c>
+      <c r="AU69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.61093847110006216</v>
+      </c>
+      <c r="AV69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.83022388059701491</v>
+      </c>
+      <c r="AW69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.61366459627329195</v>
+      </c>
+      <c r="AX69" s="3">
+        <f t="shared" si="274"/>
+        <v>-8.1402629931120844E-3</v>
+      </c>
+      <c r="AY69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.81654228855721389</v>
+      </c>
+      <c r="AZ69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.85915492957746475</v>
+      </c>
+      <c r="BA69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.75240384615384615</v>
+      </c>
+      <c r="BB69" s="3">
+        <f t="shared" si="274"/>
+        <v>0.90182926829268295</v>
+      </c>
+      <c r="BC69" s="3">
+        <f t="shared" ref="BC69:BD69" si="275">BC68/BC70</f>
+        <v>1.0252307692307692</v>
+      </c>
+      <c r="BD69" s="3">
+        <f t="shared" si="275"/>
+        <v>1.0263480392156863</v>
+      </c>
+      <c r="BE69" s="3">
+        <f t="shared" ref="BE69:BF69" si="276">BE68/BE70</f>
+        <v>1.2134146341463414</v>
+      </c>
+      <c r="BF69" s="3">
+        <f t="shared" si="276"/>
+        <v>1.219725343320849</v>
+      </c>
+      <c r="BG69" s="3">
+        <f t="shared" ref="BG69:BH69" si="277">BG68/BG70</f>
+        <v>1.2932002495321273</v>
+      </c>
+      <c r="BH69" s="3">
+        <f t="shared" si="277"/>
+        <v>1.434375</v>
+      </c>
+      <c r="BI69" s="3">
+        <f t="shared" ref="BI69" si="278">BI68/BI70</f>
+        <v>1.4235807860262009</v>
+      </c>
+      <c r="BJ69" s="3">
+        <f t="shared" ref="BJ69:BK69" si="279">BJ68/BJ70</f>
+        <v>1.4937578027465668</v>
+      </c>
+      <c r="BK69" s="3">
+        <f t="shared" si="279"/>
+        <v>1.8847117794486214</v>
+      </c>
+      <c r="BL69" s="3">
+        <f t="shared" ref="BL69:BM69" si="280">BL68/BL70</f>
+        <v>1.9993638676844783</v>
+      </c>
+      <c r="BM69" s="3">
+        <f t="shared" si="280"/>
+        <v>2.1485148514851486</v>
+      </c>
+      <c r="BN69" s="3">
+        <f t="shared" ref="BN69:BR69" si="281">BN68/BN70</f>
+        <v>1.9067288474350432</v>
+      </c>
+      <c r="BO69" s="3">
+        <f t="shared" si="281"/>
+        <v>2.1564396493594065</v>
+      </c>
+      <c r="BP69" s="3">
+        <f t="shared" si="281"/>
+        <v>2.2749326145552562</v>
+      </c>
+      <c r="BQ69" s="3">
+        <f t="shared" ref="BQ69" si="282">BQ68/BQ70</f>
+        <v>2.3385030343897504</v>
+      </c>
+      <c r="BR69" s="3">
+        <f t="shared" si="281"/>
+        <v>2.2181818181818183</v>
+      </c>
+      <c r="BS69" s="3">
+        <f t="shared" ref="BS69:BT69" si="283">BS68/BS70</f>
+        <v>2.4346361185983829</v>
+      </c>
+      <c r="BT69" s="3">
+        <f t="shared" si="283"/>
+        <v>2.3642987249544625</v>
+      </c>
+      <c r="BU69" s="3">
+        <f t="shared" ref="BU69:CA69" si="284">BU68/BU70</f>
+        <v>3.5152198421645999</v>
+      </c>
+      <c r="BV69" s="3">
+        <f t="shared" si="284"/>
+        <v>3.6188063063063063</v>
+      </c>
+      <c r="BW69" s="3">
+        <f t="shared" si="284"/>
+        <v>2.9532394366197181</v>
+      </c>
+      <c r="BX69" s="3">
+        <f t="shared" si="284"/>
+        <v>3.1171171171171173</v>
+      </c>
+      <c r="BY69" s="3">
+        <f t="shared" si="284"/>
+        <v>3.3134496342149689</v>
+      </c>
+      <c r="BZ69" s="3">
+        <f t="shared" si="284"/>
+        <v>3.3278965129358831</v>
+      </c>
+      <c r="CA69" s="3">
+        <f t="shared" si="284"/>
+        <v>3.2699662542182226</v>
+      </c>
+      <c r="CB69" s="3">
+        <f t="shared" ref="CB69:CD69" si="285">CB68/CB70</f>
+        <v>3.6418918918918921</v>
+      </c>
+      <c r="CC69" s="3">
         <f t="shared" si="285"/>
-        <v>0.71597265382224984</v>
-      </c>
-      <c r="AS69" s="3">
+        <v>3.7201576576576576</v>
+      </c>
+      <c r="CD69" s="3">
         <f t="shared" si="285"/>
-        <v>0.74465408805031441</v>
-      </c>
-      <c r="AT69" s="3">
-        <f t="shared" si="285"/>
-        <v>0.74067164179104472</v>
-      </c>
-      <c r="AU69" s="3">
-        <f t="shared" si="285"/>
-        <v>0.61093847110006216</v>
-      </c>
-      <c r="AV69" s="3">
-        <f t="shared" si="285"/>
-        <v>0.83022388059701491</v>
-      </c>
-      <c r="AW69" s="3">
-        <f t="shared" si="285"/>
-        <v>0.61366459627329195</v>
-      </c>
-      <c r="AX69" s="3">
-        <f t="shared" si="285"/>
-        <v>-8.1402629931120844E-3</v>
-      </c>
-      <c r="AY69" s="3">
-        <f t="shared" si="285"/>
-        <v>0.81654228855721389</v>
-      </c>
-      <c r="AZ69" s="3">
-        <f t="shared" si="285"/>
-        <v>0.85915492957746475</v>
-      </c>
-      <c r="BA69" s="3">
-        <f t="shared" si="285"/>
-        <v>0.75240384615384615</v>
-      </c>
-      <c r="BB69" s="3">
-        <f t="shared" si="285"/>
-        <v>0.90182926829268295</v>
-      </c>
-      <c r="BC69" s="3">
-        <f t="shared" ref="BC69:BD69" si="286">BC68/BC70</f>
-        <v>1.0252307692307692</v>
-      </c>
-      <c r="BD69" s="3">
+        <v>3.5032826576576577</v>
+      </c>
+      <c r="CE69" s="3">
+        <f t="shared" ref="CE69:CJ69" si="286">CE68/CE70</f>
+        <v>2.7820945945945947</v>
+      </c>
+      <c r="CF69" s="3">
         <f t="shared" si="286"/>
-        <v>1.0263480392156863</v>
-      </c>
-      <c r="BE69" s="3">
-        <f t="shared" ref="BE69:BF69" si="287">BE68/BE70</f>
-        <v>1.2134146341463414</v>
-      </c>
-      <c r="BF69" s="3">
+        <v>3.1852060982495765</v>
+      </c>
+      <c r="CG69" s="3">
+        <f t="shared" si="286"/>
+        <v>3.0175042348955392</v>
+      </c>
+      <c r="CH69" s="3">
+        <f t="shared" si="286"/>
+        <v>3.3075620767494356</v>
+      </c>
+      <c r="CI69" s="3">
+        <f t="shared" si="286"/>
+        <v>2.4215575620767495</v>
+      </c>
+      <c r="CJ69" s="3">
+        <f t="shared" si="286"/>
+        <v>3.1902879728966687</v>
+      </c>
+      <c r="CK69" s="3">
+        <f t="shared" ref="CK69:CL69" si="287">CK68/CK70</f>
+        <v>3.0524830699774266</v>
+      </c>
+      <c r="CL69" s="3">
         <f t="shared" si="287"/>
-        <v>1.219725343320849</v>
-      </c>
-      <c r="BG69" s="3">
-        <f t="shared" ref="BG69:BH69" si="288">BG68/BG70</f>
-        <v>1.2932002495321273</v>
-      </c>
-      <c r="BH69" s="3">
+        <v>3.0659898477157359</v>
+      </c>
+      <c r="CM69" s="3">
+        <f t="shared" ref="CM69:CQ69" si="288">CM68/CM70</f>
+        <v>2.5474604966139958</v>
+      </c>
+      <c r="CN69" s="3">
         <f t="shared" si="288"/>
-        <v>1.434375</v>
-      </c>
-      <c r="BI69" s="3">
-        <f t="shared" ref="BI69" si="289">BI68/BI70</f>
-        <v>1.4235807860262009</v>
-      </c>
-      <c r="BJ69" s="3">
-        <f t="shared" ref="BJ69:BK69" si="290">BJ68/BJ70</f>
-        <v>1.4937578027465668</v>
-      </c>
-      <c r="BK69" s="3">
-        <f t="shared" si="290"/>
-        <v>1.8847117794486214</v>
-      </c>
-      <c r="BL69" s="3">
-        <f t="shared" ref="BL69:BM69" si="291">BL68/BL70</f>
-        <v>1.9993638676844783</v>
-      </c>
-      <c r="BM69" s="3">
-        <f t="shared" si="291"/>
-        <v>2.1485148514851486</v>
-      </c>
-      <c r="BN69" s="3">
-        <f t="shared" ref="BN69:BR69" si="292">BN68/BN70</f>
-        <v>1.9067288474350432</v>
-      </c>
-      <c r="BO69" s="3">
-        <f t="shared" si="292"/>
-        <v>2.1564396493594065</v>
-      </c>
-      <c r="BP69" s="3">
-        <f t="shared" si="292"/>
-        <v>2.2749326145552562</v>
-      </c>
-      <c r="BQ69" s="3">
-        <f t="shared" ref="BQ69" si="293">BQ68/BQ70</f>
-        <v>2.3385030343897504</v>
-      </c>
-      <c r="BR69" s="3">
-        <f t="shared" si="292"/>
-        <v>2.2181818181818183</v>
-      </c>
-      <c r="BS69" s="3">
-        <f t="shared" ref="BS69:BT69" si="294">BS68/BS70</f>
-        <v>2.4346361185983829</v>
-      </c>
-      <c r="BT69" s="3">
-        <f t="shared" si="294"/>
-        <v>2.3642987249544625</v>
-      </c>
-      <c r="BU69" s="3">
-        <f t="shared" ref="BU69:CA69" si="295">BU68/BU70</f>
-        <v>3.5152198421645999</v>
-      </c>
-      <c r="BV69" s="3">
-        <f t="shared" si="295"/>
-        <v>3.6188063063063063</v>
-      </c>
-      <c r="BW69" s="3">
-        <f t="shared" si="295"/>
-        <v>2.9532394366197181</v>
-      </c>
-      <c r="BX69" s="3">
-        <f t="shared" si="295"/>
-        <v>3.1171171171171173</v>
-      </c>
-      <c r="BY69" s="3">
-        <f t="shared" si="295"/>
-        <v>3.3134496342149689</v>
-      </c>
-      <c r="BZ69" s="3">
-        <f t="shared" si="295"/>
-        <v>3.3278965129358831</v>
-      </c>
-      <c r="CA69" s="3">
-        <f t="shared" si="295"/>
-        <v>3.2699662542182226</v>
-      </c>
-      <c r="CB69" s="3">
-        <f t="shared" ref="CB69:CD69" si="296">CB68/CB70</f>
-        <v>3.6418918918918921</v>
-      </c>
-      <c r="CC69" s="3">
-        <f t="shared" si="296"/>
-        <v>3.7201576576576576</v>
-      </c>
-      <c r="CD69" s="3">
-        <f t="shared" si="296"/>
-        <v>3.5032826576576577</v>
-      </c>
-      <c r="CE69" s="3">
-        <f t="shared" ref="CE69:CJ69" si="297">CE68/CE70</f>
-        <v>2.7820945945945947</v>
-      </c>
-      <c r="CF69" s="3">
-        <f t="shared" si="297"/>
-        <v>3.1852060982495765</v>
-      </c>
-      <c r="CG69" s="3">
-        <f t="shared" si="297"/>
-        <v>3.0175042348955392</v>
-      </c>
-      <c r="CH69" s="3">
-        <f t="shared" si="297"/>
-        <v>3.3075620767494356</v>
-      </c>
-      <c r="CI69" s="3">
-        <f t="shared" si="297"/>
-        <v>2.4215575620767495</v>
-      </c>
-      <c r="CJ69" s="3">
-        <f t="shared" si="297"/>
-        <v>3.1902879728966687</v>
-      </c>
-      <c r="CK69" s="3">
-        <f t="shared" ref="CK69:CL69" si="298">CK68/CK70</f>
-        <v>3.0524830699774266</v>
-      </c>
-      <c r="CL69" s="3">
-        <f t="shared" si="298"/>
-        <v>3.0659898477157359</v>
-      </c>
-      <c r="CM69" s="3">
-        <f t="shared" ref="CM69:CP69" si="299">CM68/CM70</f>
-        <v>2.5474604966139958</v>
-      </c>
-      <c r="CN69" s="3">
-        <f t="shared" si="299"/>
         <v>3.4596273291925468</v>
       </c>
       <c r="CO69" s="3">
-        <f t="shared" si="299"/>
+        <f t="shared" si="288"/>
         <v>3.686279813664596</v>
       </c>
       <c r="CP69" s="3">
-        <f t="shared" si="299"/>
+        <f t="shared" si="288"/>
         <v>3.8081535855448894</v>
       </c>
-      <c r="CQ69" s="3"/>
+      <c r="CQ69" s="3">
+        <f t="shared" si="288"/>
+        <v>3.2688838782412626</v>
+      </c>
       <c r="CR69" s="3"/>
       <c r="CS69" s="3"/>
       <c r="CT69" s="3"/>
@@ -23552,15 +23518,15 @@
       <c r="DB69" s="3"/>
       <c r="DC69" s="3"/>
       <c r="DD69" s="3">
-        <f t="shared" ref="DD69:DF69" si="300">+DD68/DD70</f>
+        <f t="shared" ref="DD69:DF69" si="289">+DD68/DD70</f>
         <v>7.9353169469598965</v>
       </c>
       <c r="DE69" s="3">
-        <f t="shared" si="300"/>
+        <f t="shared" si="289"/>
         <v>8.9880370682392581</v>
       </c>
       <c r="DF69" s="3">
-        <f t="shared" si="300"/>
+        <f t="shared" si="289"/>
         <v>12.076036521478821</v>
       </c>
       <c r="DG69" s="3">
@@ -23576,31 +23542,31 @@
         <v>12.291678420310296</v>
       </c>
       <c r="DJ69" s="3">
-        <f t="shared" ref="DJ69:DP69" si="301">+DJ68/DJ70</f>
+        <f t="shared" ref="DJ69:DP69" si="290">+DJ68/DJ70</f>
         <v>11.730248306997742</v>
       </c>
       <c r="DK69" s="3">
-        <f t="shared" si="301"/>
+        <f t="shared" si="290"/>
         <v>13.489762342978119</v>
       </c>
       <c r="DL69" s="3">
-        <f t="shared" si="301"/>
+        <f t="shared" si="290"/>
         <v>18.705735022582921</v>
       </c>
       <c r="DM69" s="3">
-        <f t="shared" si="301"/>
+        <f t="shared" si="290"/>
         <v>19.676441709209595</v>
       </c>
       <c r="DN69" s="3">
-        <f t="shared" si="301"/>
+        <f t="shared" si="290"/>
         <v>19.939644090455538</v>
       </c>
       <c r="DO69" s="3">
-        <f t="shared" si="301"/>
+        <f t="shared" si="290"/>
         <v>20.418908266287303</v>
       </c>
       <c r="DP69" s="3">
-        <f t="shared" si="301"/>
+        <f t="shared" si="290"/>
         <v>17.94983539074137</v>
       </c>
     </row>
@@ -23800,14 +23766,16 @@
         <v>1771</v>
       </c>
       <c r="CO70" s="6">
-        <f t="shared" ref="CO70" si="302">+CN70</f>
+        <f t="shared" ref="CO70" si="291">+CN70</f>
         <v>1771</v>
       </c>
       <c r="CP70" s="6">
-        <f t="shared" ref="CP70" si="303">+CO70</f>
+        <f t="shared" ref="CP70" si="292">+CO70</f>
         <v>1771</v>
       </c>
-      <c r="CQ70" s="6"/>
+      <c r="CQ70" s="6">
+        <v>1774</v>
+      </c>
       <c r="CR70" s="6"/>
       <c r="CS70" s="6"/>
       <c r="CT70" s="6"/>
@@ -23853,23 +23821,23 @@
         <v>1771.25</v>
       </c>
       <c r="DL70" s="6">
-        <f t="shared" ref="DL70:DP70" si="304">DK70</f>
+        <f t="shared" ref="DL70:DP70" si="293">DK70</f>
         <v>1771.25</v>
       </c>
       <c r="DM70" s="6">
-        <f t="shared" si="304"/>
+        <f t="shared" si="293"/>
         <v>1771.25</v>
       </c>
       <c r="DN70" s="6">
-        <f t="shared" si="304"/>
+        <f t="shared" si="293"/>
         <v>1771.25</v>
       </c>
       <c r="DO70" s="6">
-        <f t="shared" si="304"/>
+        <f t="shared" si="293"/>
         <v>1771.25</v>
       </c>
       <c r="DP70" s="6">
-        <f t="shared" si="304"/>
+        <f t="shared" si="293"/>
         <v>1771.25</v>
       </c>
     </row>
@@ -23934,83 +23902,83 @@
       <c r="BE72" s="22"/>
       <c r="BF72" s="22"/>
       <c r="BG72" s="22">
-        <f t="shared" ref="BG72:BU72" si="305">+BG58/BC58-1</f>
+        <f t="shared" ref="BG72:BU72" si="294">+BG58/BC58-1</f>
         <v>9.7348103390399565E-2</v>
       </c>
       <c r="BH72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>7.9601990049751326E-2</v>
       </c>
       <c r="BI72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>9.536486063263383E-2</v>
       </c>
       <c r="BJ72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>0.14077240566037741</v>
       </c>
       <c r="BK72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>0.21352095442031205</v>
       </c>
       <c r="BL72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>0.18922811059907829</v>
       </c>
       <c r="BM72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>0.1774124374553252</v>
       </c>
       <c r="BN72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>7.3136064090967734E-2</v>
       </c>
       <c r="BO72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>-1.3360221830098329E-2</v>
       </c>
       <c r="BP72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>-3.6328408815688995E-4</v>
       </c>
       <c r="BQ72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>2.9504613890237952E-2</v>
       </c>
       <c r="BR72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>4.8043347381095725E-2</v>
       </c>
       <c r="BS72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>0.10104752171691356</v>
       </c>
       <c r="BT72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>0.26287098728043601</v>
       </c>
       <c r="BU72" s="22">
-        <f t="shared" si="305"/>
+        <f t="shared" si="294"/>
         <v>0.51928293430829098</v>
       </c>
       <c r="BV72" s="22">
-        <f t="shared" ref="BV72:BZ72" si="306">+BV58/BR58-1</f>
+        <f t="shared" ref="BV72:BZ72" si="295">+BV58/BR58-1</f>
         <v>0.59214154411764697</v>
       </c>
       <c r="BW72" s="22">
-        <f t="shared" si="306"/>
+        <f t="shared" si="295"/>
         <v>0.50075414781297134</v>
       </c>
       <c r="BX72" s="22">
-        <f t="shared" si="306"/>
+        <f t="shared" si="295"/>
         <v>0.3389928057553957</v>
       </c>
       <c r="BY72" s="22">
-        <f t="shared" si="306"/>
+        <f t="shared" si="295"/>
         <v>0.11333643844123586</v>
       </c>
       <c r="BZ72" s="22">
-        <f t="shared" si="306"/>
+        <f t="shared" si="295"/>
         <v>7.4180978496175554E-2</v>
       </c>
       <c r="CA72" s="22">
@@ -24018,7 +23986,7 @@
         <v>4.6617703904135999E-2</v>
       </c>
       <c r="CB72" s="22">
-        <f t="shared" ref="CB72" si="307">+CB58/BX58-1</f>
+        <f t="shared" ref="CB72" si="296">+CB58/BX58-1</f>
         <v>4.4702342574683085E-2</v>
       </c>
       <c r="CC72" s="22">
@@ -24026,43 +23994,43 @@
         <v>3.2770882722074957E-2</v>
       </c>
       <c r="CD72" s="22">
-        <f t="shared" ref="CD72" si="308">+CD58/BZ58-1</f>
+        <f t="shared" ref="CD72" si="297">+CD58/BZ58-1</f>
         <v>1.5786645169958424E-2</v>
       </c>
       <c r="CE72" s="22">
-        <f t="shared" ref="CE72" si="309">+CE58/CA58-1</f>
+        <f t="shared" ref="CE72" si="298">+CE58/CA58-1</f>
         <v>-9.6986260895257748E-2</v>
       </c>
       <c r="CF72" s="22">
-        <f t="shared" ref="CF72" si="310">+CF58/CB58-1</f>
+        <f t="shared" ref="CF72" si="299">+CF58/CB58-1</f>
         <v>-4.9235411095110759E-2</v>
       </c>
       <c r="CG72" s="22">
-        <f t="shared" ref="CG72" si="311">+CG58/CC58-1</f>
+        <f t="shared" ref="CG72" si="300">+CG58/CC58-1</f>
         <v>-5.9748852281933607E-2</v>
       </c>
       <c r="CH72" s="22">
-        <f t="shared" ref="CH72:CL72" si="312">+CH58/CD58-1</f>
+        <f t="shared" ref="CH72:CL72" si="301">+CH58/CD58-1</f>
         <v>-5.4229217644335637E-2</v>
       </c>
       <c r="CI72" s="22">
-        <f t="shared" si="312"/>
+        <f t="shared" si="301"/>
         <v>6.952965235173858E-3</v>
       </c>
       <c r="CJ72" s="22">
-        <f t="shared" si="312"/>
+        <f t="shared" si="301"/>
         <v>4.3058059862964404E-2</v>
       </c>
       <c r="CK72" s="22">
-        <f t="shared" si="312"/>
+        <f t="shared" si="301"/>
         <v>3.8270984418754983E-2</v>
       </c>
       <c r="CL72" s="22">
-        <f t="shared" si="312"/>
+        <f t="shared" si="301"/>
         <v>5.6010069225928216E-2</v>
       </c>
       <c r="CM72" s="22">
-        <f t="shared" ref="CM72" si="313">+CM58/CI58-1</f>
+        <f t="shared" ref="CM72" si="302">+CM58/CI58-1</f>
         <v>7.4906580016246949E-2</v>
       </c>
       <c r="CN72" s="22">
@@ -24070,17 +24038,29 @@
         <v>6.6450006914672954E-2</v>
       </c>
       <c r="CO72" s="22">
-        <f t="shared" ref="CO72" si="314">+CO58/CK58-1</f>
+        <f t="shared" ref="CO72" si="303">+CO58/CK58-1</f>
         <v>9.1028354080221252E-2</v>
       </c>
       <c r="CP72" s="22">
-        <f t="shared" ref="CP72" si="315">+CP58/CL58-1</f>
+        <f t="shared" ref="CP72:CT72" si="304">+CP58/CL58-1</f>
         <v>0.10038405509204074</v>
       </c>
-      <c r="CQ72" s="22"/>
-      <c r="CR72" s="22"/>
-      <c r="CS72" s="22"/>
-      <c r="CT72" s="22"/>
+      <c r="CQ72" s="22">
+        <f t="shared" si="304"/>
+        <v>0.13375805805578844</v>
+      </c>
+      <c r="CR72" s="22">
+        <f t="shared" si="304"/>
+        <v>0.13526551254619723</v>
+      </c>
+      <c r="CS72" s="22">
+        <f t="shared" si="304"/>
+        <v>0.13209757439496173</v>
+      </c>
+      <c r="CT72" s="22">
+        <f t="shared" si="304"/>
+        <v>0.13659886869659399</v>
+      </c>
       <c r="CU72" s="22"/>
       <c r="CV72" s="22"/>
       <c r="CW72" s="22"/>
@@ -24108,55 +24088,55 @@
         <v>3.4425002672748617E-2</v>
       </c>
       <c r="DI72" s="22">
-        <f t="shared" ref="DI72:DU72" si="316">+DI58/DH58-1</f>
+        <f t="shared" ref="DI72:DU72" si="305">+DI58/DH58-1</f>
         <v>-6.4353877424466854E-2</v>
       </c>
       <c r="DJ72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>3.7114768584999513E-2</v>
       </c>
       <c r="DK72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>8.3348776937550939E-2</v>
       </c>
       <c r="DL72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>2.7057849360070607E-2</v>
       </c>
       <c r="DM72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>4.2284678535026154E-2</v>
       </c>
       <c r="DN72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>5.85107633030435E-3</v>
       </c>
       <c r="DO72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>1.6357795606378289E-2</v>
       </c>
       <c r="DP72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>-0.12542757292810547</v>
       </c>
       <c r="DQ72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>-0.19985841530681359</v>
       </c>
       <c r="DR72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>-1.0520004482865719E-3</v>
       </c>
       <c r="DS72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>2.7098978767254867E-2</v>
       </c>
       <c r="DT72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>2.959176121601681E-2</v>
       </c>
       <c r="DU72" s="22">
-        <f t="shared" si="316"/>
+        <f t="shared" si="305"/>
         <v>2.5542055817289189E-2</v>
       </c>
     </row>
@@ -24296,7 +24276,9 @@
       </c>
       <c r="CO73" s="22"/>
       <c r="CP73" s="22"/>
-      <c r="CQ73" s="22"/>
+      <c r="CQ73" s="22">
+        <v>0.10299999999999999</v>
+      </c>
       <c r="CR73" s="22"/>
       <c r="CS73" s="22"/>
       <c r="CT73" s="22"/>
@@ -24388,134 +24370,137 @@
       <c r="BI74" s="19"/>
       <c r="BJ74" s="19"/>
       <c r="BK74" s="19">
-        <f t="shared" ref="BK74:CL74" si="317">+BK5/BG5-1</f>
+        <f t="shared" ref="BK74:CL74" si="306">+BK5/BG5-1</f>
         <v>0.14351627003399714</v>
       </c>
       <c r="BL74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>9.9448685326547936E-2</v>
       </c>
       <c r="BM74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>8.9980855137204774E-2</v>
       </c>
       <c r="BN74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>5.3147996729354663E-3</v>
       </c>
       <c r="BO74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-5.5850499044383106E-2</v>
       </c>
       <c r="BP74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-6.0752169720347138E-2</v>
       </c>
       <c r="BQ74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-3.669008587041378E-2</v>
       </c>
       <c r="BR74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-2.0333468889788264E-4</v>
       </c>
       <c r="BS74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>5.7804768331084055E-2</v>
       </c>
       <c r="BT74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-6.7761806981520012E-3</v>
       </c>
       <c r="BU74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>4.1329011345218714E-2</v>
       </c>
       <c r="BV74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>4.7793369941020902E-2</v>
       </c>
       <c r="BW74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>3.4871358707208255E-2</v>
       </c>
       <c r="BX74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>4.7756874095513657E-2</v>
       </c>
       <c r="BY74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>5.5447470817120648E-2</v>
       </c>
       <c r="BZ74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>3.5326086956521729E-2</v>
       </c>
       <c r="CA74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-2.6915964659954827E-2</v>
       </c>
       <c r="CB74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>5.8208366219415941E-2</v>
       </c>
       <c r="CC74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>2.4700460829493176E-2</v>
       </c>
       <c r="CD74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>4.5931758530183719E-2</v>
       </c>
       <c r="CE74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-0.25232263513513509</v>
       </c>
       <c r="CF74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-0.25191124370688045</v>
       </c>
       <c r="CG74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-0.36193559992804458</v>
       </c>
       <c r="CH74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-0.40777917189460477</v>
       </c>
       <c r="CI74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-0.35893815306410615</v>
       </c>
       <c r="CJ74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-0.29860418743768691</v>
       </c>
       <c r="CK74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-0.37214547504933748</v>
       </c>
       <c r="CL74" s="19">
-        <f t="shared" si="317"/>
+        <f t="shared" si="306"/>
         <v>-0.4909200968523002</v>
       </c>
       <c r="CM74" s="19">
-        <f t="shared" ref="CM74:CP74" si="318">+CM5/CI5-1</f>
+        <f t="shared" ref="CM74:CQ74" si="307">+CM5/CI5-1</f>
         <v>-0.50616740088105727</v>
       </c>
       <c r="CN74" s="19">
-        <f t="shared" si="318"/>
+        <f t="shared" si="307"/>
         <v>-0.58066808813077464</v>
       </c>
       <c r="CO74" s="19">
-        <f t="shared" si="318"/>
+        <f t="shared" si="307"/>
         <v>-0.55410866636731027</v>
       </c>
       <c r="CP74" s="19">
-        <f t="shared" si="318"/>
+        <f t="shared" si="307"/>
         <v>-0.25921521997621877</v>
       </c>
-      <c r="CQ74" s="19"/>
+      <c r="CQ74" s="19">
+        <f t="shared" si="307"/>
+        <v>-0.38626226583407675</v>
+      </c>
       <c r="CR74" s="19"/>
       <c r="CS74" s="19"/>
       <c r="CT74" s="19"/>
@@ -24530,51 +24515,51 @@
       <c r="DC74" s="19"/>
       <c r="DD74" s="19"/>
       <c r="DE74" s="19">
-        <f t="shared" ref="DE74:DP74" si="319">+DE5/DD5-1</f>
+        <f t="shared" ref="DE74:DP74" si="308">+DE5/DD5-1</f>
         <v>-3.8473113964687E-2</v>
       </c>
       <c r="DF74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>3.4587093745109376E-2</v>
       </c>
       <c r="DG74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>4.3465106897942807E-2</v>
       </c>
       <c r="DH74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>2.623948970716139E-2</v>
       </c>
       <c r="DI74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>-0.32174977633375712</v>
       </c>
       <c r="DJ74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>-0.37565953901693971</v>
       </c>
       <c r="DK74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>-0.49516290448126321</v>
       </c>
       <c r="DL74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>-0.19999999999999996</v>
       </c>
       <c r="DM74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>-0.19999999999999984</v>
       </c>
       <c r="DN74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>-0.5</v>
       </c>
       <c r="DO74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>-0.5</v>
       </c>
       <c r="DP74" s="19">
-        <f t="shared" si="319"/>
+        <f t="shared" si="308"/>
         <v>-0.5</v>
       </c>
     </row>
@@ -24643,134 +24628,137 @@
       <c r="BI75" s="19"/>
       <c r="BJ75" s="19"/>
       <c r="BK75" s="19">
-        <f t="shared" ref="BK75:CL75" si="320">+BK7/BG7-1</f>
+        <f t="shared" ref="BK75:CL75" si="309">+BK7/BG7-1</f>
         <v>0.38294010889292207</v>
       </c>
       <c r="BL75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>0.35782747603833864</v>
       </c>
       <c r="BM75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>0.41279069767441867</v>
       </c>
       <c r="BN75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>0.42090395480225995</v>
       </c>
       <c r="BO75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>0.34120734908136474</v>
       </c>
       <c r="BP75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>0.29294117647058826</v>
       </c>
       <c r="BQ75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>0.29320987654320985</v>
       </c>
       <c r="BR75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>0.28827037773359843</v>
       </c>
       <c r="BS75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>0.20547945205479445</v>
       </c>
       <c r="BT75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>0.17197452229299359</v>
       </c>
       <c r="BU75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>8.9896579156722334E-2</v>
       </c>
       <c r="BV75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>9.8765432098765427E-2</v>
       </c>
       <c r="BW75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>2.9220779220779258E-2</v>
       </c>
       <c r="BX75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>7.2204968944099335E-2</v>
       </c>
       <c r="BY75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>2.9197080291971655E-3</v>
       </c>
       <c r="BZ75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-2.73876404494382E-2</v>
       </c>
       <c r="CA75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-7.4921135646687675E-2</v>
       </c>
       <c r="CB75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-0.17089065894279509</v>
       </c>
       <c r="CC75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-0.17394468704512378</v>
       </c>
       <c r="CD75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-0.19494584837545126</v>
       </c>
       <c r="CE75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-0.25149190110826936</v>
       </c>
       <c r="CF75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-0.20786026200873364</v>
       </c>
       <c r="CG75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-0.19999999999999996</v>
       </c>
       <c r="CH75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-0.19013452914798201</v>
       </c>
       <c r="CI75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-4.5558086560364419E-2</v>
       </c>
       <c r="CJ75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-8.158765159867698E-2</v>
       </c>
       <c r="CK75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-8.8105726872246715E-2</v>
       </c>
       <c r="CL75" s="19">
-        <f t="shared" si="320"/>
+        <f t="shared" si="309"/>
         <v>-6.0908084163898146E-2</v>
       </c>
       <c r="CM75" s="19">
-        <f t="shared" ref="CM75:CP75" si="321">+CM7/CI7-1</f>
+        <f t="shared" ref="CM75:CQ75" si="310">+CM7/CI7-1</f>
         <v>-5.0000000000000155E-2</v>
       </c>
       <c r="CN75" s="19">
-        <f t="shared" si="321"/>
+        <f t="shared" si="310"/>
         <v>-9.4837935174069576E-2</v>
       </c>
       <c r="CO75" s="19">
-        <f t="shared" si="321"/>
+        <f t="shared" si="310"/>
         <v>-5.0000000000000155E-2</v>
       </c>
       <c r="CP75" s="19">
-        <f t="shared" si="321"/>
+        <f t="shared" si="310"/>
         <v>-0.20872641509433965</v>
       </c>
-      <c r="CQ75" s="19"/>
+      <c r="CQ75" s="19">
+        <f t="shared" si="310"/>
+        <v>-0.30159527697525423</v>
+      </c>
       <c r="CR75" s="19"/>
       <c r="CS75" s="19"/>
       <c r="CT75" s="19"/>
@@ -24785,51 +24773,51 @@
       <c r="DC75" s="19"/>
       <c r="DD75" s="19"/>
       <c r="DE75" s="19">
-        <f t="shared" ref="DE75:DP75" si="322">+DE7/DD7-1</f>
+        <f t="shared" ref="DE75:DP75" si="311">+DE7/DD7-1</f>
         <v>0.30194986072423391</v>
       </c>
       <c r="DF75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>0.13692768506632436</v>
       </c>
       <c r="DG75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>1.7689123071132906E-2</v>
       </c>
       <c r="DH75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>-0.15532544378698221</v>
       </c>
       <c r="DI75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>-0.21278458844133097</v>
       </c>
       <c r="DJ75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>-6.9243604004449399E-2</v>
       </c>
       <c r="DK75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>-0.1013743651030774</v>
       </c>
       <c r="DL75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="DM75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>-9.9999999999999867E-2</v>
       </c>
       <c r="DN75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>-0.10000000000000009</v>
       </c>
       <c r="DO75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="DP75" s="19">
-        <f t="shared" si="322"/>
+        <f t="shared" si="311"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="DW75" s="30" t="s">
@@ -24941,98 +24929,101 @@
         <v>202</v>
       </c>
       <c r="BT76" s="19">
-        <f t="shared" ref="BT76:CL76" si="323">+BT8/BP8-1</f>
+        <f t="shared" ref="BT76:CL76" si="312">+BT8/BP8-1</f>
         <v>5.875</v>
       </c>
       <c r="BU76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>3.7802197802197801</v>
       </c>
       <c r="BV76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>1.4305555555555554</v>
       </c>
       <c r="BW76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.91333333333333333</v>
       </c>
       <c r="BX76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>1.0424242424242425</v>
       </c>
       <c r="BY76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.8298850574712644</v>
       </c>
       <c r="BZ76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.7047619047619047</v>
       </c>
       <c r="CA76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.63763066202090601</v>
       </c>
       <c r="CB76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.85756676557863498</v>
       </c>
       <c r="CC76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.75502512562814061</v>
       </c>
       <c r="CD76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.76089385474860327</v>
       </c>
       <c r="CE76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.44680851063829796</v>
       </c>
       <c r="CF76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.5039936102236422</v>
       </c>
       <c r="CG76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.52183249821045097</v>
       </c>
       <c r="CH76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.51903553299492389</v>
       </c>
       <c r="CI76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.4764705882352942</v>
       </c>
       <c r="CJ76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.44822092405735536</v>
       </c>
       <c r="CK76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.50752587017873951</v>
       </c>
       <c r="CL76" s="19">
-        <f t="shared" si="323"/>
+        <f t="shared" si="312"/>
         <v>0.57811194653299913</v>
       </c>
       <c r="CM76" s="19">
-        <f t="shared" ref="CM76:CP76" si="324">+CM8/CI8-1</f>
+        <f t="shared" ref="CM76:CQ76" si="313">+CM8/CI8-1</f>
         <v>0.70567729083665331</v>
       </c>
       <c r="CN76" s="19">
-        <f t="shared" si="324"/>
+        <f t="shared" si="313"/>
         <v>0.621928859552622</v>
       </c>
       <c r="CO76" s="19">
-        <f t="shared" si="324"/>
+        <f t="shared" si="313"/>
         <v>0.4689547581903275</v>
       </c>
       <c r="CP76" s="19">
-        <f t="shared" si="324"/>
+        <f t="shared" si="313"/>
         <v>0.32503970354685019</v>
       </c>
-      <c r="CQ76" s="19"/>
+      <c r="CQ76" s="19">
+        <f t="shared" si="313"/>
+        <v>0.30890510948905114</v>
+      </c>
       <c r="CR76" s="19"/>
       <c r="CS76" s="19"/>
       <c r="CT76" s="19"/>
@@ -25050,47 +25041,47 @@
         <v>202</v>
       </c>
       <c r="DF76" s="19">
-        <f t="shared" ref="DF76:DP76" si="325">+DF8/DE8-1</f>
+        <f t="shared" ref="DF76:DP76" si="314">+DF8/DE8-1</f>
         <v>3.47887323943662</v>
       </c>
       <c r="DG76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>0.84842767295597477</v>
       </c>
       <c r="DH76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>0.75740047635250085</v>
       </c>
       <c r="DI76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>0.50300096805421113</v>
       </c>
       <c r="DJ76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>0.50946798917944092</v>
       </c>
       <c r="DK76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>0.4987199180747568</v>
       </c>
       <c r="DL76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DM76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DN76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DO76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DP76" s="19">
-        <f t="shared" si="325"/>
+        <f t="shared" si="314"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DW76" s="28" t="s">
@@ -25169,118 +25160,121 @@
       <c r="BM77" s="19"/>
       <c r="BN77" s="19"/>
       <c r="BO77" s="19">
-        <f t="shared" ref="BO77:CL77" si="326">+BO3/BK3-1</f>
+        <f t="shared" ref="BO77:CL77" si="315">+BO3/BK3-1</f>
         <v>-5.5850499044383106E-2</v>
       </c>
       <c r="BP77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>-5.1494696239151372E-2</v>
       </c>
       <c r="BQ77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>-1.6198282591725177E-2</v>
       </c>
       <c r="BR77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>5.0427002846685554E-2</v>
       </c>
       <c r="BS77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.14462438146648671</v>
       </c>
       <c r="BT77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>8.0927206181374611E-2</v>
       </c>
       <c r="BU77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.14858163062884344</v>
       </c>
       <c r="BV77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.1533101045296168</v>
       </c>
       <c r="BW77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.1287089801532717</v>
       </c>
       <c r="BX77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.15124153498871329</v>
       </c>
       <c r="BY77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.15267702936096716</v>
       </c>
       <c r="BZ77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.13225914736488753</v>
       </c>
       <c r="CA77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>6.9115598885793883E-2</v>
       </c>
       <c r="CB77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.17761437908496736</v>
       </c>
       <c r="CC77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.14638897213065638</v>
       </c>
       <c r="CD77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>0.17477023421286697</v>
       </c>
       <c r="CE77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>-9.0213320306139044E-2</v>
       </c>
       <c r="CF77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>-5.4669071735812369E-2</v>
       </c>
       <c r="CG77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>-0.11344922232387922</v>
       </c>
       <c r="CH77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>-0.12264984227129339</v>
       </c>
       <c r="CI77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>-3.8661177734025443E-2</v>
       </c>
       <c r="CJ77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>2.3190958461764222E-2</v>
       </c>
       <c r="CK77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>3.8773404098481512E-2</v>
       </c>
       <c r="CL77" s="19">
-        <f t="shared" si="326"/>
+        <f t="shared" si="315"/>
         <v>4.9043578311520175E-2</v>
       </c>
       <c r="CM77" s="19">
-        <f t="shared" ref="CM77:CP77" si="327">+CM3/CI3-1</f>
+        <f t="shared" ref="CM77:CQ77" si="316">+CM3/CI3-1</f>
         <v>0.16626326568609207</v>
       </c>
       <c r="CN77" s="19">
-        <f t="shared" si="327"/>
+        <f t="shared" si="316"/>
         <v>9.4677951513412628E-2</v>
       </c>
       <c r="CO77" s="19">
-        <f t="shared" si="327"/>
+        <f t="shared" si="316"/>
         <v>0.11907465228498437</v>
       </c>
       <c r="CP77" s="19">
-        <f t="shared" si="327"/>
+        <f t="shared" si="316"/>
         <v>0.18261584864272007</v>
       </c>
-      <c r="CQ77" s="19"/>
+      <c r="CQ77" s="19">
+        <f t="shared" si="316"/>
+        <v>0.1637931034482758</v>
+      </c>
       <c r="CR77" s="19"/>
       <c r="CS77" s="19"/>
       <c r="CT77" s="19"/>
@@ -25463,82 +25457,85 @@
         <v>202</v>
       </c>
       <c r="BX78" s="19">
-        <f>BX9/BT9-1</f>
+        <f t="shared" ref="BX78:CL79" si="317">BX9/BT9-1</f>
         <v>1.584070796460177</v>
       </c>
       <c r="BY78" s="19">
-        <f>BY9/BU9-1</f>
+        <f t="shared" si="317"/>
         <v>0.38676844783715003</v>
       </c>
       <c r="BZ78" s="19">
-        <f>BZ9/BV9-1</f>
+        <f t="shared" si="317"/>
         <v>0.26977687626774838</v>
       </c>
       <c r="CA78" s="19">
-        <f>CA9/BW9-1</f>
+        <f t="shared" si="317"/>
         <v>0.34381551362683438</v>
       </c>
       <c r="CB78" s="19">
-        <f>CB9/BX9-1</f>
+        <f t="shared" si="317"/>
         <v>0.19006849315068486</v>
       </c>
       <c r="CC78" s="19">
-        <f>CC9/BY9-1</f>
+        <f t="shared" si="317"/>
         <v>0.16880733944954129</v>
       </c>
       <c r="CD78" s="19">
-        <f>CD9/BZ9-1</f>
+        <f t="shared" si="317"/>
         <v>2.5559105431310014E-2</v>
       </c>
       <c r="CE78" s="19">
-        <f>CE9/CA9-1</f>
+        <f t="shared" si="317"/>
         <v>2.808112324492984E-2</v>
       </c>
       <c r="CF78" s="19">
-        <f>CF9/CB9-1</f>
+        <f t="shared" si="317"/>
         <v>-1.4388489208633115E-2</v>
       </c>
       <c r="CG78" s="19">
-        <f>CG9/CC9-1</f>
+        <f t="shared" si="317"/>
         <v>-2.6687598116169498E-2</v>
       </c>
       <c r="CH78" s="19">
-        <f>CH9/CD9-1</f>
+        <f t="shared" si="317"/>
         <v>0.11838006230529596</v>
       </c>
       <c r="CI78" s="19">
-        <f>CI9/CE9-1</f>
+        <f t="shared" si="317"/>
         <v>-3.9453717754172946E-2</v>
       </c>
       <c r="CJ78" s="19">
-        <f>CJ9/CF9-1</f>
+        <f t="shared" si="317"/>
         <v>6.4233576642335866E-2</v>
       </c>
       <c r="CK78" s="19">
-        <f>CK9/CG9-1</f>
+        <f t="shared" si="317"/>
         <v>8.2258064516129048E-2</v>
       </c>
       <c r="CL78" s="19">
-        <f>CL9/CH9-1</f>
+        <f t="shared" si="317"/>
         <v>-4.3175487465181073E-2</v>
       </c>
       <c r="CM78" s="19">
-        <f t="shared" ref="CM78:CP78" si="328">CM9/CI9-1</f>
+        <f t="shared" ref="CM78:CQ81" si="318">CM9/CI9-1</f>
         <v>-0.12164296998420221</v>
       </c>
       <c r="CN78" s="19">
-        <f t="shared" si="328"/>
+        <f t="shared" si="318"/>
         <v>-5.0754458161865523E-2</v>
       </c>
       <c r="CO78" s="19">
-        <f t="shared" si="328"/>
+        <f t="shared" si="318"/>
         <v>-3.0000000000000027E-2</v>
       </c>
       <c r="CP78" s="19">
-        <f t="shared" si="328"/>
+        <f t="shared" si="318"/>
         <v>4.366812227074246E-2</v>
       </c>
-      <c r="CQ78" s="19"/>
+      <c r="CQ78" s="19">
+        <f t="shared" si="318"/>
+        <v>0.20143884892086339</v>
+      </c>
       <c r="CR78" s="19"/>
       <c r="CS78" s="19"/>
       <c r="CT78" s="19"/>
@@ -25555,43 +25552,43 @@
       <c r="DE78" s="19"/>
       <c r="DF78" s="19"/>
       <c r="DG78" s="19">
-        <f t="shared" ref="DG78:DP78" si="329">+DG9/DF9-1</f>
+        <f t="shared" ref="DG78:DP78" si="319">+DG9/DF9-1</f>
         <v>1.0071942446043165</v>
       </c>
       <c r="DH78" s="19">
-        <f t="shared" si="329"/>
+        <f t="shared" si="319"/>
         <v>0.17159498207885315</v>
       </c>
       <c r="DI78" s="19">
-        <f t="shared" si="329"/>
+        <f t="shared" si="319"/>
         <v>2.5621414913957974E-2</v>
       </c>
       <c r="DJ78" s="19">
-        <f t="shared" si="329"/>
+        <f t="shared" si="319"/>
         <v>1.4168530947054503E-2</v>
       </c>
       <c r="DK78" s="19">
-        <f t="shared" si="329"/>
+        <f t="shared" si="319"/>
         <v>-3.8283088235294138E-2</v>
       </c>
       <c r="DL78" s="19">
-        <f t="shared" si="329"/>
+        <f t="shared" si="319"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DM78" s="19">
-        <f t="shared" si="329"/>
+        <f t="shared" si="319"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DN78" s="19">
-        <f t="shared" si="329"/>
+        <f t="shared" si="319"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DO78" s="19">
-        <f t="shared" si="329"/>
+        <f t="shared" si="319"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DP78" s="19">
-        <f t="shared" si="329"/>
+        <f t="shared" si="319"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DW78" s="21" t="s">
@@ -25716,82 +25713,85 @@
         <v>202</v>
       </c>
       <c r="BX79" s="19">
-        <f>BX10/BT10-1</f>
+        <f t="shared" si="317"/>
         <v>1.0303030303030303</v>
       </c>
       <c r="BY79" s="19">
-        <f>BY10/BU10-1</f>
+        <f t="shared" si="317"/>
         <v>0.23326959847036322</v>
       </c>
       <c r="BZ79" s="19">
-        <f>BZ10/BV10-1</f>
+        <f t="shared" si="317"/>
         <v>0.18342151675485008</v>
       </c>
       <c r="CA79" s="19">
-        <f>CA10/BW10-1</f>
+        <f t="shared" si="317"/>
         <v>0.15413533834586457</v>
       </c>
       <c r="CB79" s="19">
-        <f>CB10/BX10-1</f>
+        <f t="shared" si="317"/>
         <v>0.12437810945273631</v>
       </c>
       <c r="CC79" s="19">
-        <f>CC10/BY10-1</f>
+        <f t="shared" si="317"/>
         <v>8.3720930232558111E-2</v>
       </c>
       <c r="CD79" s="19">
-        <f>CD10/BZ10-1</f>
+        <f t="shared" si="317"/>
         <v>8.4947839046199736E-2</v>
       </c>
       <c r="CE79" s="19">
-        <f>CE10/CA10-1</f>
+        <f t="shared" si="317"/>
         <v>0.17100977198697076</v>
       </c>
       <c r="CF79" s="19">
-        <f>CF10/CB10-1</f>
+        <f t="shared" si="317"/>
         <v>0.10324483775811211</v>
       </c>
       <c r="CG79" s="19">
-        <f>CG10/CC10-1</f>
+        <f t="shared" si="317"/>
         <v>7.0100143061516462E-2</v>
       </c>
       <c r="CH79" s="19">
-        <f>CH10/CD10-1</f>
+        <f t="shared" si="317"/>
         <v>6.5934065934065922E-2</v>
       </c>
       <c r="CI79" s="19">
-        <f>CI10/CE10-1</f>
+        <f t="shared" si="317"/>
         <v>4.0333796940194677E-2</v>
       </c>
       <c r="CJ79" s="19">
-        <f>CJ10/CF10-1</f>
+        <f t="shared" si="317"/>
         <v>8.8235294117646967E-2</v>
       </c>
       <c r="CK79" s="19">
-        <f>CK10/CG10-1</f>
+        <f t="shared" si="317"/>
         <v>0.1336898395721926</v>
       </c>
       <c r="CL79" s="19">
-        <f>CL10/CH10-1</f>
+        <f t="shared" si="317"/>
         <v>0.125</v>
       </c>
       <c r="CM79" s="19">
-        <f t="shared" ref="CM79:CP79" si="330">CM10/CI10-1</f>
+        <f t="shared" ref="CM79:CQ79" si="320">CM10/CI10-1</f>
         <v>0.15775401069518713</v>
       </c>
       <c r="CN79" s="19">
-        <f t="shared" si="330"/>
+        <f t="shared" si="320"/>
         <v>0.14004914004914015</v>
       </c>
       <c r="CO79" s="19">
-        <f t="shared" si="330"/>
+        <f t="shared" si="320"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="CP79" s="19">
-        <f t="shared" si="330"/>
+        <f t="shared" si="320"/>
         <v>0.134020618556701</v>
       </c>
-      <c r="CQ79" s="19"/>
+      <c r="CQ79" s="19">
+        <f t="shared" si="318"/>
+        <v>0.16512702078521935</v>
+      </c>
       <c r="CR79" s="19"/>
       <c r="CS79" s="19"/>
       <c r="CT79" s="19"/>
@@ -25808,43 +25808,43 @@
       <c r="DE79" s="19"/>
       <c r="DF79" s="19"/>
       <c r="DG79" s="19">
-        <f t="shared" ref="DG79:DP79" si="331">+DG10/DF10-1</f>
+        <f t="shared" ref="DG79:DP79" si="321">+DG10/DF10-1</f>
         <v>0.76712328767123283</v>
       </c>
       <c r="DH79" s="19">
-        <f t="shared" si="331"/>
+        <f t="shared" si="321"/>
         <v>0.1093431252549979</v>
       </c>
       <c r="DI79" s="19">
-        <f t="shared" si="331"/>
+        <f t="shared" si="321"/>
         <v>0.10003677822728951</v>
       </c>
       <c r="DJ79" s="19">
-        <f t="shared" si="331"/>
+        <f t="shared" si="321"/>
         <v>9.7626211969241039E-2</v>
       </c>
       <c r="DK79" s="19">
-        <f t="shared" si="331"/>
+        <f t="shared" si="321"/>
         <v>0.13213524215656425</v>
       </c>
       <c r="DL79" s="19">
-        <f t="shared" si="331"/>
+        <f t="shared" si="321"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DM79" s="19">
-        <f t="shared" si="331"/>
+        <f t="shared" si="321"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DN79" s="19">
-        <f t="shared" si="331"/>
+        <f t="shared" si="321"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DO79" s="19">
-        <f t="shared" si="331"/>
+        <f t="shared" si="321"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DP79" s="19">
-        <f t="shared" si="331"/>
+        <f t="shared" si="321"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="DW79" s="33" t="s">
@@ -25960,94 +25960,97 @@
         <v>202</v>
       </c>
       <c r="BU80" s="19">
-        <f t="shared" ref="BU80:CL80" si="332">BU13/BQ13-1</f>
+        <f t="shared" ref="BU80:CL80" si="322">BU13/BQ13-1</f>
         <v>14.357142857142858</v>
       </c>
       <c r="BV80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>7.5151515151515156</v>
       </c>
       <c r="BW80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>2.5232558139534884</v>
       </c>
       <c r="BX80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>1.5369127516778525</v>
       </c>
       <c r="BY80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>1.1069767441860465</v>
       </c>
       <c r="BZ80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.83985765124555156</v>
       </c>
       <c r="CA80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.53465346534653468</v>
       </c>
       <c r="CB80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.56613756613756605</v>
       </c>
       <c r="CC80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.53421633554083892</v>
       </c>
       <c r="CD80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.4893617021276595</v>
       </c>
       <c r="CE80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.47526881720430114</v>
       </c>
       <c r="CF80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.55067567567567566</v>
       </c>
       <c r="CG80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.59712230215827344</v>
       </c>
       <c r="CH80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.62987012987012991</v>
       </c>
       <c r="CI80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.59329446064139946</v>
       </c>
       <c r="CJ80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.55773420479302827</v>
       </c>
       <c r="CK80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.45405405405405408</v>
       </c>
       <c r="CL80" s="19">
-        <f t="shared" si="332"/>
+        <f t="shared" si="322"/>
         <v>0.46135458167330667</v>
       </c>
       <c r="CM80" s="19">
-        <f t="shared" ref="CM80:CP80" si="333">CM13/CI13-1</f>
+        <f t="shared" ref="CM80:CP80" si="323">CM13/CI13-1</f>
         <v>0.57182067703568151</v>
       </c>
       <c r="CN80" s="19">
-        <f t="shared" si="333"/>
+        <f t="shared" si="323"/>
         <v>0.41818181818181821</v>
       </c>
       <c r="CO80" s="19">
-        <f t="shared" si="333"/>
+        <f t="shared" si="323"/>
         <v>0.35315985130111516</v>
       </c>
       <c r="CP80" s="19">
-        <f t="shared" si="333"/>
+        <f t="shared" si="323"/>
         <v>0.29443838604143946</v>
       </c>
-      <c r="CQ80" s="19"/>
+      <c r="CQ80" s="19" t="e">
+        <f t="shared" si="318"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CR80" s="19"/>
       <c r="CS80" s="19"/>
       <c r="CT80" s="19"/>
@@ -26064,43 +26067,43 @@
       <c r="DE80" s="19"/>
       <c r="DF80" s="19"/>
       <c r="DG80" s="19">
-        <f t="shared" ref="DG80:DP80" si="334">+DG13/DF13-1</f>
+        <f t="shared" ref="DG80:DP80" si="324">+DG13/DF13-1</f>
         <v>1.2585499316005473</v>
       </c>
       <c r="DH80" s="19">
-        <f t="shared" si="334"/>
+        <f t="shared" si="324"/>
         <v>0.52755905511811019</v>
       </c>
       <c r="DI80" s="19">
-        <f t="shared" si="334"/>
+        <f t="shared" si="324"/>
         <v>0.57375099127676443</v>
       </c>
       <c r="DJ80" s="19">
-        <f t="shared" si="334"/>
+        <f t="shared" si="324"/>
         <v>0.50440917107583783</v>
       </c>
       <c r="DK80" s="19">
-        <f t="shared" si="334"/>
+        <f t="shared" si="324"/>
         <v>0.39072182214034501</v>
       </c>
       <c r="DL80" s="19">
-        <f t="shared" si="334"/>
+        <f t="shared" si="324"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="DM80" s="19">
-        <f t="shared" si="334"/>
+        <f t="shared" si="324"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="DN80" s="19">
-        <f t="shared" si="334"/>
+        <f t="shared" si="324"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DO80" s="19">
-        <f t="shared" si="334"/>
+        <f t="shared" si="324"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DP80" s="19">
-        <f t="shared" si="334"/>
+        <f t="shared" si="324"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -26182,55 +26185,55 @@
       <c r="BV81" s="19"/>
       <c r="BW81" s="19"/>
       <c r="BX81" s="19">
-        <f t="shared" ref="BX81" si="335">BX14/BT14-1</f>
+        <f t="shared" ref="BX81" si="325">BX14/BT14-1</f>
         <v>1.25</v>
       </c>
       <c r="BY81" s="19">
-        <f t="shared" ref="BY81" si="336">BY14/BU14-1</f>
+        <f t="shared" ref="BY81" si="326">BY14/BU14-1</f>
         <v>0.2877094972067038</v>
       </c>
       <c r="BZ81" s="19">
-        <f t="shared" ref="BZ81" si="337">BZ14/BV14-1</f>
+        <f t="shared" ref="BZ81" si="327">BZ14/BV14-1</f>
         <v>0.21945137157107242</v>
       </c>
       <c r="CA81" s="19">
-        <f t="shared" ref="CA81" si="338">CA14/BW14-1</f>
+        <f t="shared" ref="CA81" si="328">CA14/BW14-1</f>
         <v>0.23410404624277459</v>
       </c>
       <c r="CB81" s="19">
-        <f t="shared" ref="CB81" si="339">CB14/BX14-1</f>
+        <f t="shared" ref="CB81" si="329">CB14/BX14-1</f>
         <v>0.13888888888888884</v>
       </c>
       <c r="CC81" s="19">
-        <f t="shared" ref="CC81" si="340">CC14/BY14-1</f>
+        <f t="shared" ref="CC81" si="330">CC14/BY14-1</f>
         <v>0.20173535791757047</v>
       </c>
       <c r="CD81" s="19">
-        <f t="shared" ref="CD81" si="341">CD14/BZ14-1</f>
+        <f t="shared" ref="CD81" si="331">CD14/BZ14-1</f>
         <v>0.15541922290388555</v>
       </c>
       <c r="CE81" s="19">
-        <f t="shared" ref="CE81:CJ81" si="342">CE14/CA14-1</f>
+        <f t="shared" ref="CE81:CJ81" si="332">CE14/CA14-1</f>
         <v>0.31381733021077274</v>
       </c>
       <c r="CF81" s="19">
-        <f t="shared" si="342"/>
+        <f t="shared" si="332"/>
         <v>0.33739837398373984</v>
       </c>
       <c r="CG81" s="19">
-        <f t="shared" si="342"/>
+        <f t="shared" si="332"/>
         <v>0.35559566787003605</v>
       </c>
       <c r="CH81" s="19">
-        <f t="shared" si="342"/>
+        <f t="shared" si="332"/>
         <v>0.39646017699115044</v>
       </c>
       <c r="CI81" s="19">
-        <f t="shared" si="342"/>
+        <f t="shared" si="332"/>
         <v>0.23707664884135471</v>
       </c>
       <c r="CJ81" s="19">
-        <f t="shared" si="342"/>
+        <f t="shared" si="332"/>
         <v>0.17629179331306988</v>
       </c>
       <c r="CK81" s="19">
@@ -26238,26 +26241,29 @@
         <v>0.16511318242343531</v>
       </c>
       <c r="CL81" s="19">
-        <f t="shared" ref="CL81:CP81" si="343">CL14/CH14-1</f>
+        <f t="shared" ref="CL81:CP81" si="333">CL14/CH14-1</f>
         <v>0.17110266159695819</v>
       </c>
       <c r="CM81" s="19">
-        <f t="shared" si="343"/>
+        <f t="shared" si="333"/>
         <v>0.10230547550432267</v>
       </c>
       <c r="CN81" s="19">
-        <f t="shared" si="343"/>
+        <f t="shared" si="333"/>
         <v>0.16279069767441867</v>
       </c>
       <c r="CO81" s="19">
-        <f t="shared" si="343"/>
+        <f t="shared" si="333"/>
         <v>6.7428571428571393E-2</v>
       </c>
       <c r="CP81" s="19">
-        <f t="shared" si="343"/>
+        <f t="shared" si="333"/>
         <v>0.10606060606060597</v>
       </c>
-      <c r="CQ81" s="19"/>
+      <c r="CQ81" s="19">
+        <f t="shared" si="318"/>
+        <v>0.15789473684210531</v>
+      </c>
       <c r="CR81" s="19"/>
       <c r="CS81" s="19"/>
       <c r="CT81" s="19"/>
@@ -26274,19 +26280,19 @@
       <c r="DE81" s="19"/>
       <c r="DF81" s="19"/>
       <c r="DG81" s="19">
-        <f t="shared" ref="DG81:DJ81" si="344">+DG14/DF14-1</f>
+        <f t="shared" ref="DG81:DJ81" si="334">+DG14/DF14-1</f>
         <v>0.81703470031545744</v>
       </c>
       <c r="DH81" s="19">
-        <f t="shared" si="344"/>
+        <f t="shared" si="334"/>
         <v>0.17939814814814814</v>
       </c>
       <c r="DI81" s="19">
-        <f t="shared" si="344"/>
+        <f t="shared" si="334"/>
         <v>0.35377821393523057</v>
       </c>
       <c r="DJ81" s="19">
-        <f t="shared" si="344"/>
+        <f t="shared" si="334"/>
         <v>0.18412468285610739</v>
       </c>
       <c r="DK81" s="19">
@@ -26294,23 +26300,23 @@
         <v>0.1083562901744719</v>
       </c>
       <c r="DL81" s="19">
-        <f t="shared" ref="DL81:DP81" si="345">+DL14/DK14-1</f>
+        <f t="shared" ref="DL81:DP81" si="335">+DL14/DK14-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DM81" s="19">
-        <f t="shared" si="345"/>
+        <f t="shared" si="335"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DN81" s="19">
-        <f t="shared" si="345"/>
+        <f t="shared" si="335"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DO81" s="19">
-        <f t="shared" si="345"/>
+        <f t="shared" si="335"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="DP81" s="19">
-        <f t="shared" si="345"/>
+        <f t="shared" si="335"/>
         <v>-0.9</v>
       </c>
     </row>
@@ -26618,39 +26624,39 @@
       <c r="BG84" s="19"/>
       <c r="BH84" s="19"/>
       <c r="BI84" s="19">
-        <f t="shared" ref="BI84" si="346">+BI60/BI58</f>
+        <f t="shared" ref="BI84" si="336">+BI60/BI58</f>
         <v>0.80814867762687637</v>
       </c>
       <c r="BJ84" s="19">
-        <f t="shared" ref="BJ84" si="347">+BJ60/BJ58</f>
+        <f t="shared" ref="BJ84" si="337">+BJ60/BJ58</f>
         <v>0.79002455097557822</v>
       </c>
       <c r="BK84" s="19">
-        <f t="shared" ref="BK84" si="348">+BK60/BK58</f>
+        <f t="shared" ref="BK84" si="338">+BK60/BK58</f>
         <v>0.80186538946307029</v>
       </c>
       <c r="BL84" s="19">
-        <f t="shared" ref="BL84:BQ84" si="349">+BL60/BL58</f>
+        <f t="shared" ref="BL84:BQ84" si="339">+BL60/BL58</f>
         <v>0.80540082344393316</v>
       </c>
       <c r="BM84" s="19">
-        <f t="shared" si="349"/>
+        <f t="shared" si="339"/>
         <v>0.81677999028654691</v>
       </c>
       <c r="BN84" s="19">
-        <f t="shared" si="349"/>
+        <f t="shared" si="339"/>
         <v>0.79843467790487654</v>
       </c>
       <c r="BO84" s="19">
-        <f t="shared" si="349"/>
+        <f t="shared" si="339"/>
         <v>0.83354624425140522</v>
       </c>
       <c r="BP84" s="19">
-        <f t="shared" si="349"/>
+        <f t="shared" si="339"/>
         <v>0.8271350696547547</v>
       </c>
       <c r="BQ84" s="19">
-        <f t="shared" si="349"/>
+        <f t="shared" si="339"/>
         <v>0.82014388489208634</v>
       </c>
       <c r="BR84" s="19">
@@ -26670,31 +26676,31 @@
         <v>0.81664337835739786</v>
       </c>
       <c r="BV84" s="19">
-        <f t="shared" ref="BV84:CD84" si="350">+BV60/BV58</f>
+        <f t="shared" ref="BV84:CD84" si="340">+BV60/BV58</f>
         <v>0.81793909655072883</v>
       </c>
       <c r="BW84" s="19">
-        <f t="shared" si="350"/>
+        <f t="shared" si="340"/>
         <v>0.83880943177425593</v>
       </c>
       <c r="BX84" s="19">
-        <f t="shared" si="350"/>
+        <f t="shared" si="340"/>
         <v>0.82240848198295002</v>
       </c>
       <c r="BY84" s="19">
-        <f t="shared" si="350"/>
+        <f t="shared" si="340"/>
         <v>0.83175289359921911</v>
       </c>
       <c r="BZ84" s="19">
-        <f t="shared" si="350"/>
+        <f t="shared" si="340"/>
         <v>0.83555018137847648</v>
       </c>
       <c r="CA84" s="19">
-        <f t="shared" si="350"/>
+        <f t="shared" si="340"/>
         <v>0.84465947702762589</v>
       </c>
       <c r="CB84" s="19">
-        <f t="shared" si="350"/>
+        <f t="shared" si="340"/>
         <v>0.85140231776726327</v>
       </c>
       <c r="CC84" s="19">
@@ -26702,58 +26708,61 @@
         <v>0.85369970294355924</v>
       </c>
       <c r="CD84" s="19">
-        <f t="shared" si="350"/>
+        <f t="shared" si="340"/>
         <v>0.85</v>
       </c>
       <c r="CE84" s="19">
-        <f t="shared" ref="CE84:CH84" si="351">+CE60/CE58</f>
+        <f t="shared" ref="CE84:CH84" si="341">+CE60/CE58</f>
         <v>0.84204498977505116</v>
       </c>
       <c r="CF84" s="19">
-        <f t="shared" si="351"/>
+        <f t="shared" si="341"/>
         <v>0.84731337901190051</v>
       </c>
       <c r="CG84" s="19">
-        <f t="shared" si="351"/>
+        <f t="shared" si="341"/>
         <v>0.83478135994830183</v>
       </c>
       <c r="CH84" s="19">
-        <f t="shared" si="351"/>
+        <f t="shared" si="341"/>
         <v>0.83938186140829307</v>
       </c>
       <c r="CI84" s="19">
-        <f t="shared" ref="CI84:CL84" si="352">+CI60/CI58</f>
+        <f t="shared" ref="CI84:CL84" si="342">+CI60/CI58</f>
         <v>0.82875710804224212</v>
       </c>
       <c r="CJ84" s="19">
-        <f t="shared" si="352"/>
+        <f t="shared" si="342"/>
         <v>0.85237173281703771</v>
       </c>
       <c r="CK84" s="19">
-        <f t="shared" si="352"/>
+        <f t="shared" si="342"/>
         <v>0.84432918395573997</v>
       </c>
       <c r="CL84" s="19">
-        <f t="shared" si="352"/>
+        <f t="shared" si="342"/>
         <v>0.83757118262481789</v>
       </c>
       <c r="CM84" s="19">
-        <f t="shared" ref="CM84:CP84" si="353">+CM60/CM58</f>
+        <f t="shared" ref="CM84:CQ84" si="343">+CM60/CM58</f>
         <v>0.84008585183001938</v>
       </c>
       <c r="CN84" s="19">
-        <f t="shared" si="353"/>
+        <f t="shared" si="343"/>
         <v>0.84354535434091937</v>
       </c>
       <c r="CO84" s="19">
-        <f t="shared" si="353"/>
+        <f t="shared" si="343"/>
         <v>0.85</v>
       </c>
       <c r="CP84" s="19">
-        <f t="shared" si="353"/>
+        <f t="shared" si="343"/>
         <v>0.85</v>
       </c>
-      <c r="CQ84" s="19"/>
+      <c r="CQ84" s="19">
+        <f t="shared" si="343"/>
+        <v>0.83588854819357417</v>
+      </c>
       <c r="CR84" s="19"/>
       <c r="CS84" s="19"/>
       <c r="CT84" s="19"/>
@@ -26787,35 +26796,35 @@
         <v>0.85005081475867295</v>
       </c>
       <c r="DI84" s="19">
-        <f t="shared" ref="DI84:DM84" si="354">+DI60/DI58</f>
+        <f t="shared" ref="DI84:DM84" si="344">+DI60/DI58</f>
         <v>0.84082624544349938</v>
       </c>
       <c r="DJ84" s="19">
-        <f t="shared" si="354"/>
+        <f t="shared" si="344"/>
         <v>0.84117939432669431</v>
       </c>
       <c r="DK84" s="19">
-        <f t="shared" si="354"/>
+        <f t="shared" si="344"/>
         <v>0.84617012268027669</v>
       </c>
       <c r="DL84" s="19">
-        <f t="shared" si="354"/>
+        <f t="shared" si="344"/>
         <v>0.85</v>
       </c>
       <c r="DM84" s="19">
-        <f t="shared" si="354"/>
+        <f t="shared" si="344"/>
         <v>0.85</v>
       </c>
       <c r="DN84" s="19">
-        <f t="shared" ref="DN84:DP84" si="355">+DN60/DN58</f>
+        <f t="shared" ref="DN84:DP84" si="345">+DN60/DN58</f>
         <v>0.85</v>
       </c>
       <c r="DO84" s="19">
-        <f t="shared" si="355"/>
+        <f t="shared" si="345"/>
         <v>0.85</v>
       </c>
       <c r="DP84" s="19">
-        <f t="shared" si="355"/>
+        <f t="shared" si="345"/>
         <v>0.85</v>
       </c>
     </row>
@@ -26882,39 +26891,39 @@
       <c r="BG85" s="19"/>
       <c r="BH85" s="19"/>
       <c r="BI85" s="19">
-        <f t="shared" ref="BI85" si="356">+BI67/BI66</f>
+        <f t="shared" ref="BI85" si="346">+BI67/BI66</f>
         <v>0.18934280639431617</v>
       </c>
       <c r="BJ85" s="19">
-        <f t="shared" ref="BJ85" si="357">+BJ67/BJ66</f>
+        <f t="shared" ref="BJ85" si="347">+BJ67/BJ66</f>
         <v>0.18853848762292302</v>
       </c>
       <c r="BK85" s="19">
-        <f t="shared" ref="BK85" si="358">+BK67/BK66</f>
+        <f t="shared" ref="BK85" si="348">+BK67/BK66</f>
         <v>7.6450721522873813E-2</v>
       </c>
       <c r="BL85" s="19">
-        <f t="shared" ref="BL85:BQ85" si="359">+BL67/BL66</f>
+        <f t="shared" ref="BL85:BQ85" si="349">+BL67/BL66</f>
         <v>9.0040532715691957E-2</v>
       </c>
       <c r="BM85" s="19">
-        <f t="shared" si="359"/>
+        <f t="shared" si="349"/>
         <v>9.1036023457134879E-2</v>
       </c>
       <c r="BN85" s="19">
-        <f t="shared" si="359"/>
+        <f t="shared" si="349"/>
         <v>9.1716915264995244E-2</v>
       </c>
       <c r="BO85" s="19">
-        <f t="shared" si="359"/>
+        <f t="shared" si="349"/>
         <v>7.8917050691244245E-2</v>
       </c>
       <c r="BP85" s="19">
-        <f t="shared" si="359"/>
+        <f t="shared" si="349"/>
         <v>8.7567567567567561E-2</v>
       </c>
       <c r="BQ85" s="19">
-        <f t="shared" si="359"/>
+        <f t="shared" si="349"/>
         <v>8.7848500789058384E-2</v>
       </c>
       <c r="BR85" s="19">
@@ -26934,31 +26943,31 @@
         <v>9.6755504055619931E-2</v>
       </c>
       <c r="BV85" s="19">
-        <f t="shared" ref="BV85:CD85" si="360">+BV67/BV66</f>
+        <f t="shared" ref="BV85:CD85" si="350">+BV67/BV66</f>
         <v>9.6443132292984679E-2</v>
       </c>
       <c r="BW85" s="19">
-        <f t="shared" si="360"/>
+        <f t="shared" si="350"/>
         <v>0.1234113712374582</v>
       </c>
       <c r="BX85" s="19">
-        <f t="shared" si="360"/>
+        <f t="shared" si="350"/>
         <v>0.12653834017040075</v>
       </c>
       <c r="BY85" s="19">
-        <f t="shared" si="360"/>
+        <f t="shared" si="350"/>
         <v>0.12783291364242336</v>
       </c>
       <c r="BZ85" s="19">
-        <f t="shared" si="360"/>
+        <f t="shared" si="350"/>
         <v>0.12496302868973676</v>
       </c>
       <c r="CA85" s="19">
-        <f t="shared" si="360"/>
+        <f t="shared" si="350"/>
         <v>0.11802184466019418</v>
       </c>
       <c r="CB85" s="19">
-        <f t="shared" si="360"/>
+        <f t="shared" si="350"/>
         <v>0.12982644961657475</v>
       </c>
       <c r="CC85" s="19">
@@ -26966,58 +26975,61 @@
         <v>0.1274432118330692</v>
       </c>
       <c r="CD85" s="19">
-        <f t="shared" si="360"/>
+        <f t="shared" si="350"/>
         <v>0.15</v>
       </c>
       <c r="CE85" s="19">
-        <f t="shared" ref="CE85:CH85" si="361">+CE67/CE66</f>
+        <f t="shared" ref="CE85:CH85" si="351">+CE67/CE66</f>
         <v>0.1364907375043691</v>
       </c>
       <c r="CF85" s="19">
-        <f t="shared" si="361"/>
+        <f t="shared" si="351"/>
         <v>9.4106311225309144E-2</v>
       </c>
       <c r="CG85" s="19">
-        <f t="shared" si="361"/>
+        <f t="shared" si="351"/>
         <v>0.1549652118912081</v>
       </c>
       <c r="CH85" s="19">
-        <f t="shared" si="361"/>
+        <f t="shared" si="351"/>
         <v>6.2390017597184454E-2</v>
       </c>
       <c r="CI85" s="19">
-        <f t="shared" ref="CI85:CL85" si="362">+CI67/CI66</f>
+        <f t="shared" ref="CI85:CL85" si="352">+CI67/CI66</f>
         <v>0.14282860567319217</v>
       </c>
       <c r="CJ85" s="19">
-        <f t="shared" si="362"/>
+        <f t="shared" si="352"/>
         <v>0.16184542352766651</v>
       </c>
       <c r="CK85" s="19">
-        <f t="shared" si="362"/>
+        <f t="shared" si="352"/>
         <v>0.15957116221255438</v>
       </c>
       <c r="CL85" s="19">
-        <f t="shared" si="362"/>
+        <f t="shared" si="352"/>
         <v>0.15142054324071183</v>
       </c>
       <c r="CM85" s="19">
-        <f t="shared" ref="CM85:CP85" si="363">+CM67/CM66</f>
+        <f t="shared" ref="CM85:CQ85" si="353">+CM67/CM66</f>
         <v>0.13854697429438367</v>
       </c>
       <c r="CN85" s="19">
-        <f t="shared" si="363"/>
+        <f t="shared" si="353"/>
         <v>0.14307692307692307</v>
       </c>
       <c r="CO85" s="19">
-        <f t="shared" si="363"/>
+        <f t="shared" si="353"/>
         <v>0.10000000000000002</v>
       </c>
       <c r="CP85" s="19">
-        <f t="shared" si="363"/>
+        <f t="shared" si="353"/>
         <v>0.1</v>
       </c>
-      <c r="CQ85" s="19"/>
+      <c r="CQ85" s="19">
+        <f t="shared" si="353"/>
+        <v>8.1419293521305239E-2</v>
+      </c>
       <c r="CR85" s="19"/>
       <c r="CS85" s="19"/>
       <c r="CT85" s="19"/>
@@ -27031,55 +27043,55 @@
       <c r="DB85" s="19"/>
       <c r="DC85" s="19"/>
       <c r="DD85" s="19">
-        <f t="shared" ref="DD85" si="364">+DD67/DD66</f>
+        <f t="shared" ref="DD85" si="354">+DD67/DD66</f>
         <v>8.7406084951275761E-2</v>
       </c>
       <c r="DE85" s="19">
-        <f t="shared" ref="DE85:DM85" si="365">+DE67/DE66</f>
+        <f t="shared" ref="DE85:DM85" si="355">+DE67/DE66</f>
         <v>8.5823964902659713E-2</v>
       </c>
       <c r="DF85" s="19">
-        <f t="shared" si="365"/>
+        <f t="shared" si="355"/>
         <v>0.10015614543832255</v>
       </c>
       <c r="DG85" s="19">
-        <f t="shared" si="365"/>
+        <f t="shared" si="355"/>
         <v>0.12574038945453136</v>
       </c>
       <c r="DH85" s="19">
-        <f t="shared" si="365"/>
+        <f t="shared" si="355"/>
         <v>0.13161795219388039</v>
       </c>
       <c r="DI85" s="19">
-        <f t="shared" si="365"/>
+        <f t="shared" si="355"/>
         <v>0.11160495840809004</v>
       </c>
       <c r="DJ85" s="19">
-        <f t="shared" si="365"/>
+        <f t="shared" si="355"/>
         <v>0.15466265403229087</v>
       </c>
       <c r="DK85" s="19">
-        <f t="shared" si="365"/>
+        <f t="shared" si="355"/>
         <v>0.11888044204108278</v>
       </c>
       <c r="DL85" s="19">
-        <f t="shared" si="365"/>
+        <f t="shared" si="355"/>
         <v>0.15</v>
       </c>
       <c r="DM85" s="19">
-        <f t="shared" si="365"/>
+        <f t="shared" si="355"/>
         <v>0.15</v>
       </c>
       <c r="DN85" s="19">
-        <f t="shared" ref="DN85:DP85" si="366">+DN67/DN66</f>
+        <f t="shared" ref="DN85:DP85" si="356">+DN67/DN66</f>
         <v>0.15</v>
       </c>
       <c r="DO85" s="19">
-        <f t="shared" si="366"/>
+        <f t="shared" si="356"/>
         <v>0.15</v>
       </c>
       <c r="DP85" s="19">
-        <f t="shared" si="366"/>
+        <f t="shared" si="356"/>
         <v>0.15</v>
       </c>
     </row>
@@ -27088,59 +27100,59 @@
         <v>145</v>
       </c>
       <c r="CA87" s="6">
-        <f t="shared" ref="CA87:CG87" si="367">CA88-CA97</f>
+        <f t="shared" ref="CA87:CG87" si="357">CA88-CA97</f>
         <v>-65642</v>
       </c>
       <c r="CB87" s="6">
-        <f t="shared" si="367"/>
+        <f t="shared" si="357"/>
         <v>-62727</v>
       </c>
       <c r="CC87" s="6">
-        <f t="shared" si="367"/>
+        <f t="shared" si="357"/>
         <v>-57492</v>
       </c>
       <c r="CD87" s="6">
-        <f t="shared" si="367"/>
+        <f t="shared" si="357"/>
         <v>0</v>
       </c>
       <c r="CE87" s="6">
-        <f t="shared" si="367"/>
+        <f t="shared" si="357"/>
         <v>-55114</v>
       </c>
       <c r="CF87" s="6">
-        <f t="shared" si="367"/>
+        <f t="shared" si="357"/>
         <v>-51961</v>
       </c>
       <c r="CG87" s="6">
-        <f t="shared" si="367"/>
+        <f t="shared" si="357"/>
         <v>-47181</v>
       </c>
       <c r="CH87" s="6">
-        <f t="shared" ref="CH87:CN87" si="368">CH88-CH97</f>
+        <f t="shared" ref="CH87:CN87" si="358">CH88-CH97</f>
         <v>-46265</v>
       </c>
       <c r="CI87" s="6">
-        <f t="shared" si="368"/>
+        <f t="shared" si="358"/>
         <v>-55627</v>
       </c>
       <c r="CJ87" s="6">
-        <f t="shared" si="368"/>
+        <f t="shared" si="358"/>
         <v>-57205</v>
       </c>
       <c r="CK87" s="6">
-        <f t="shared" si="368"/>
+        <f t="shared" si="358"/>
         <v>-63527</v>
       </c>
       <c r="CL87" s="6">
-        <f t="shared" si="368"/>
+        <f t="shared" si="358"/>
         <v>-61310</v>
       </c>
       <c r="CM87" s="6">
-        <f t="shared" si="368"/>
+        <f t="shared" si="358"/>
         <v>-64426</v>
       </c>
       <c r="CN87" s="6">
-        <f t="shared" si="368"/>
+        <f t="shared" si="358"/>
         <v>-63704</v>
       </c>
       <c r="CO87" s="6"/>
@@ -28301,43 +28313,43 @@
       </c>
       <c r="CD95" s="6"/>
       <c r="CE95" s="6">
-        <f t="shared" ref="CE95:CK95" si="369">SUM(CE88:CE94)</f>
+        <f t="shared" ref="CE95:CK95" si="359">SUM(CE88:CE94)</f>
         <v>134544</v>
       </c>
       <c r="CF95" s="6">
-        <f t="shared" si="369"/>
+        <f t="shared" si="359"/>
         <v>135367</v>
       </c>
       <c r="CG95" s="6">
-        <f t="shared" si="369"/>
+        <f t="shared" si="359"/>
         <v>136221</v>
       </c>
       <c r="CH95" s="6">
-        <f t="shared" si="369"/>
+        <f t="shared" si="359"/>
         <v>134711</v>
       </c>
       <c r="CI95" s="6">
-        <f t="shared" si="369"/>
+        <f t="shared" si="359"/>
         <v>148874</v>
       </c>
       <c r="CJ95" s="6">
-        <f t="shared" si="369"/>
+        <f t="shared" si="359"/>
         <v>141937</v>
       </c>
       <c r="CK95" s="6">
-        <f t="shared" si="369"/>
+        <f t="shared" si="359"/>
         <v>143422</v>
       </c>
       <c r="CL95" s="6">
-        <f t="shared" ref="CL95:CN95" si="370">SUM(CL88:CL94)</f>
+        <f t="shared" ref="CL95:CN95" si="360">SUM(CL88:CL94)</f>
         <v>135161</v>
       </c>
       <c r="CM95" s="6">
-        <f t="shared" si="370"/>
+        <f t="shared" si="360"/>
         <v>136165</v>
       </c>
       <c r="CN95" s="6">
-        <f t="shared" si="370"/>
+        <f t="shared" si="360"/>
         <v>137182</v>
       </c>
       <c r="CO95" s="6"/>
@@ -29216,35 +29228,35 @@
       </c>
       <c r="CD102" s="6"/>
       <c r="CE102" s="6">
-        <f t="shared" ref="CE102:CL102" si="371">SUM(CE97:CE101)</f>
+        <f t="shared" ref="CE102:CL102" si="361">SUM(CE97:CE101)</f>
         <v>134544</v>
       </c>
       <c r="CF102" s="6">
-        <f t="shared" si="371"/>
+        <f t="shared" si="361"/>
         <v>135367</v>
       </c>
       <c r="CG102" s="6">
-        <f t="shared" si="371"/>
+        <f t="shared" si="361"/>
         <v>136221</v>
       </c>
       <c r="CH102" s="6">
-        <f t="shared" si="371"/>
+        <f t="shared" si="361"/>
         <v>134711</v>
       </c>
       <c r="CI102" s="6">
-        <f t="shared" si="371"/>
+        <f t="shared" si="361"/>
         <v>148874</v>
       </c>
       <c r="CJ102" s="6">
-        <f t="shared" si="371"/>
+        <f t="shared" si="361"/>
         <v>141937</v>
       </c>
       <c r="CK102" s="6">
-        <f t="shared" si="371"/>
+        <f t="shared" si="361"/>
         <v>143422</v>
       </c>
       <c r="CL102" s="6">
-        <f t="shared" si="371"/>
+        <f t="shared" si="361"/>
         <v>135161</v>
       </c>
       <c r="CM102" s="6">
@@ -29371,31 +29383,31 @@
       <c r="CC104" s="6"/>
       <c r="CD104" s="6"/>
       <c r="CE104" s="6">
-        <f t="shared" ref="CE104:CK104" si="372">+CE68</f>
+        <f t="shared" ref="CE104:CK104" si="362">+CE68</f>
         <v>4941</v>
       </c>
       <c r="CF104" s="6">
-        <f t="shared" si="372"/>
+        <f t="shared" si="362"/>
         <v>5641</v>
       </c>
       <c r="CG104" s="6">
-        <f t="shared" si="372"/>
+        <f t="shared" si="362"/>
         <v>5344</v>
       </c>
       <c r="CH104" s="6">
-        <f t="shared" si="372"/>
+        <f t="shared" si="362"/>
         <v>5861</v>
       </c>
       <c r="CI104" s="6">
-        <f t="shared" si="372"/>
+        <f t="shared" si="362"/>
         <v>4291</v>
       </c>
       <c r="CJ104" s="6">
-        <f t="shared" si="372"/>
+        <f t="shared" si="362"/>
         <v>5650</v>
       </c>
       <c r="CK104" s="6">
-        <f t="shared" si="372"/>
+        <f t="shared" si="362"/>
         <v>5409</v>
       </c>
       <c r="CL104" s="6">
@@ -30487,31 +30499,31 @@
         <v>4908</v>
       </c>
       <c r="CE114" s="6">
-        <f t="shared" ref="CE114:CK114" si="373">SUM(CE105:CE113)</f>
+        <f t="shared" ref="CE114:CK114" si="363">SUM(CE105:CE113)</f>
         <v>4193</v>
       </c>
       <c r="CF114" s="6">
-        <f t="shared" si="373"/>
+        <f t="shared" si="363"/>
         <v>6319</v>
       </c>
       <c r="CG114" s="6">
-        <f t="shared" si="373"/>
+        <f t="shared" si="363"/>
         <v>7574</v>
       </c>
       <c r="CH114" s="6">
-        <f t="shared" si="373"/>
+        <f t="shared" si="363"/>
         <v>4753</v>
       </c>
       <c r="CI114" s="6">
-        <f t="shared" si="373"/>
+        <f t="shared" si="363"/>
         <v>4040</v>
       </c>
       <c r="CJ114" s="6">
-        <f t="shared" si="373"/>
+        <f t="shared" si="363"/>
         <v>2271</v>
       </c>
       <c r="CK114" s="6">
-        <f t="shared" si="373"/>
+        <f t="shared" si="363"/>
         <v>5447</v>
       </c>
       <c r="CL114" s="6">
@@ -31071,39 +31083,39 @@
       <c r="CC119" s="6"/>
       <c r="CD119" s="6"/>
       <c r="CE119" s="6">
-        <f t="shared" ref="CE119:CM119" si="374">SUM(CE116:CE118)</f>
+        <f t="shared" ref="CE119:CM119" si="364">SUM(CE116:CE118)</f>
         <v>-499</v>
       </c>
       <c r="CF119" s="6">
-        <f t="shared" si="374"/>
+        <f t="shared" si="364"/>
         <v>-341</v>
       </c>
       <c r="CG119" s="6">
-        <f t="shared" si="374"/>
+        <f t="shared" si="364"/>
         <v>-369</v>
       </c>
       <c r="CH119" s="6">
-        <f t="shared" si="374"/>
+        <f t="shared" si="364"/>
         <v>-800</v>
       </c>
       <c r="CI119" s="6">
-        <f t="shared" si="374"/>
+        <f t="shared" si="364"/>
         <v>-9588</v>
       </c>
       <c r="CJ119" s="6">
-        <f t="shared" si="374"/>
+        <f t="shared" si="364"/>
         <v>-1102</v>
       </c>
       <c r="CK119" s="6">
-        <f t="shared" si="374"/>
+        <f t="shared" si="364"/>
         <v>-8256</v>
       </c>
       <c r="CL119" s="6">
-        <f t="shared" si="374"/>
+        <f t="shared" si="364"/>
         <v>-1874</v>
       </c>
       <c r="CM119" s="6">
-        <f t="shared" si="374"/>
+        <f t="shared" si="364"/>
         <v>-735</v>
       </c>
       <c r="CN119" s="6"/>
@@ -31443,39 +31455,39 @@
         <v>-6972</v>
       </c>
       <c r="CE127" s="6">
-        <f t="shared" ref="CE127:CM127" si="375">SUM(CE121:CE126)</f>
+        <f t="shared" ref="CE127:CM127" si="365">SUM(CE121:CE126)</f>
         <v>-6192</v>
       </c>
       <c r="CF127" s="6">
-        <f t="shared" si="375"/>
+        <f t="shared" si="365"/>
         <v>-3920</v>
       </c>
       <c r="CG127" s="6">
-        <f t="shared" si="375"/>
+        <f t="shared" si="365"/>
         <v>-2661</v>
       </c>
       <c r="CH127" s="6">
-        <f t="shared" si="375"/>
+        <f t="shared" si="365"/>
         <v>-4449</v>
       </c>
       <c r="CI127" s="6">
-        <f t="shared" si="375"/>
+        <f t="shared" si="365"/>
         <v>10819</v>
       </c>
       <c r="CJ127" s="6">
-        <f t="shared" si="375"/>
+        <f t="shared" si="365"/>
         <v>-6097</v>
       </c>
       <c r="CK127" s="6">
-        <f t="shared" si="375"/>
+        <f t="shared" si="365"/>
         <v>-3072</v>
       </c>
       <c r="CL127" s="6">
-        <f t="shared" si="375"/>
+        <f t="shared" si="365"/>
         <v>-6861</v>
       </c>
       <c r="CM127" s="6">
-        <f t="shared" si="375"/>
+        <f t="shared" si="365"/>
         <v>-1258</v>
       </c>
       <c r="CN127" s="6"/>
@@ -31543,39 +31555,39 @@
         <v>-3648</v>
       </c>
       <c r="CE129" s="6">
-        <f t="shared" ref="CE129:CM129" si="376">+CE128+CE127+CE119+CE114</f>
+        <f t="shared" ref="CE129:CM129" si="366">+CE128+CE127+CE119+CE114</f>
         <v>-2490</v>
       </c>
       <c r="CF129" s="6">
-        <f t="shared" si="376"/>
+        <f t="shared" si="366"/>
         <v>2048</v>
       </c>
       <c r="CG129" s="6">
-        <f t="shared" si="376"/>
+        <f t="shared" si="366"/>
         <v>4528</v>
       </c>
       <c r="CH129" s="6">
-        <f t="shared" si="376"/>
+        <f t="shared" si="366"/>
         <v>-473</v>
       </c>
       <c r="CI129" s="6">
-        <f t="shared" si="376"/>
+        <f t="shared" si="366"/>
         <v>5253</v>
       </c>
       <c r="CJ129" s="6">
-        <f t="shared" si="376"/>
+        <f t="shared" si="366"/>
         <v>-4937</v>
       </c>
       <c r="CK129" s="6">
-        <f t="shared" si="376"/>
+        <f t="shared" si="366"/>
         <v>-5873</v>
       </c>
       <c r="CL129" s="6">
-        <f t="shared" si="376"/>
+        <f t="shared" si="366"/>
         <v>-1733</v>
       </c>
       <c r="CM129" s="6">
-        <f t="shared" si="376"/>
+        <f t="shared" si="366"/>
         <v>-349</v>
       </c>
       <c r="CN129" s="6"/>
